--- a/example/lab-data.original.xlsx
+++ b/example/lab-data.original.xlsx
@@ -29,7 +29,7 @@
     <definedName name="L_door">lists!$P$2:$P$4</definedName>
     <definedName name="L_level">lists!$S$2:$S$3</definedName>
     <definedName name="L_condition">lists!$V$2:$V$5</definedName>
-    <definedName name="L_plan">lists!$Y$2:$Y$7</definedName>
+    <definedName name="L_plan">lists!$Y$2:$Y$8</definedName>
     <definedName name="L_usage">lists!$AB$2:$AB$6</definedName>
     <definedName name="L_usage_source">lists!$AE$2:$AE$4</definedName>
     <definedName name="L_plug_type">lists!$AH$2:$AH$8</definedName>
@@ -41,7 +41,7 @@
     <definedName name="L_doc_status">lists!$AZ$2:$AZ$5</definedName>
     <definedName name="L_link_type">lists!$BC$2:$BC$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rooms'!$A$2:$K$102</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'placeables'!$A$2:$AB$1502</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'placeables'!$A$2:$AG$1502</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'equipment'!$A$2:$V$1002</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'services'!$A$2:$N$1002</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'circuits'!$A$2:$H$302</definedName>
@@ -486,60 +486,85 @@
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
-        <t>Must stay free in front: standing room, drawer pull-out, door swing. Applies in the plane it sits in: bench surface for things on a bench, floor for things on the floor.</t>
+        <t>Fume hoods, biosafety cabinets, gloveboxes, ovens: the working space inside, width along the front. Assumed centred left to right and flush with the front (the sash). Things can then be placed in it (mount = in, with x and y).</t>
       </text>
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
-        <t>Behind: ventilation, cables, hoses.</t>
+        <t>Working space inside, front to back: from the sash to the rear baffle.</t>
       </text>
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t>To your left as you face the front: hinge side, vents, access panels.</t>
+        <t>Working space inside, height above the work surface (up to the sash opening, for a fume hood).</t>
       </text>
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
-        <t>To your right as you face the front.</t>
+        <t>Height of the inside work surface above the floor (above the object's underside), cm.</t>
       </text>
     </comment>
     <comment ref="T1" authorId="0" shapeId="0">
       <text>
-        <t>Headroom above: lids that open upwards, sashes, hot exhaust. Checked against shelves and the ceiling.</t>
+        <t>Must stay free in front: standing room, drawer pull-out, door swing. Applies in the plane it sits in: bench surface for things on a bench, floor for things on the floor.</t>
       </text>
     </comment>
     <comment ref="U1" authorId="0" shapeId="0">
       <text>
-        <t>Fridges, freezers, cabinets: which side the door is hinged on, as you face the front (left, right, both = double doors). The swing is kept clear in front, and door_gap (settings) beside the hinge so it opens fully.</t>
+        <t>Behind: ventilation, cables, hoses.</t>
       </text>
     </comment>
     <comment ref="V1" authorId="0" shapeId="0">
       <text>
-        <t>yes = plumbing, structure or safety equipment. The layout must work around it.</t>
+        <t>To your left as you face the front: hinge side, vents, access panels.</t>
       </text>
     </comment>
     <comment ref="W1" authorId="0" shapeId="0">
       <text>
-        <t>yes = carts, pedestals on castors. Its position is its parking spot.</t>
+        <t>To your right as you face the front.</t>
       </text>
     </comment>
     <comment ref="X1" authorId="0" shapeId="0">
       <text>
-        <t>May other things sit on top? Blank = category default (bench, desk, table, shelf, cabinet, cart: yes; the rest: no).</t>
+        <t>Headroom above: lids that open upwards, sashes, hot exhaust. Checked against shelves and the ceiling.</t>
       </text>
     </comment>
     <comment ref="Y1" authorId="0" shapeId="0">
       <text>
-        <t>Containers only (drawer, shelf, cabinet, box): how full, 0-100, eyeballed. Finds consolidation opportunities.</t>
+        <t>Fridges, freezers, cabinets: which side the door is hinged on, as you face the front (left, right, both = double doors). The swing is kept clear in front, and door_gap (settings) beside the hinge so it opens fully.</t>
       </text>
     </comment>
     <comment ref="Z1" authorId="0" shapeId="0">
       <text>
+        <t>yes = plumbing, structure or safety equipment. The layout must work around it.</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0" shapeId="0">
+      <text>
+        <t>yes = carts, pedestals on castors. Its position is its parking spot.</t>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0" shapeId="0">
+      <text>
+        <t>May other things sit on top? Blank = category default (bench, desk, table, shelf, cabinet, cart: yes; the rest: no).</t>
+      </text>
+    </comment>
+    <comment ref="AC1" authorId="0" shapeId="0">
+      <text>
+        <t>Containers only (drawer, shelf, cabinet, box): how full, 0-100, eyeballed. Finds consolidation opportunities.</t>
+      </text>
+    </comment>
+    <comment ref="AD1" authorId="0" shapeId="0">
+      <text>
         <t>Containers: date the contents were last verified against the items sheet. Shown in the directory.</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AE1" authorId="0" shapeId="0">
+      <text>
+        <t>Filled = it's gone. The row stays as a record (with its equipment row: asset tag, serial), but it's left out of the maps, the checks, the layout and the search. Its drawers and parts go with it. Anything still pointing at it is flagged, so nothing is left behind. Never reuse the ID.</t>
+      </text>
+    </comment>
+    <comment ref="AF1" authorId="0" shapeId="0">
       <text>
         <t>What it is or does, for the keep_apart sheet: e.g. vibrates, vibration-sensitive, heat-source, flammable. Anything tagged there is kept at the distance it sets.</t>
       </text>
@@ -1558,7 +1583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1829,9 +1854,29 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sash_clearance</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Work inside a fume hood is kept at least this far behind the sash.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Whole number" error="A whole number above 0, in the unit shown." type="whole" operator="greaterThan">
+    <dataValidation sqref="B2:B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Whole number" error="A whole number above 0, in the unit shown." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -1853,7 +1898,7 @@
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="2" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
     <col width="2" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
@@ -1873,7 +1918,7 @@
     <col width="9" customWidth="1" min="22" max="22"/>
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="2" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
     <col width="31" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="9" customWidth="1" min="28" max="28"/>
@@ -2661,7 +2706,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>decommission</t>
+          <t>to be decommissioned</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2751,7 +2796,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>inside parent; no position</t>
+          <t>inside parent: no position (drawer), or x/y inside a fume hood</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2766,12 +2811,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>decommissioned</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>arriving, needs a spot</t>
+          <t>gone: kept as a record</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2871,7 +2916,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>undecided</t>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>arriving, needs a spot</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -2942,6 +2992,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>towards the left</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>undecided</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -4081,7 +4136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1502"/>
+  <dimension ref="A1:AG1502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4105,13 +4160,18 @@
     <col width="8" customWidth="1" min="19" max="19"/>
     <col width="8" customWidth="1" min="20" max="20"/>
     <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="7" customWidth="1" min="22" max="22"/>
-    <col width="7" customWidth="1" min="23" max="23"/>
-    <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="7" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="40" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="7" customWidth="1" min="26" max="26"/>
+    <col width="7" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="7" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
+    <col width="40" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4192,65 +4252,90 @@
       </c>
       <c r="P1" s="7" t="inlineStr">
         <is>
+          <t>inner_w</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>inner_d</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>inner_h</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>inner_z</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
           <t>clear_front</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>clear_back</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
+      <c r="V1" s="7" t="inlineStr">
         <is>
           <t>clear_left</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>clear_right</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="X1" s="7" t="inlineStr">
         <is>
           <t>clear_top</t>
         </is>
       </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="Y1" s="7" t="inlineStr">
         <is>
           <t>door</t>
         </is>
       </c>
-      <c r="V1" s="7" t="inlineStr">
+      <c r="Z1" s="7" t="inlineStr">
         <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="W1" s="7" t="inlineStr">
+      <c r="AA1" s="7" t="inlineStr">
         <is>
           <t>mobile</t>
         </is>
       </c>
-      <c r="X1" s="7" t="inlineStr">
+      <c r="AB1" s="7" t="inlineStr">
         <is>
           <t>stackable</t>
         </is>
       </c>
-      <c r="Y1" s="7" t="inlineStr">
+      <c r="AC1" s="7" t="inlineStr">
         <is>
           <t>fill</t>
         </is>
       </c>
-      <c r="Z1" s="7" t="inlineStr">
+      <c r="AD1" s="7" t="inlineStr">
         <is>
           <t>checked</t>
         </is>
       </c>
-      <c r="AA1" s="7" t="inlineStr">
+      <c r="AE1" s="7" t="inlineStr">
+        <is>
+          <t>decommissioned</t>
+        </is>
+      </c>
+      <c r="AF1" s="7" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="AB1" s="7" t="inlineStr">
+      <c r="AG1" s="7" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -4334,65 +4419,90 @@
       </c>
       <c r="P2" s="8" t="inlineStr">
         <is>
+          <t>cm, inside</t>
+        </is>
+      </c>
+      <c r="Q2" s="8" t="inlineStr">
+        <is>
+          <t>cm, inside</t>
+        </is>
+      </c>
+      <c r="R2" s="8" t="inlineStr">
+        <is>
+          <t>cm, inside</t>
+        </is>
+      </c>
+      <c r="S2" s="8" t="inlineStr">
+        <is>
+          <t>cm, work surface</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
           <t>cm</t>
         </is>
       </c>
-      <c r="Q2" s="8" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>cm</t>
         </is>
       </c>
-      <c r="R2" s="8" t="inlineStr">
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>cm, your left</t>
         </is>
       </c>
-      <c r="S2" s="8" t="inlineStr">
+      <c r="W2" s="8" t="inlineStr">
         <is>
           <t>cm, your right</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
+      <c r="X2" s="8" t="inlineStr">
         <is>
           <t>cm, lids</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
+      <c r="Y2" s="8" t="inlineStr">
         <is>
           <t>hinge side</t>
         </is>
       </c>
-      <c r="V2" s="8" t="inlineStr">
+      <c r="Z2" s="8" t="inlineStr">
         <is>
           <t>yes = can't move</t>
         </is>
       </c>
-      <c r="W2" s="8" t="inlineStr">
+      <c r="AA2" s="8" t="inlineStr">
         <is>
           <t>yes = wheels</t>
         </is>
       </c>
-      <c r="X2" s="8" t="inlineStr">
+      <c r="AB2" s="8" t="inlineStr">
         <is>
           <t>things on top?</t>
         </is>
       </c>
-      <c r="Y2" s="8" t="inlineStr">
+      <c r="AC2" s="8" t="inlineStr">
         <is>
           <t>% full</t>
         </is>
       </c>
-      <c r="Z2" s="8" t="inlineStr">
+      <c r="AD2" s="8" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="AA2" s="8" t="inlineStr">
+      <c r="AE2" s="8" t="inlineStr">
+        <is>
+          <t>date it left</t>
+        </is>
+      </c>
+      <c r="AF2" s="8" t="inlineStr">
         <is>
           <t>tags; separated; by ;</t>
         </is>
       </c>
-      <c r="AB2" s="8" t="n"/>
+      <c r="AG2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4440,16 +4550,17 @@
       <c r="N3" t="n">
         <v>210</v>
       </c>
-      <c r="P3" t="n">
+      <c r="T3" t="n">
         <v>100</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AB3" t="inlineStr">
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>clear_front = door swing</t>
         </is>
@@ -4504,13 +4615,14 @@
       <c r="N4" t="n">
         <v>120</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AB4" t="inlineStr">
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>sill at 100 cm: benches fit under, tall units block it</t>
         </is>
@@ -4557,13 +4669,14 @@
       <c r="N5" t="n">
         <v>270</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z5" s="10" t="n"/>
-      <c r="AB5" t="inlineStr">
+      <c r="AD5" s="10" t="n"/>
+      <c r="AE5" s="10" t="n"/>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>pilaster on the left wall</t>
         </is>
@@ -4618,16 +4731,17 @@
       <c r="N6" t="n">
         <v>80</v>
       </c>
-      <c r="P6" t="n">
+      <c r="T6" t="n">
         <v>100</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z6" s="10" t="n"/>
-      <c r="AB6" t="inlineStr">
+      <c r="AD6" s="10" t="n"/>
+      <c r="AE6" s="10" t="n"/>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>keep clear in front (check local rules)</t>
         </is>
@@ -4682,16 +4796,17 @@
       <c r="N7" t="n">
         <v>40</v>
       </c>
-      <c r="P7" t="n">
+      <c r="T7" t="n">
         <v>100</v>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z7" s="10" t="n"/>
-      <c r="AB7" t="inlineStr">
+      <c r="AD7" s="10" t="n"/>
+      <c r="AE7" s="10" t="n"/>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>must stay unobstructed</t>
         </is>
@@ -4739,14 +4854,27 @@
         <v>240</v>
       </c>
       <c r="P8" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>65</v>
+      </c>
+      <c r="R8" t="n">
+        <v>110</v>
+      </c>
+      <c r="S8" t="n">
+        <v>90</v>
+      </c>
+      <c r="T8" t="n">
         <v>100</v>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z8" s="10" t="n"/>
+      <c r="AD8" s="10" t="n"/>
+      <c r="AE8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4779,6 +4907,12 @@
           <t>in</t>
         </is>
       </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>15</v>
+      </c>
       <c r="L9" t="n">
         <v>20</v>
       </c>
@@ -4788,7 +4922,8 @@
       <c r="N9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" s="10" t="n"/>
+      <c r="AD9" s="10" t="n"/>
+      <c r="AE9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4821,6 +4956,12 @@
           <t>in</t>
         </is>
       </c>
+      <c r="G10" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" t="n">
+        <v>30</v>
+      </c>
       <c r="L10" t="n">
         <v>20</v>
       </c>
@@ -4830,7 +4971,13 @@
       <c r="N10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" s="10" t="n"/>
+      <c r="AD10" s="10" t="n"/>
+      <c r="AE10" s="10" t="n"/>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>EXAMPLE WARNING: 5 cm from the sash</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4873,16 +5020,17 @@
       <c r="N11" t="n">
         <v>90</v>
       </c>
-      <c r="P11" t="n">
+      <c r="T11" t="n">
         <v>90</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z11" s="10" t="n"/>
-      <c r="AB11" t="inlineStr">
+      <c r="AD11" s="10" t="n"/>
+      <c r="AE11" s="10" t="n"/>
+      <c r="AG11" t="inlineStr">
         <is>
           <t>fixed: plumbing; cupboard base, so nothing fits under it</t>
         </is>
@@ -4934,7 +5082,8 @@
       <c r="N12" t="n">
         <v>30</v>
       </c>
-      <c r="Z12" s="10" t="n"/>
+      <c r="AD12" s="10" t="n"/>
+      <c r="AE12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4982,16 +5131,17 @@
       <c r="N13" t="n">
         <v>50</v>
       </c>
-      <c r="T13" t="n">
+      <c r="X13" t="n">
         <v>40</v>
       </c>
-      <c r="Z13" s="10" t="n"/>
-      <c r="AA13" t="inlineStr">
+      <c r="AD13" s="10" t="n"/>
+      <c r="AE13" s="10" t="n"/>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>heat-source</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>top-loading lid</t>
         </is>
@@ -5043,7 +5193,8 @@
       <c r="N14" t="n">
         <v>15</v>
       </c>
-      <c r="Z14" s="10" t="n"/>
+      <c r="AD14" s="10" t="n"/>
+      <c r="AE14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5091,18 +5242,19 @@
       <c r="N15" t="n">
         <v>30</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="Z15" s="10" t="n"/>
-      <c r="AB15" t="inlineStr">
+      <c r="AD15" s="10" t="n"/>
+      <c r="AE15" s="10" t="n"/>
+      <c r="AG15" t="inlineStr">
         <is>
           <t>an occupant, not a cutout: blocks this bit of bench top</t>
         </is>
@@ -5145,8 +5297,9 @@
           <t>group</t>
         </is>
       </c>
-      <c r="Z16" s="10" t="n"/>
-      <c r="AB16" t="inlineStr">
+      <c r="AD16" s="10" t="n"/>
+      <c r="AE16" s="10" t="n"/>
+      <c r="AG16" t="inlineStr">
         <is>
           <t>geometry lives in its parts .A and .B</t>
         </is>
@@ -5201,10 +5354,11 @@
       <c r="O17" t="n">
         <v>88</v>
       </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
         <v>90</v>
       </c>
-      <c r="Z17" s="10" t="n"/>
+      <c r="AD17" s="10" t="n"/>
+      <c r="AE17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5260,11 +5414,12 @@
       <c r="O18" t="n">
         <v>88</v>
       </c>
-      <c r="P18" t="n">
+      <c r="T18" t="n">
         <v>90</v>
       </c>
-      <c r="Z18" s="10" t="n"/>
-      <c r="AB18" t="inlineStr">
+      <c r="AD18" s="10" t="n"/>
+      <c r="AE18" s="10" t="n"/>
+      <c r="AG18" t="inlineStr">
         <is>
           <t>faces E: its front is the inside of the L</t>
         </is>
@@ -5316,10 +5471,11 @@
       <c r="N19" t="n">
         <v>30</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="U19" t="n">
         <v>10</v>
       </c>
-      <c r="Z19" s="10" t="n"/>
+      <c r="AD19" s="10" t="n"/>
+      <c r="AE19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5367,22 +5523,23 @@
       <c r="N20" t="n">
         <v>35</v>
       </c>
-      <c r="R20" t="n">
+      <c r="V20" t="n">
         <v>10</v>
       </c>
-      <c r="S20" t="n">
+      <c r="W20" t="n">
         <v>10</v>
       </c>
-      <c r="T20" t="n">
+      <c r="X20" t="n">
         <v>40</v>
       </c>
-      <c r="Z20" s="10" t="n"/>
-      <c r="AA20" t="inlineStr">
+      <c r="AD20" s="10" t="n"/>
+      <c r="AE20" s="10" t="n"/>
+      <c r="AF20" t="inlineStr">
         <is>
           <t>vibrates</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>EXAMPLE PROBLEM: open lid reaches 165 cm, SHELF-01 is at 150 cm</t>
         </is>
@@ -5434,8 +5591,9 @@
       <c r="N21" t="n">
         <v>50</v>
       </c>
-      <c r="Z21" s="10" t="n"/>
-      <c r="AB21" t="inlineStr">
+      <c r="AD21" s="10" t="n"/>
+      <c r="AE21" s="10" t="n"/>
+      <c r="AG21" t="inlineStr">
         <is>
           <t>reserves bench top for actual work</t>
         </is>
@@ -5487,16 +5645,17 @@
       <c r="N22" t="n">
         <v>60</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
         <v>50</v>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z22" s="10" t="n"/>
-      <c r="AB22" t="inlineStr">
+      <c r="AD22" s="10" t="n"/>
+      <c r="AE22" s="10" t="n"/>
+      <c r="AG22" t="inlineStr">
         <is>
           <t>clear_front = drawer pull-out</t>
         </is>
@@ -5542,12 +5701,13 @@
       <c r="N23" t="n">
         <v>8</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AC23" t="n">
         <v>60</v>
       </c>
-      <c r="Z23" s="10" t="n">
+      <c r="AD23" s="10" t="n">
         <v>46286</v>
       </c>
+      <c r="AE23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5589,12 +5749,13 @@
       <c r="N24" t="n">
         <v>12</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AC24" t="n">
         <v>90</v>
       </c>
-      <c r="Z24" s="10" t="n">
+      <c r="AD24" s="10" t="n">
         <v>46286</v>
       </c>
+      <c r="AE24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5636,10 +5797,11 @@
       <c r="N25" t="n">
         <v>25</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AC25" t="n">
         <v>30</v>
       </c>
-      <c r="Z25" s="10" t="n"/>
+      <c r="AD25" s="10" t="n"/>
+      <c r="AE25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5687,8 +5849,9 @@
       <c r="N26" t="n">
         <v>35</v>
       </c>
-      <c r="Z26" s="10" t="n"/>
-      <c r="AB26" t="inlineStr">
+      <c r="AD26" s="10" t="n"/>
+      <c r="AE26" s="10" t="n"/>
+      <c r="AG26" t="inlineStr">
         <is>
           <t>broken, plan = dispose: frees bench top</t>
         </is>
@@ -5740,11 +5903,12 @@
       <c r="N27" t="n">
         <v>85</v>
       </c>
-      <c r="P27" t="n">
+      <c r="T27" t="n">
         <v>60</v>
       </c>
-      <c r="Z27" s="10" t="n"/>
-      <c r="AB27" t="inlineStr">
+      <c r="AD27" s="10" t="n"/>
+      <c r="AE27" s="10" t="n"/>
+      <c r="AG27" t="inlineStr">
         <is>
           <t>exactly as tall as the space under the bench</t>
         </is>
@@ -5794,7 +5958,8 @@
       <c r="N28" t="n">
         <v>3</v>
       </c>
-      <c r="Z28" s="10" t="n"/>
+      <c r="AD28" s="10" t="n"/>
+      <c r="AE28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5842,10 +6007,11 @@
       <c r="N29" t="n">
         <v>15</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AC29" t="n">
         <v>50</v>
       </c>
-      <c r="Z29" s="10" t="n"/>
+      <c r="AD29" s="10" t="n"/>
+      <c r="AE29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5896,11 +6062,12 @@
       <c r="O30" t="n">
         <v>80</v>
       </c>
-      <c r="P30" t="n">
+      <c r="T30" t="n">
         <v>90</v>
       </c>
-      <c r="Z30" s="10" t="n"/>
-      <c r="AB30" t="inlineStr">
+      <c r="AD30" s="10" t="n"/>
+      <c r="AE30" s="10" t="n"/>
+      <c r="AG30" t="inlineStr">
         <is>
           <t>under the window</t>
         </is>
@@ -5952,16 +6119,17 @@
       <c r="N31" t="n">
         <v>35</v>
       </c>
-      <c r="P31" t="n">
+      <c r="T31" t="n">
         <v>30</v>
       </c>
-      <c r="Z31" s="10" t="n"/>
-      <c r="AA31" t="inlineStr">
+      <c r="AD31" s="10" t="n"/>
+      <c r="AE31" s="10" t="n"/>
+      <c r="AF31" t="inlineStr">
         <is>
           <t>vibration-sensitive</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>vibration-sensitive: away from door, HVAC, centrifuge</t>
         </is>
@@ -6013,8 +6181,9 @@
       <c r="N32" t="n">
         <v>15</v>
       </c>
-      <c r="Z32" s="10" t="n"/>
-      <c r="AB32" t="inlineStr">
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="10" t="n"/>
+      <c r="AG32" t="inlineStr">
         <is>
           <t>EXAMPLE PROBLEM: placed on top of BAL-01</t>
         </is>
@@ -6060,10 +6229,11 @@
       <c r="N33" t="n">
         <v>10</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AC33" t="n">
         <v>40</v>
       </c>
-      <c r="Z33" s="10" t="n"/>
+      <c r="AD33" s="10" t="n"/>
+      <c r="AE33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6105,10 +6275,11 @@
       <c r="N34" t="n">
         <v>10</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AC34" t="n">
         <v>75</v>
       </c>
-      <c r="Z34" s="10" t="n"/>
+      <c r="AD34" s="10" t="n"/>
+      <c r="AE34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6156,16 +6327,17 @@
       <c r="N35" t="n">
         <v>85</v>
       </c>
-      <c r="P35" t="n">
+      <c r="T35" t="n">
         <v>60</v>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="Z35" s="10" t="n"/>
-      <c r="AB35" t="inlineStr">
+      <c r="AD35" s="10" t="n"/>
+      <c r="AE35" s="10" t="n"/>
+      <c r="AG35" t="inlineStr">
         <is>
           <t>EXAMPLE PROBLEM: 85 cm tall, only 80 cm free under BENCH-02</t>
         </is>
@@ -6217,16 +6389,17 @@
       <c r="N36" t="n">
         <v>35</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="U36" t="n">
         <v>10</v>
       </c>
-      <c r="Z36" s="10" t="n"/>
-      <c r="AA36" t="inlineStr">
+      <c r="AD36" s="10" t="n"/>
+      <c r="AE36" s="10" t="n"/>
+      <c r="AF36" t="inlineStr">
         <is>
           <t>vibrates; noisy</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>noisy and warm</t>
         </is>
@@ -6278,25 +6451,26 @@
       <c r="N37" t="n">
         <v>198</v>
       </c>
-      <c r="P37" t="n">
+      <c r="T37" t="n">
         <v>100</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="U37" t="n">
         <v>10</v>
       </c>
-      <c r="R37" t="n">
+      <c r="V37" t="n">
         <v>5</v>
       </c>
-      <c r="S37" t="n">
+      <c r="W37" t="n">
         <v>5</v>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="Z37" s="10" t="n"/>
-      <c r="AB37" t="inlineStr">
+      <c r="AD37" s="10" t="n"/>
+      <c r="AE37" s="10" t="n"/>
+      <c r="AG37" t="inlineStr">
         <is>
           <t>10 cm off the wall for ventilation</t>
         </is>
@@ -6348,16 +6522,17 @@
       <c r="N38" t="n">
         <v>230</v>
       </c>
-      <c r="P38" t="n">
+      <c r="T38" t="n">
         <v>70</v>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="Z38" s="10" t="n"/>
-      <c r="AB38" t="inlineStr">
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="10" t="n"/>
+      <c r="AG38" t="inlineStr">
         <is>
           <t>EXAMPLE PROBLEM: 230 cm tall, within 45 cm of a sprinklered ceiling</t>
         </is>
@@ -6403,10 +6578,11 @@
       <c r="N39" t="n">
         <v>40</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AC39" t="n">
         <v>80</v>
       </c>
-      <c r="Z39" s="10" t="n"/>
+      <c r="AD39" s="10" t="n"/>
+      <c r="AE39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6448,12 +6624,13 @@
       <c r="N40" t="n">
         <v>40</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AC40" t="n">
         <v>45</v>
       </c>
-      <c r="Z40" s="10" t="n">
+      <c r="AD40" s="10" t="n">
         <v>46286</v>
       </c>
+      <c r="AE40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6504,10 +6681,11 @@
       <c r="O41" t="n">
         <v>68</v>
       </c>
-      <c r="P41" t="n">
+      <c r="T41" t="n">
         <v>90</v>
       </c>
-      <c r="Z41" s="10" t="n"/>
+      <c r="AD41" s="10" t="n"/>
+      <c r="AE41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6555,7 +6733,8 @@
       <c r="N42" t="n">
         <v>45</v>
       </c>
-      <c r="Z42" s="10" t="n"/>
+      <c r="AD42" s="10" t="n"/>
+      <c r="AE42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6603,7 +6782,8 @@
       <c r="N43" t="n">
         <v>45</v>
       </c>
-      <c r="Z43" s="10" t="n"/>
+      <c r="AD43" s="10" t="n"/>
+      <c r="AE43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6651,8 +6831,9 @@
       <c r="N44" t="n">
         <v>65</v>
       </c>
-      <c r="Z44" s="10" t="n"/>
-      <c r="AB44" t="inlineStr">
+      <c r="AD44" s="10" t="n"/>
+      <c r="AE44" s="10" t="n"/>
+      <c r="AG44" t="inlineStr">
         <is>
           <t>keeps the space under the desk free for legs</t>
         </is>
@@ -6702,14 +6883,15 @@
       <c r="O45" t="n">
         <v>75</v>
       </c>
-      <c r="P45" t="n">
+      <c r="T45" t="n">
         <v>90</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="U45" t="n">
         <v>60</v>
       </c>
-      <c r="Z45" s="10" t="n"/>
-      <c r="AB45" t="inlineStr">
+      <c r="AD45" s="10" t="n"/>
+      <c r="AE45" s="10" t="n"/>
+      <c r="AG45" t="inlineStr">
         <is>
           <t>open frame: free_under 75</t>
         </is>
@@ -6761,8 +6943,9 @@
       <c r="N46" t="n">
         <v>50</v>
       </c>
-      <c r="Z46" s="10" t="n"/>
-      <c r="AA46" t="inlineStr">
+      <c r="AD46" s="10" t="n"/>
+      <c r="AE46" s="10" t="n"/>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>vibration-sensitive</t>
         </is>
@@ -6814,7 +6997,8 @@
       <c r="N47" t="n">
         <v>3</v>
       </c>
-      <c r="Z47" s="10" t="n"/>
+      <c r="AD47" s="10" t="n"/>
+      <c r="AE47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6862,13 +7046,14 @@
       <c r="N48" t="n">
         <v>9</v>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z48" s="10" t="n"/>
-      <c r="AB48" t="inlineStr">
+      <c r="AD48" s="10" t="n"/>
+      <c r="AE48" s="10" t="n"/>
+      <c r="AG48" t="inlineStr">
         <is>
           <t>bottom of a stack of three</t>
         </is>
@@ -6920,13 +7105,14 @@
       <c r="N49" t="n">
         <v>9</v>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z49" s="10" t="n"/>
-      <c r="AB49" t="inlineStr">
+      <c r="AD49" s="10" t="n"/>
+      <c r="AE49" s="10" t="n"/>
+      <c r="AG49" t="inlineStr">
         <is>
           <t>stacked on SMU-01</t>
         </is>
@@ -6978,8 +7164,9 @@
       <c r="N50" t="n">
         <v>9</v>
       </c>
-      <c r="Z50" s="10" t="n"/>
-      <c r="AB50" t="inlineStr">
+      <c r="AD50" s="10" t="n"/>
+      <c r="AE50" s="10" t="n"/>
+      <c r="AG50" t="inlineStr">
         <is>
           <t>top of the stack</t>
         </is>
@@ -7031,8 +7218,9 @@
       <c r="N51" t="n">
         <v>60</v>
       </c>
-      <c r="Z51" s="10" t="n"/>
-      <c r="AB51" t="inlineStr">
+      <c r="AD51" s="10" t="n"/>
+      <c r="AE51" s="10" t="n"/>
+      <c r="AG51" t="inlineStr">
         <is>
           <t>not a child of TBL-01, but fits under it</t>
         </is>
@@ -7079,13 +7267,14 @@
       <c r="N52" t="n">
         <v>90</v>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z52" s="10" t="n"/>
-      <c r="AB52" t="inlineStr">
+      <c r="AD52" s="10" t="n"/>
+      <c r="AE52" s="10" t="n"/>
+      <c r="AG52" t="inlineStr">
         <is>
           <t>position = parking spot</t>
         </is>
@@ -7132,13 +7321,14 @@
       <c r="N53" t="n">
         <v>90</v>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z53" s="10" t="n"/>
-      <c r="AB53" t="inlineStr">
+      <c r="AD53" s="10" t="n"/>
+      <c r="AE53" s="10" t="n"/>
+      <c r="AG53" t="inlineStr">
         <is>
           <t>EXAMPLE PROBLEM: parked in the eyewash clear zone</t>
         </is>
@@ -7190,8 +7380,9 @@
       <c r="N54" t="n">
         <v>150</v>
       </c>
-      <c r="Z54" s="10" t="n"/>
-      <c r="AB54" t="inlineStr">
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="10" t="n"/>
+      <c r="AG54" t="inlineStr">
         <is>
           <t>chain to the wall</t>
         </is>
@@ -7243,7 +7434,8 @@
       <c r="N55" t="n">
         <v>150</v>
       </c>
-      <c r="Z55" s="10" t="n"/>
+      <c r="AD55" s="10" t="n"/>
+      <c r="AE55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7280,11 +7472,12 @@
       <c r="N56" t="n">
         <v>90</v>
       </c>
-      <c r="P56" t="n">
+      <c r="T56" t="n">
         <v>70</v>
       </c>
-      <c r="Z56" s="10" t="n"/>
-      <c r="AB56" t="inlineStr">
+      <c r="AD56" s="10" t="n"/>
+      <c r="AE56" s="10" t="n"/>
+      <c r="AG56" t="inlineStr">
         <is>
           <t>no x/y yet: lands in the staging area, drag it into place</t>
         </is>
@@ -7336,16 +7529,17 @@
       <c r="N57" t="n">
         <v>210</v>
       </c>
-      <c r="P57" t="n">
+      <c r="T57" t="n">
         <v>100</v>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z57" s="10" t="n"/>
-      <c r="AB57" t="inlineStr">
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="10" t="n"/>
+      <c r="AG57" t="inlineStr">
         <is>
           <t>clear_front = door swing</t>
         </is>
@@ -7392,13 +7586,14 @@
       <c r="N58" t="n">
         <v>280</v>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z58" s="10" t="n"/>
-      <c r="AB58" t="inlineStr">
+      <c r="AD58" s="10" t="n"/>
+      <c r="AE58" s="10" t="n"/>
+      <c r="AG58" t="inlineStr">
         <is>
           <t>the island is notched around it</t>
         </is>
@@ -7445,13 +7640,14 @@
       <c r="N59" t="n">
         <v>280</v>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z59" s="10" t="n"/>
-      <c r="AB59" t="inlineStr">
+      <c r="AD59" s="10" t="n"/>
+      <c r="AE59" s="10" t="n"/>
+      <c r="AG59" t="inlineStr">
         <is>
           <t>splits the raised tier of BENCH-13</t>
         </is>
@@ -7503,8 +7699,9 @@
       <c r="N60" t="n">
         <v>90</v>
       </c>
-      <c r="Z60" s="10" t="n"/>
-      <c r="AB60" t="inlineStr">
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="10" t="n"/>
+      <c r="AG60" t="inlineStr">
         <is>
           <t>footprint + clearance come from shapes/corner-45.svg</t>
         </is>
@@ -7556,7 +7753,8 @@
       <c r="N61" t="n">
         <v>15</v>
       </c>
-      <c r="Z61" s="10" t="n"/>
+      <c r="AD61" s="10" t="n"/>
+      <c r="AE61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7602,10 +7800,11 @@
       <c r="O62" t="n">
         <v>75</v>
       </c>
-      <c r="P62" t="n">
+      <c r="T62" t="n">
         <v>90</v>
       </c>
-      <c r="Z62" s="10" t="n"/>
+      <c r="AD62" s="10" t="n"/>
+      <c r="AE62" s="10" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7653,7 +7852,8 @@
       <c r="N63" t="n">
         <v>45</v>
       </c>
-      <c r="Z63" s="10" t="n"/>
+      <c r="AD63" s="10" t="n"/>
+      <c r="AE63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7701,7 +7901,8 @@
       <c r="N64" t="n">
         <v>50</v>
       </c>
-      <c r="Z64" s="10" t="n"/>
+      <c r="AD64" s="10" t="n"/>
+      <c r="AE64" s="10" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7749,15 +7950,16 @@
       <c r="N65" t="n">
         <v>60</v>
       </c>
-      <c r="P65" t="n">
+      <c r="T65" t="n">
         <v>50</v>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z65" s="10" t="n"/>
+      <c r="AD65" s="10" t="n"/>
+      <c r="AE65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7799,12 +8001,13 @@
       <c r="N66" t="n">
         <v>8</v>
       </c>
-      <c r="Y66" t="n">
+      <c r="AC66" t="n">
         <v>70</v>
       </c>
-      <c r="Z66" s="10" t="n">
+      <c r="AD66" s="10" t="n">
         <v>46286</v>
       </c>
+      <c r="AE66" s="10" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7846,10 +8049,11 @@
       <c r="N67" t="n">
         <v>12</v>
       </c>
-      <c r="Y67" t="n">
+      <c r="AC67" t="n">
         <v>50</v>
       </c>
-      <c r="Z67" s="10" t="n"/>
+      <c r="AD67" s="10" t="n"/>
+      <c r="AE67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7891,10 +8095,11 @@
       <c r="N68" t="n">
         <v>25</v>
       </c>
-      <c r="Y68" t="n">
+      <c r="AC68" t="n">
         <v>35</v>
       </c>
-      <c r="Z68" s="10" t="n"/>
+      <c r="AD68" s="10" t="n"/>
+      <c r="AE68" s="10" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7937,15 +8142,16 @@
       <c r="N69" t="n">
         <v>200</v>
       </c>
-      <c r="P69" t="n">
+      <c r="T69" t="n">
         <v>70</v>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="Z69" s="10" t="n"/>
+      <c r="AD69" s="10" t="n"/>
+      <c r="AE69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7987,10 +8193,11 @@
       <c r="N70" t="n">
         <v>45</v>
       </c>
-      <c r="Y70" t="n">
+      <c r="AC70" t="n">
         <v>60</v>
       </c>
-      <c r="Z70" s="10" t="n"/>
+      <c r="AD70" s="10" t="n"/>
+      <c r="AE70" s="10" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8032,12 +8239,13 @@
       <c r="N71" t="n">
         <v>45</v>
       </c>
-      <c r="Y71" t="n">
+      <c r="AC71" t="n">
         <v>85</v>
       </c>
-      <c r="Z71" s="10" t="n">
+      <c r="AD71" s="10" t="n">
         <v>46286</v>
       </c>
+      <c r="AE71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8079,10 +8287,11 @@
       <c r="N72" t="n">
         <v>45</v>
       </c>
-      <c r="Y72" t="n">
+      <c r="AC72" t="n">
         <v>20</v>
       </c>
-      <c r="Z72" s="10" t="n"/>
+      <c r="AD72" s="10" t="n"/>
+      <c r="AE72" s="10" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8121,8 +8330,9 @@
           <t>group</t>
         </is>
       </c>
-      <c r="Z73" s="10" t="n"/>
-      <c r="AB73" t="inlineStr">
+      <c r="AD73" s="10" t="n"/>
+      <c r="AE73" s="10" t="n"/>
+      <c r="AG73" t="inlineStr">
         <is>
           <t>three parts: straight run, diagonal piece (.B faces SW), straight run</t>
         </is>
@@ -8177,10 +8387,11 @@
       <c r="O74" t="n">
         <v>75</v>
       </c>
-      <c r="P74" t="n">
+      <c r="T74" t="n">
         <v>90</v>
       </c>
-      <c r="Z74" s="10" t="n"/>
+      <c r="AD74" s="10" t="n"/>
+      <c r="AE74" s="10" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8236,11 +8447,12 @@
       <c r="O75" t="n">
         <v>75</v>
       </c>
-      <c r="P75" t="n">
+      <c r="T75" t="n">
         <v>90</v>
       </c>
-      <c r="Z75" s="10" t="n"/>
-      <c r="AB75" t="inlineStr">
+      <c r="AD75" s="10" t="n"/>
+      <c r="AE75" s="10" t="n"/>
+      <c r="AG75" t="inlineStr">
         <is>
           <t>w along its front edge; x/y = corner of its bounding box, easier to drag in</t>
         </is>
@@ -8300,10 +8512,11 @@
       <c r="O76" t="n">
         <v>75</v>
       </c>
-      <c r="P76" t="n">
+      <c r="T76" t="n">
         <v>90</v>
       </c>
-      <c r="Z76" s="10" t="n"/>
+      <c r="AD76" s="10" t="n"/>
+      <c r="AE76" s="10" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8351,7 +8564,8 @@
       <c r="N77" t="n">
         <v>90</v>
       </c>
-      <c r="Z77" s="10" t="n"/>
+      <c r="AD77" s="10" t="n"/>
+      <c r="AE77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8399,7 +8613,8 @@
       <c r="N78" t="n">
         <v>65</v>
       </c>
-      <c r="Z78" s="10" t="n"/>
+      <c r="AD78" s="10" t="n"/>
+      <c r="AE78" s="10" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8447,7 +8662,8 @@
       <c r="N79" t="n">
         <v>45</v>
       </c>
-      <c r="Z79" s="10" t="n"/>
+      <c r="AD79" s="10" t="n"/>
+      <c r="AE79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8495,7 +8711,8 @@
       <c r="N80" t="n">
         <v>40</v>
       </c>
-      <c r="Z80" s="10" t="n"/>
+      <c r="AD80" s="10" t="n"/>
+      <c r="AE80" s="10" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8543,7 +8760,8 @@
       <c r="N81" t="n">
         <v>45</v>
       </c>
-      <c r="Z81" s="10" t="n"/>
+      <c r="AD81" s="10" t="n"/>
+      <c r="AE81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8591,13 +8809,14 @@
       <c r="N82" t="n">
         <v>30</v>
       </c>
-      <c r="Z82" s="10" t="n"/>
-      <c r="AA82" t="inlineStr">
+      <c r="AD82" s="10" t="n"/>
+      <c r="AE82" s="10" t="n"/>
+      <c r="AF82" t="inlineStr">
         <is>
           <t>vibrates; noisy</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
+      <c r="AG82" t="inlineStr">
         <is>
           <t>noisy</t>
         </is>
@@ -8649,11 +8868,12 @@
       <c r="N83" t="n">
         <v>10</v>
       </c>
-      <c r="Y83" t="n">
+      <c r="AC83" t="n">
         <v>40</v>
       </c>
-      <c r="Z83" s="10" t="n"/>
-      <c r="AB83" t="inlineStr">
+      <c r="AD83" s="10" t="n"/>
+      <c r="AE83" s="10" t="n"/>
+      <c r="AG83" t="inlineStr">
         <is>
           <t>sits on the diagonal piece</t>
         </is>
@@ -8705,7 +8925,8 @@
       <c r="N84" t="n">
         <v>25</v>
       </c>
-      <c r="Z84" s="10" t="n"/>
+      <c r="AD84" s="10" t="n"/>
+      <c r="AE84" s="10" t="n"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8753,7 +8974,8 @@
       <c r="N85" t="n">
         <v>25</v>
       </c>
-      <c r="Z85" s="10" t="n"/>
+      <c r="AD85" s="10" t="n"/>
+      <c r="AE85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8801,7 +9023,8 @@
       <c r="N86" t="n">
         <v>50</v>
       </c>
-      <c r="Z86" s="10" t="n"/>
+      <c r="AD86" s="10" t="n"/>
+      <c r="AE86" s="10" t="n"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8849,7 +9072,8 @@
       <c r="N87" t="n">
         <v>60</v>
       </c>
-      <c r="Z87" s="10" t="n"/>
+      <c r="AD87" s="10" t="n"/>
+      <c r="AE87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8897,8 +9121,9 @@
       <c r="N88" t="n">
         <v>75</v>
       </c>
-      <c r="Z88" s="10" t="n"/>
-      <c r="AB88" t="inlineStr">
+      <c r="AD88" s="10" t="n"/>
+      <c r="AE88" s="10" t="n"/>
+      <c r="AG88" t="inlineStr">
         <is>
           <t>EXAMPLE PROBLEM: straddles the wall into the missing corner</t>
         </is>
@@ -8941,8 +9166,9 @@
           <t>group</t>
         </is>
       </c>
-      <c r="Z89" s="10" t="n"/>
-      <c r="AB89" t="inlineStr">
+      <c r="AD89" s="10" t="n"/>
+      <c r="AE89" s="10" t="n"/>
+      <c r="AG89" t="inlineStr">
         <is>
           <t>worktop in front, 30 cm deep raised tier behind it</t>
         </is>
@@ -9002,10 +9228,11 @@
       <c r="O90" t="n">
         <v>75</v>
       </c>
-      <c r="P90" t="n">
+      <c r="T90" t="n">
         <v>90</v>
       </c>
-      <c r="Z90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="10" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9058,8 +9285,9 @@
       <c r="N91" t="n">
         <v>120</v>
       </c>
-      <c r="Z91" s="10" t="n"/>
-      <c r="AB91" t="inlineStr">
+      <c r="AD91" s="10" t="n"/>
+      <c r="AE91" s="10" t="n"/>
+      <c r="AG91" t="inlineStr">
         <is>
           <t>solid to the floor</t>
         </is>
@@ -9116,8 +9344,9 @@
       <c r="N92" t="n">
         <v>120</v>
       </c>
-      <c r="Z92" s="10" t="n"/>
-      <c r="AB92" t="inlineStr">
+      <c r="AD92" s="10" t="n"/>
+      <c r="AE92" s="10" t="n"/>
+      <c r="AG92" t="inlineStr">
         <is>
           <t>solid to the floor</t>
         </is>
@@ -9169,10 +9398,11 @@
       <c r="N93" t="n">
         <v>50</v>
       </c>
-      <c r="P93" t="n">
+      <c r="T93" t="n">
         <v>30</v>
       </c>
-      <c r="Z93" s="10" t="n"/>
+      <c r="AD93" s="10" t="n"/>
+      <c r="AE93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9220,7 +9450,8 @@
       <c r="N94" t="n">
         <v>45</v>
       </c>
-      <c r="Z94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="10" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9268,7 +9499,8 @@
       <c r="N95" t="n">
         <v>30</v>
       </c>
-      <c r="Z95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9316,7 +9548,8 @@
       <c r="N96" t="n">
         <v>3</v>
       </c>
-      <c r="Z96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="10" t="n"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9364,7 +9597,8 @@
       <c r="N97" t="n">
         <v>45</v>
       </c>
-      <c r="Z97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9412,10 +9646,11 @@
       <c r="N98" t="n">
         <v>20</v>
       </c>
-      <c r="Y98" t="n">
+      <c r="AC98" t="n">
         <v>70</v>
       </c>
-      <c r="Z98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="10" t="n"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9463,10 +9698,11 @@
       <c r="N99" t="n">
         <v>15</v>
       </c>
-      <c r="Y99" t="n">
+      <c r="AC99" t="n">
         <v>55</v>
       </c>
-      <c r="Z99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9505,8 +9741,9 @@
           <t>group</t>
         </is>
       </c>
-      <c r="Z100" s="10" t="n"/>
-      <c r="AB100" t="inlineStr">
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="10" t="n"/>
+      <c r="AG100" t="inlineStr">
         <is>
           <t>three parts: the middle one is shallower where COL-02 cuts in</t>
         </is>
@@ -9561,10 +9798,11 @@
       <c r="O101" t="n">
         <v>75</v>
       </c>
-      <c r="P101" t="n">
+      <c r="T101" t="n">
         <v>90</v>
       </c>
-      <c r="Z101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9615,10 +9853,11 @@
       <c r="O102" t="n">
         <v>75</v>
       </c>
-      <c r="P102" t="n">
+      <c r="T102" t="n">
         <v>90</v>
       </c>
-      <c r="Z102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="10" t="n"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9669,10 +9908,11 @@
       <c r="O103" t="n">
         <v>75</v>
       </c>
-      <c r="P103" t="n">
+      <c r="T103" t="n">
         <v>90</v>
       </c>
-      <c r="Z103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="10" t="n"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9720,11 +9960,12 @@
       <c r="N104" t="n">
         <v>25</v>
       </c>
-      <c r="T104" t="n">
+      <c r="X104" t="n">
         <v>15</v>
       </c>
-      <c r="Z104" s="10" t="n"/>
-      <c r="AA104" t="inlineStr">
+      <c r="AD104" s="10" t="n"/>
+      <c r="AE104" s="10" t="n"/>
+      <c r="AF104" t="inlineStr">
         <is>
           <t>vibrates</t>
         </is>
@@ -9776,7 +10017,8 @@
       <c r="N105" t="n">
         <v>15</v>
       </c>
-      <c r="Z105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="10" t="n"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9824,11 +10066,12 @@
       <c r="N106" t="n">
         <v>35</v>
       </c>
-      <c r="P106" t="n">
+      <c r="T106" t="n">
         <v>30</v>
       </c>
-      <c r="Z106" s="10" t="n"/>
-      <c r="AA106" t="inlineStr">
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="10" t="n"/>
+      <c r="AF106" t="inlineStr">
         <is>
           <t>vibration-sensitive</t>
         </is>
@@ -9880,15 +10123,16 @@
       <c r="N107" t="n">
         <v>60</v>
       </c>
-      <c r="P107" t="n">
+      <c r="T107" t="n">
         <v>50</v>
       </c>
-      <c r="W107" t="inlineStr">
+      <c r="AA107" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z107" s="10" t="n"/>
+      <c r="AD107" s="10" t="n"/>
+      <c r="AE107" s="10" t="n"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9930,10 +10174,11 @@
       <c r="N108" t="n">
         <v>8</v>
       </c>
-      <c r="Y108" t="n">
+      <c r="AC108" t="n">
         <v>40</v>
       </c>
-      <c r="Z108" s="10" t="n"/>
+      <c r="AD108" s="10" t="n"/>
+      <c r="AE108" s="10" t="n"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9975,12 +10220,13 @@
       <c r="N109" t="n">
         <v>12</v>
       </c>
-      <c r="Y109" t="n">
+      <c r="AC109" t="n">
         <v>65</v>
       </c>
-      <c r="Z109" s="10" t="n">
+      <c r="AD109" s="10" t="n">
         <v>46286</v>
       </c>
+      <c r="AE109" s="10" t="n"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10022,10 +10268,11 @@
       <c r="N110" t="n">
         <v>25</v>
       </c>
-      <c r="Y110" t="n">
+      <c r="AC110" t="n">
         <v>50</v>
       </c>
-      <c r="Z110" s="10" t="n"/>
+      <c r="AD110" s="10" t="n"/>
+      <c r="AE110" s="10" t="n"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10073,8 +10320,9 @@
       <c r="N111" t="n">
         <v>150</v>
       </c>
-      <c r="Z111" s="10" t="n"/>
-      <c r="AB111" t="inlineStr">
+      <c r="AD111" s="10" t="n"/>
+      <c r="AE111" s="10" t="n"/>
+      <c r="AG111" t="inlineStr">
         <is>
           <t>chain to the wall</t>
         </is>
@@ -10126,8 +10374,9 @@
       <c r="N112" t="n">
         <v>150</v>
       </c>
-      <c r="Z112" s="10" t="n"/>
-      <c r="AB112" t="inlineStr">
+      <c r="AD112" s="10" t="n"/>
+      <c r="AE112" s="10" t="n"/>
+      <c r="AG112" t="inlineStr">
         <is>
           <t>chain to the wall</t>
         </is>
@@ -10182,10 +10431,11 @@
       <c r="O113" t="n">
         <v>68</v>
       </c>
-      <c r="P113" t="n">
+      <c r="T113" t="n">
         <v>90</v>
       </c>
-      <c r="Z113" s="10" t="n"/>
+      <c r="AD113" s="10" t="n"/>
+      <c r="AE113" s="10" t="n"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10233,7 +10483,8 @@
       <c r="N114" t="n">
         <v>65</v>
       </c>
-      <c r="Z114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="10" t="n"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10281,8 +10532,9 @@
       <c r="N115" t="n">
         <v>40</v>
       </c>
-      <c r="Z115" s="10" t="n"/>
-      <c r="AB115" t="inlineStr">
+      <c r="AD115" s="10" t="n"/>
+      <c r="AE115" s="10" t="n"/>
+      <c r="AG115" t="inlineStr">
         <is>
           <t>not a child of TBL-02, but fits under it</t>
         </is>
@@ -10323,11 +10575,12 @@
       <c r="N116" t="n">
         <v>190</v>
       </c>
-      <c r="P116" t="n">
+      <c r="T116" t="n">
         <v>90</v>
       </c>
-      <c r="Z116" s="10" t="n"/>
-      <c r="AB116" t="inlineStr">
+      <c r="AD116" s="10" t="n"/>
+      <c r="AE116" s="10" t="n"/>
+      <c r="AG116" t="inlineStr">
         <is>
           <t>EXAMPLE WARNING: 105 cm deep, too big for a 100 cm door even on its side</t>
         </is>
@@ -10377,4175 +10630,5602 @@
       <c r="N117" t="n">
         <v>30</v>
       </c>
-      <c r="V117" t="inlineStr">
+      <c r="Z117" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="Z117" s="10" t="n"/>
-      <c r="AB117" t="inlineStr">
+      <c r="AD117" s="10" t="n"/>
+      <c r="AE117" s="10" t="n"/>
+      <c r="AG117" t="inlineStr">
         <is>
           <t>overhead things are wall mounts with z = their underside</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="Z118" s="10" t="n"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>OVEN-01</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Drying oven</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>instrument</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LAB-A</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>floor</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>60</v>
+      </c>
+      <c r="M118" t="n">
+        <v>55</v>
+      </c>
+      <c r="N118" t="n">
+        <v>80</v>
+      </c>
+      <c r="AD118" s="10" t="n"/>
+      <c r="AE118" s="10" t="n">
+        <v>46203</v>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>EXAMPLE: decommissioned, kept as a record</t>
+        </is>
+      </c>
     </row>
     <row r="119">
-      <c r="Z119" s="10" t="n"/>
+      <c r="AD119" s="10" t="n"/>
+      <c r="AE119" s="10" t="n"/>
     </row>
     <row r="120">
-      <c r="Z120" s="10" t="n"/>
+      <c r="AD120" s="10" t="n"/>
+      <c r="AE120" s="10" t="n"/>
     </row>
     <row r="121">
-      <c r="Z121" s="10" t="n"/>
+      <c r="AD121" s="10" t="n"/>
+      <c r="AE121" s="10" t="n"/>
     </row>
     <row r="122">
-      <c r="Z122" s="10" t="n"/>
+      <c r="AD122" s="10" t="n"/>
+      <c r="AE122" s="10" t="n"/>
     </row>
     <row r="123">
-      <c r="Z123" s="10" t="n"/>
+      <c r="AD123" s="10" t="n"/>
+      <c r="AE123" s="10" t="n"/>
     </row>
     <row r="124">
-      <c r="Z124" s="10" t="n"/>
+      <c r="AD124" s="10" t="n"/>
+      <c r="AE124" s="10" t="n"/>
     </row>
     <row r="125">
-      <c r="Z125" s="10" t="n"/>
+      <c r="AD125" s="10" t="n"/>
+      <c r="AE125" s="10" t="n"/>
     </row>
     <row r="126">
-      <c r="Z126" s="10" t="n"/>
+      <c r="AD126" s="10" t="n"/>
+      <c r="AE126" s="10" t="n"/>
     </row>
     <row r="127">
-      <c r="Z127" s="10" t="n"/>
+      <c r="AD127" s="10" t="n"/>
+      <c r="AE127" s="10" t="n"/>
     </row>
     <row r="128">
-      <c r="Z128" s="10" t="n"/>
+      <c r="AD128" s="10" t="n"/>
+      <c r="AE128" s="10" t="n"/>
     </row>
     <row r="129">
-      <c r="Z129" s="10" t="n"/>
+      <c r="AD129" s="10" t="n"/>
+      <c r="AE129" s="10" t="n"/>
     </row>
     <row r="130">
-      <c r="Z130" s="10" t="n"/>
+      <c r="AD130" s="10" t="n"/>
+      <c r="AE130" s="10" t="n"/>
     </row>
     <row r="131">
-      <c r="Z131" s="10" t="n"/>
+      <c r="AD131" s="10" t="n"/>
+      <c r="AE131" s="10" t="n"/>
     </row>
     <row r="132">
-      <c r="Z132" s="10" t="n"/>
+      <c r="AD132" s="10" t="n"/>
+      <c r="AE132" s="10" t="n"/>
     </row>
     <row r="133">
-      <c r="Z133" s="10" t="n"/>
+      <c r="AD133" s="10" t="n"/>
+      <c r="AE133" s="10" t="n"/>
     </row>
     <row r="134">
-      <c r="Z134" s="10" t="n"/>
+      <c r="AD134" s="10" t="n"/>
+      <c r="AE134" s="10" t="n"/>
     </row>
     <row r="135">
-      <c r="Z135" s="10" t="n"/>
+      <c r="AD135" s="10" t="n"/>
+      <c r="AE135" s="10" t="n"/>
     </row>
     <row r="136">
-      <c r="Z136" s="10" t="n"/>
+      <c r="AD136" s="10" t="n"/>
+      <c r="AE136" s="10" t="n"/>
     </row>
     <row r="137">
-      <c r="Z137" s="10" t="n"/>
+      <c r="AD137" s="10" t="n"/>
+      <c r="AE137" s="10" t="n"/>
     </row>
     <row r="138">
-      <c r="Z138" s="10" t="n"/>
+      <c r="AD138" s="10" t="n"/>
+      <c r="AE138" s="10" t="n"/>
     </row>
     <row r="139">
-      <c r="Z139" s="10" t="n"/>
+      <c r="AD139" s="10" t="n"/>
+      <c r="AE139" s="10" t="n"/>
     </row>
     <row r="140">
-      <c r="Z140" s="10" t="n"/>
+      <c r="AD140" s="10" t="n"/>
+      <c r="AE140" s="10" t="n"/>
     </row>
     <row r="141">
-      <c r="Z141" s="10" t="n"/>
+      <c r="AD141" s="10" t="n"/>
+      <c r="AE141" s="10" t="n"/>
     </row>
     <row r="142">
-      <c r="Z142" s="10" t="n"/>
+      <c r="AD142" s="10" t="n"/>
+      <c r="AE142" s="10" t="n"/>
     </row>
     <row r="143">
-      <c r="Z143" s="10" t="n"/>
+      <c r="AD143" s="10" t="n"/>
+      <c r="AE143" s="10" t="n"/>
     </row>
     <row r="144">
-      <c r="Z144" s="10" t="n"/>
+      <c r="AD144" s="10" t="n"/>
+      <c r="AE144" s="10" t="n"/>
     </row>
     <row r="145">
-      <c r="Z145" s="10" t="n"/>
+      <c r="AD145" s="10" t="n"/>
+      <c r="AE145" s="10" t="n"/>
     </row>
     <row r="146">
-      <c r="Z146" s="10" t="n"/>
+      <c r="AD146" s="10" t="n"/>
+      <c r="AE146" s="10" t="n"/>
     </row>
     <row r="147">
-      <c r="Z147" s="10" t="n"/>
+      <c r="AD147" s="10" t="n"/>
+      <c r="AE147" s="10" t="n"/>
     </row>
     <row r="148">
-      <c r="Z148" s="10" t="n"/>
+      <c r="AD148" s="10" t="n"/>
+      <c r="AE148" s="10" t="n"/>
     </row>
     <row r="149">
-      <c r="Z149" s="10" t="n"/>
+      <c r="AD149" s="10" t="n"/>
+      <c r="AE149" s="10" t="n"/>
     </row>
     <row r="150">
-      <c r="Z150" s="10" t="n"/>
+      <c r="AD150" s="10" t="n"/>
+      <c r="AE150" s="10" t="n"/>
     </row>
     <row r="151">
-      <c r="Z151" s="10" t="n"/>
+      <c r="AD151" s="10" t="n"/>
+      <c r="AE151" s="10" t="n"/>
     </row>
     <row r="152">
-      <c r="Z152" s="10" t="n"/>
+      <c r="AD152" s="10" t="n"/>
+      <c r="AE152" s="10" t="n"/>
     </row>
     <row r="153">
-      <c r="Z153" s="10" t="n"/>
+      <c r="AD153" s="10" t="n"/>
+      <c r="AE153" s="10" t="n"/>
     </row>
     <row r="154">
-      <c r="Z154" s="10" t="n"/>
+      <c r="AD154" s="10" t="n"/>
+      <c r="AE154" s="10" t="n"/>
     </row>
     <row r="155">
-      <c r="Z155" s="10" t="n"/>
+      <c r="AD155" s="10" t="n"/>
+      <c r="AE155" s="10" t="n"/>
     </row>
     <row r="156">
-      <c r="Z156" s="10" t="n"/>
+      <c r="AD156" s="10" t="n"/>
+      <c r="AE156" s="10" t="n"/>
     </row>
     <row r="157">
-      <c r="Z157" s="10" t="n"/>
+      <c r="AD157" s="10" t="n"/>
+      <c r="AE157" s="10" t="n"/>
     </row>
     <row r="158">
-      <c r="Z158" s="10" t="n"/>
+      <c r="AD158" s="10" t="n"/>
+      <c r="AE158" s="10" t="n"/>
     </row>
     <row r="159">
-      <c r="Z159" s="10" t="n"/>
+      <c r="AD159" s="10" t="n"/>
+      <c r="AE159" s="10" t="n"/>
     </row>
     <row r="160">
-      <c r="Z160" s="10" t="n"/>
+      <c r="AD160" s="10" t="n"/>
+      <c r="AE160" s="10" t="n"/>
     </row>
     <row r="161">
-      <c r="Z161" s="10" t="n"/>
+      <c r="AD161" s="10" t="n"/>
+      <c r="AE161" s="10" t="n"/>
     </row>
     <row r="162">
-      <c r="Z162" s="10" t="n"/>
+      <c r="AD162" s="10" t="n"/>
+      <c r="AE162" s="10" t="n"/>
     </row>
     <row r="163">
-      <c r="Z163" s="10" t="n"/>
+      <c r="AD163" s="10" t="n"/>
+      <c r="AE163" s="10" t="n"/>
     </row>
     <row r="164">
-      <c r="Z164" s="10" t="n"/>
+      <c r="AD164" s="10" t="n"/>
+      <c r="AE164" s="10" t="n"/>
     </row>
     <row r="165">
-      <c r="Z165" s="10" t="n"/>
+      <c r="AD165" s="10" t="n"/>
+      <c r="AE165" s="10" t="n"/>
     </row>
     <row r="166">
-      <c r="Z166" s="10" t="n"/>
+      <c r="AD166" s="10" t="n"/>
+      <c r="AE166" s="10" t="n"/>
     </row>
     <row r="167">
-      <c r="Z167" s="10" t="n"/>
+      <c r="AD167" s="10" t="n"/>
+      <c r="AE167" s="10" t="n"/>
     </row>
     <row r="168">
-      <c r="Z168" s="10" t="n"/>
+      <c r="AD168" s="10" t="n"/>
+      <c r="AE168" s="10" t="n"/>
     </row>
     <row r="169">
-      <c r="Z169" s="10" t="n"/>
+      <c r="AD169" s="10" t="n"/>
+      <c r="AE169" s="10" t="n"/>
     </row>
     <row r="170">
-      <c r="Z170" s="10" t="n"/>
+      <c r="AD170" s="10" t="n"/>
+      <c r="AE170" s="10" t="n"/>
     </row>
     <row r="171">
-      <c r="Z171" s="10" t="n"/>
+      <c r="AD171" s="10" t="n"/>
+      <c r="AE171" s="10" t="n"/>
     </row>
     <row r="172">
-      <c r="Z172" s="10" t="n"/>
+      <c r="AD172" s="10" t="n"/>
+      <c r="AE172" s="10" t="n"/>
     </row>
     <row r="173">
-      <c r="Z173" s="10" t="n"/>
+      <c r="AD173" s="10" t="n"/>
+      <c r="AE173" s="10" t="n"/>
     </row>
     <row r="174">
-      <c r="Z174" s="10" t="n"/>
+      <c r="AD174" s="10" t="n"/>
+      <c r="AE174" s="10" t="n"/>
     </row>
     <row r="175">
-      <c r="Z175" s="10" t="n"/>
+      <c r="AD175" s="10" t="n"/>
+      <c r="AE175" s="10" t="n"/>
     </row>
     <row r="176">
-      <c r="Z176" s="10" t="n"/>
+      <c r="AD176" s="10" t="n"/>
+      <c r="AE176" s="10" t="n"/>
     </row>
     <row r="177">
-      <c r="Z177" s="10" t="n"/>
+      <c r="AD177" s="10" t="n"/>
+      <c r="AE177" s="10" t="n"/>
     </row>
     <row r="178">
-      <c r="Z178" s="10" t="n"/>
+      <c r="AD178" s="10" t="n"/>
+      <c r="AE178" s="10" t="n"/>
     </row>
     <row r="179">
-      <c r="Z179" s="10" t="n"/>
+      <c r="AD179" s="10" t="n"/>
+      <c r="AE179" s="10" t="n"/>
     </row>
     <row r="180">
-      <c r="Z180" s="10" t="n"/>
+      <c r="AD180" s="10" t="n"/>
+      <c r="AE180" s="10" t="n"/>
     </row>
     <row r="181">
-      <c r="Z181" s="10" t="n"/>
+      <c r="AD181" s="10" t="n"/>
+      <c r="AE181" s="10" t="n"/>
     </row>
     <row r="182">
-      <c r="Z182" s="10" t="n"/>
+      <c r="AD182" s="10" t="n"/>
+      <c r="AE182" s="10" t="n"/>
     </row>
     <row r="183">
-      <c r="Z183" s="10" t="n"/>
+      <c r="AD183" s="10" t="n"/>
+      <c r="AE183" s="10" t="n"/>
     </row>
     <row r="184">
-      <c r="Z184" s="10" t="n"/>
+      <c r="AD184" s="10" t="n"/>
+      <c r="AE184" s="10" t="n"/>
     </row>
     <row r="185">
-      <c r="Z185" s="10" t="n"/>
+      <c r="AD185" s="10" t="n"/>
+      <c r="AE185" s="10" t="n"/>
     </row>
     <row r="186">
-      <c r="Z186" s="10" t="n"/>
+      <c r="AD186" s="10" t="n"/>
+      <c r="AE186" s="10" t="n"/>
     </row>
     <row r="187">
-      <c r="Z187" s="10" t="n"/>
+      <c r="AD187" s="10" t="n"/>
+      <c r="AE187" s="10" t="n"/>
     </row>
     <row r="188">
-      <c r="Z188" s="10" t="n"/>
+      <c r="AD188" s="10" t="n"/>
+      <c r="AE188" s="10" t="n"/>
     </row>
     <row r="189">
-      <c r="Z189" s="10" t="n"/>
+      <c r="AD189" s="10" t="n"/>
+      <c r="AE189" s="10" t="n"/>
     </row>
     <row r="190">
-      <c r="Z190" s="10" t="n"/>
+      <c r="AD190" s="10" t="n"/>
+      <c r="AE190" s="10" t="n"/>
     </row>
     <row r="191">
-      <c r="Z191" s="10" t="n"/>
+      <c r="AD191" s="10" t="n"/>
+      <c r="AE191" s="10" t="n"/>
     </row>
     <row r="192">
-      <c r="Z192" s="10" t="n"/>
+      <c r="AD192" s="10" t="n"/>
+      <c r="AE192" s="10" t="n"/>
     </row>
     <row r="193">
-      <c r="Z193" s="10" t="n"/>
+      <c r="AD193" s="10" t="n"/>
+      <c r="AE193" s="10" t="n"/>
     </row>
     <row r="194">
-      <c r="Z194" s="10" t="n"/>
+      <c r="AD194" s="10" t="n"/>
+      <c r="AE194" s="10" t="n"/>
     </row>
     <row r="195">
-      <c r="Z195" s="10" t="n"/>
+      <c r="AD195" s="10" t="n"/>
+      <c r="AE195" s="10" t="n"/>
     </row>
     <row r="196">
-      <c r="Z196" s="10" t="n"/>
+      <c r="AD196" s="10" t="n"/>
+      <c r="AE196" s="10" t="n"/>
     </row>
     <row r="197">
-      <c r="Z197" s="10" t="n"/>
+      <c r="AD197" s="10" t="n"/>
+      <c r="AE197" s="10" t="n"/>
     </row>
     <row r="198">
-      <c r="Z198" s="10" t="n"/>
+      <c r="AD198" s="10" t="n"/>
+      <c r="AE198" s="10" t="n"/>
     </row>
     <row r="199">
-      <c r="Z199" s="10" t="n"/>
+      <c r="AD199" s="10" t="n"/>
+      <c r="AE199" s="10" t="n"/>
     </row>
     <row r="200">
-      <c r="Z200" s="10" t="n"/>
+      <c r="AD200" s="10" t="n"/>
+      <c r="AE200" s="10" t="n"/>
     </row>
     <row r="201">
-      <c r="Z201" s="10" t="n"/>
+      <c r="AD201" s="10" t="n"/>
+      <c r="AE201" s="10" t="n"/>
     </row>
     <row r="202">
-      <c r="Z202" s="10" t="n"/>
+      <c r="AD202" s="10" t="n"/>
+      <c r="AE202" s="10" t="n"/>
     </row>
     <row r="203">
-      <c r="Z203" s="10" t="n"/>
+      <c r="AD203" s="10" t="n"/>
+      <c r="AE203" s="10" t="n"/>
     </row>
     <row r="204">
-      <c r="Z204" s="10" t="n"/>
+      <c r="AD204" s="10" t="n"/>
+      <c r="AE204" s="10" t="n"/>
     </row>
     <row r="205">
-      <c r="Z205" s="10" t="n"/>
+      <c r="AD205" s="10" t="n"/>
+      <c r="AE205" s="10" t="n"/>
     </row>
     <row r="206">
-      <c r="Z206" s="10" t="n"/>
+      <c r="AD206" s="10" t="n"/>
+      <c r="AE206" s="10" t="n"/>
     </row>
     <row r="207">
-      <c r="Z207" s="10" t="n"/>
+      <c r="AD207" s="10" t="n"/>
+      <c r="AE207" s="10" t="n"/>
     </row>
     <row r="208">
-      <c r="Z208" s="10" t="n"/>
+      <c r="AD208" s="10" t="n"/>
+      <c r="AE208" s="10" t="n"/>
     </row>
     <row r="209">
-      <c r="Z209" s="10" t="n"/>
+      <c r="AD209" s="10" t="n"/>
+      <c r="AE209" s="10" t="n"/>
     </row>
     <row r="210">
-      <c r="Z210" s="10" t="n"/>
+      <c r="AD210" s="10" t="n"/>
+      <c r="AE210" s="10" t="n"/>
     </row>
     <row r="211">
-      <c r="Z211" s="10" t="n"/>
+      <c r="AD211" s="10" t="n"/>
+      <c r="AE211" s="10" t="n"/>
     </row>
     <row r="212">
-      <c r="Z212" s="10" t="n"/>
+      <c r="AD212" s="10" t="n"/>
+      <c r="AE212" s="10" t="n"/>
     </row>
     <row r="213">
-      <c r="Z213" s="10" t="n"/>
+      <c r="AD213" s="10" t="n"/>
+      <c r="AE213" s="10" t="n"/>
     </row>
     <row r="214">
-      <c r="Z214" s="10" t="n"/>
+      <c r="AD214" s="10" t="n"/>
+      <c r="AE214" s="10" t="n"/>
     </row>
     <row r="215">
-      <c r="Z215" s="10" t="n"/>
+      <c r="AD215" s="10" t="n"/>
+      <c r="AE215" s="10" t="n"/>
     </row>
     <row r="216">
-      <c r="Z216" s="10" t="n"/>
+      <c r="AD216" s="10" t="n"/>
+      <c r="AE216" s="10" t="n"/>
     </row>
     <row r="217">
-      <c r="Z217" s="10" t="n"/>
+      <c r="AD217" s="10" t="n"/>
+      <c r="AE217" s="10" t="n"/>
     </row>
     <row r="218">
-      <c r="Z218" s="10" t="n"/>
+      <c r="AD218" s="10" t="n"/>
+      <c r="AE218" s="10" t="n"/>
     </row>
     <row r="219">
-      <c r="Z219" s="10" t="n"/>
+      <c r="AD219" s="10" t="n"/>
+      <c r="AE219" s="10" t="n"/>
     </row>
     <row r="220">
-      <c r="Z220" s="10" t="n"/>
+      <c r="AD220" s="10" t="n"/>
+      <c r="AE220" s="10" t="n"/>
     </row>
     <row r="221">
-      <c r="Z221" s="10" t="n"/>
+      <c r="AD221" s="10" t="n"/>
+      <c r="AE221" s="10" t="n"/>
     </row>
     <row r="222">
-      <c r="Z222" s="10" t="n"/>
+      <c r="AD222" s="10" t="n"/>
+      <c r="AE222" s="10" t="n"/>
     </row>
     <row r="223">
-      <c r="Z223" s="10" t="n"/>
+      <c r="AD223" s="10" t="n"/>
+      <c r="AE223" s="10" t="n"/>
     </row>
     <row r="224">
-      <c r="Z224" s="10" t="n"/>
+      <c r="AD224" s="10" t="n"/>
+      <c r="AE224" s="10" t="n"/>
     </row>
     <row r="225">
-      <c r="Z225" s="10" t="n"/>
+      <c r="AD225" s="10" t="n"/>
+      <c r="AE225" s="10" t="n"/>
     </row>
     <row r="226">
-      <c r="Z226" s="10" t="n"/>
+      <c r="AD226" s="10" t="n"/>
+      <c r="AE226" s="10" t="n"/>
     </row>
     <row r="227">
-      <c r="Z227" s="10" t="n"/>
+      <c r="AD227" s="10" t="n"/>
+      <c r="AE227" s="10" t="n"/>
     </row>
     <row r="228">
-      <c r="Z228" s="10" t="n"/>
+      <c r="AD228" s="10" t="n"/>
+      <c r="AE228" s="10" t="n"/>
     </row>
     <row r="229">
-      <c r="Z229" s="10" t="n"/>
+      <c r="AD229" s="10" t="n"/>
+      <c r="AE229" s="10" t="n"/>
     </row>
     <row r="230">
-      <c r="Z230" s="10" t="n"/>
+      <c r="AD230" s="10" t="n"/>
+      <c r="AE230" s="10" t="n"/>
     </row>
     <row r="231">
-      <c r="Z231" s="10" t="n"/>
+      <c r="AD231" s="10" t="n"/>
+      <c r="AE231" s="10" t="n"/>
     </row>
     <row r="232">
-      <c r="Z232" s="10" t="n"/>
+      <c r="AD232" s="10" t="n"/>
+      <c r="AE232" s="10" t="n"/>
     </row>
     <row r="233">
-      <c r="Z233" s="10" t="n"/>
+      <c r="AD233" s="10" t="n"/>
+      <c r="AE233" s="10" t="n"/>
     </row>
     <row r="234">
-      <c r="Z234" s="10" t="n"/>
+      <c r="AD234" s="10" t="n"/>
+      <c r="AE234" s="10" t="n"/>
     </row>
     <row r="235">
-      <c r="Z235" s="10" t="n"/>
+      <c r="AD235" s="10" t="n"/>
+      <c r="AE235" s="10" t="n"/>
     </row>
     <row r="236">
-      <c r="Z236" s="10" t="n"/>
+      <c r="AD236" s="10" t="n"/>
+      <c r="AE236" s="10" t="n"/>
     </row>
     <row r="237">
-      <c r="Z237" s="10" t="n"/>
+      <c r="AD237" s="10" t="n"/>
+      <c r="AE237" s="10" t="n"/>
     </row>
     <row r="238">
-      <c r="Z238" s="10" t="n"/>
+      <c r="AD238" s="10" t="n"/>
+      <c r="AE238" s="10" t="n"/>
     </row>
     <row r="239">
-      <c r="Z239" s="10" t="n"/>
+      <c r="AD239" s="10" t="n"/>
+      <c r="AE239" s="10" t="n"/>
     </row>
     <row r="240">
-      <c r="Z240" s="10" t="n"/>
+      <c r="AD240" s="10" t="n"/>
+      <c r="AE240" s="10" t="n"/>
     </row>
     <row r="241">
-      <c r="Z241" s="10" t="n"/>
+      <c r="AD241" s="10" t="n"/>
+      <c r="AE241" s="10" t="n"/>
     </row>
     <row r="242">
-      <c r="Z242" s="10" t="n"/>
+      <c r="AD242" s="10" t="n"/>
+      <c r="AE242" s="10" t="n"/>
     </row>
     <row r="243">
-      <c r="Z243" s="10" t="n"/>
+      <c r="AD243" s="10" t="n"/>
+      <c r="AE243" s="10" t="n"/>
     </row>
     <row r="244">
-      <c r="Z244" s="10" t="n"/>
+      <c r="AD244" s="10" t="n"/>
+      <c r="AE244" s="10" t="n"/>
     </row>
     <row r="245">
-      <c r="Z245" s="10" t="n"/>
+      <c r="AD245" s="10" t="n"/>
+      <c r="AE245" s="10" t="n"/>
     </row>
     <row r="246">
-      <c r="Z246" s="10" t="n"/>
+      <c r="AD246" s="10" t="n"/>
+      <c r="AE246" s="10" t="n"/>
     </row>
     <row r="247">
-      <c r="Z247" s="10" t="n"/>
+      <c r="AD247" s="10" t="n"/>
+      <c r="AE247" s="10" t="n"/>
     </row>
     <row r="248">
-      <c r="Z248" s="10" t="n"/>
+      <c r="AD248" s="10" t="n"/>
+      <c r="AE248" s="10" t="n"/>
     </row>
     <row r="249">
-      <c r="Z249" s="10" t="n"/>
+      <c r="AD249" s="10" t="n"/>
+      <c r="AE249" s="10" t="n"/>
     </row>
     <row r="250">
-      <c r="Z250" s="10" t="n"/>
+      <c r="AD250" s="10" t="n"/>
+      <c r="AE250" s="10" t="n"/>
     </row>
     <row r="251">
-      <c r="Z251" s="10" t="n"/>
+      <c r="AD251" s="10" t="n"/>
+      <c r="AE251" s="10" t="n"/>
     </row>
     <row r="252">
-      <c r="Z252" s="10" t="n"/>
+      <c r="AD252" s="10" t="n"/>
+      <c r="AE252" s="10" t="n"/>
     </row>
     <row r="253">
-      <c r="Z253" s="10" t="n"/>
+      <c r="AD253" s="10" t="n"/>
+      <c r="AE253" s="10" t="n"/>
     </row>
     <row r="254">
-      <c r="Z254" s="10" t="n"/>
+      <c r="AD254" s="10" t="n"/>
+      <c r="AE254" s="10" t="n"/>
     </row>
     <row r="255">
-      <c r="Z255" s="10" t="n"/>
+      <c r="AD255" s="10" t="n"/>
+      <c r="AE255" s="10" t="n"/>
     </row>
     <row r="256">
-      <c r="Z256" s="10" t="n"/>
+      <c r="AD256" s="10" t="n"/>
+      <c r="AE256" s="10" t="n"/>
     </row>
     <row r="257">
-      <c r="Z257" s="10" t="n"/>
+      <c r="AD257" s="10" t="n"/>
+      <c r="AE257" s="10" t="n"/>
     </row>
     <row r="258">
-      <c r="Z258" s="10" t="n"/>
+      <c r="AD258" s="10" t="n"/>
+      <c r="AE258" s="10" t="n"/>
     </row>
     <row r="259">
-      <c r="Z259" s="10" t="n"/>
+      <c r="AD259" s="10" t="n"/>
+      <c r="AE259" s="10" t="n"/>
     </row>
     <row r="260">
-      <c r="Z260" s="10" t="n"/>
+      <c r="AD260" s="10" t="n"/>
+      <c r="AE260" s="10" t="n"/>
     </row>
     <row r="261">
-      <c r="Z261" s="10" t="n"/>
+      <c r="AD261" s="10" t="n"/>
+      <c r="AE261" s="10" t="n"/>
     </row>
     <row r="262">
-      <c r="Z262" s="10" t="n"/>
+      <c r="AD262" s="10" t="n"/>
+      <c r="AE262" s="10" t="n"/>
     </row>
     <row r="263">
-      <c r="Z263" s="10" t="n"/>
+      <c r="AD263" s="10" t="n"/>
+      <c r="AE263" s="10" t="n"/>
     </row>
     <row r="264">
-      <c r="Z264" s="10" t="n"/>
+      <c r="AD264" s="10" t="n"/>
+      <c r="AE264" s="10" t="n"/>
     </row>
     <row r="265">
-      <c r="Z265" s="10" t="n"/>
+      <c r="AD265" s="10" t="n"/>
+      <c r="AE265" s="10" t="n"/>
     </row>
     <row r="266">
-      <c r="Z266" s="10" t="n"/>
+      <c r="AD266" s="10" t="n"/>
+      <c r="AE266" s="10" t="n"/>
     </row>
     <row r="267">
-      <c r="Z267" s="10" t="n"/>
+      <c r="AD267" s="10" t="n"/>
+      <c r="AE267" s="10" t="n"/>
     </row>
     <row r="268">
-      <c r="Z268" s="10" t="n"/>
+      <c r="AD268" s="10" t="n"/>
+      <c r="AE268" s="10" t="n"/>
     </row>
     <row r="269">
-      <c r="Z269" s="10" t="n"/>
+      <c r="AD269" s="10" t="n"/>
+      <c r="AE269" s="10" t="n"/>
     </row>
     <row r="270">
-      <c r="Z270" s="10" t="n"/>
+      <c r="AD270" s="10" t="n"/>
+      <c r="AE270" s="10" t="n"/>
     </row>
     <row r="271">
-      <c r="Z271" s="10" t="n"/>
+      <c r="AD271" s="10" t="n"/>
+      <c r="AE271" s="10" t="n"/>
     </row>
     <row r="272">
-      <c r="Z272" s="10" t="n"/>
+      <c r="AD272" s="10" t="n"/>
+      <c r="AE272" s="10" t="n"/>
     </row>
     <row r="273">
-      <c r="Z273" s="10" t="n"/>
+      <c r="AD273" s="10" t="n"/>
+      <c r="AE273" s="10" t="n"/>
     </row>
     <row r="274">
-      <c r="Z274" s="10" t="n"/>
+      <c r="AD274" s="10" t="n"/>
+      <c r="AE274" s="10" t="n"/>
     </row>
     <row r="275">
-      <c r="Z275" s="10" t="n"/>
+      <c r="AD275" s="10" t="n"/>
+      <c r="AE275" s="10" t="n"/>
     </row>
     <row r="276">
-      <c r="Z276" s="10" t="n"/>
+      <c r="AD276" s="10" t="n"/>
+      <c r="AE276" s="10" t="n"/>
     </row>
     <row r="277">
-      <c r="Z277" s="10" t="n"/>
+      <c r="AD277" s="10" t="n"/>
+      <c r="AE277" s="10" t="n"/>
     </row>
     <row r="278">
-      <c r="Z278" s="10" t="n"/>
+      <c r="AD278" s="10" t="n"/>
+      <c r="AE278" s="10" t="n"/>
     </row>
     <row r="279">
-      <c r="Z279" s="10" t="n"/>
+      <c r="AD279" s="10" t="n"/>
+      <c r="AE279" s="10" t="n"/>
     </row>
     <row r="280">
-      <c r="Z280" s="10" t="n"/>
+      <c r="AD280" s="10" t="n"/>
+      <c r="AE280" s="10" t="n"/>
     </row>
     <row r="281">
-      <c r="Z281" s="10" t="n"/>
+      <c r="AD281" s="10" t="n"/>
+      <c r="AE281" s="10" t="n"/>
     </row>
     <row r="282">
-      <c r="Z282" s="10" t="n"/>
+      <c r="AD282" s="10" t="n"/>
+      <c r="AE282" s="10" t="n"/>
     </row>
     <row r="283">
-      <c r="Z283" s="10" t="n"/>
+      <c r="AD283" s="10" t="n"/>
+      <c r="AE283" s="10" t="n"/>
     </row>
     <row r="284">
-      <c r="Z284" s="10" t="n"/>
+      <c r="AD284" s="10" t="n"/>
+      <c r="AE284" s="10" t="n"/>
     </row>
     <row r="285">
-      <c r="Z285" s="10" t="n"/>
+      <c r="AD285" s="10" t="n"/>
+      <c r="AE285" s="10" t="n"/>
     </row>
     <row r="286">
-      <c r="Z286" s="10" t="n"/>
+      <c r="AD286" s="10" t="n"/>
+      <c r="AE286" s="10" t="n"/>
     </row>
     <row r="287">
-      <c r="Z287" s="10" t="n"/>
+      <c r="AD287" s="10" t="n"/>
+      <c r="AE287" s="10" t="n"/>
     </row>
     <row r="288">
-      <c r="Z288" s="10" t="n"/>
+      <c r="AD288" s="10" t="n"/>
+      <c r="AE288" s="10" t="n"/>
     </row>
     <row r="289">
-      <c r="Z289" s="10" t="n"/>
+      <c r="AD289" s="10" t="n"/>
+      <c r="AE289" s="10" t="n"/>
     </row>
     <row r="290">
-      <c r="Z290" s="10" t="n"/>
+      <c r="AD290" s="10" t="n"/>
+      <c r="AE290" s="10" t="n"/>
     </row>
     <row r="291">
-      <c r="Z291" s="10" t="n"/>
+      <c r="AD291" s="10" t="n"/>
+      <c r="AE291" s="10" t="n"/>
     </row>
     <row r="292">
-      <c r="Z292" s="10" t="n"/>
+      <c r="AD292" s="10" t="n"/>
+      <c r="AE292" s="10" t="n"/>
     </row>
     <row r="293">
-      <c r="Z293" s="10" t="n"/>
+      <c r="AD293" s="10" t="n"/>
+      <c r="AE293" s="10" t="n"/>
     </row>
     <row r="294">
-      <c r="Z294" s="10" t="n"/>
+      <c r="AD294" s="10" t="n"/>
+      <c r="AE294" s="10" t="n"/>
     </row>
     <row r="295">
-      <c r="Z295" s="10" t="n"/>
+      <c r="AD295" s="10" t="n"/>
+      <c r="AE295" s="10" t="n"/>
     </row>
     <row r="296">
-      <c r="Z296" s="10" t="n"/>
+      <c r="AD296" s="10" t="n"/>
+      <c r="AE296" s="10" t="n"/>
     </row>
     <row r="297">
-      <c r="Z297" s="10" t="n"/>
+      <c r="AD297" s="10" t="n"/>
+      <c r="AE297" s="10" t="n"/>
     </row>
     <row r="298">
-      <c r="Z298" s="10" t="n"/>
+      <c r="AD298" s="10" t="n"/>
+      <c r="AE298" s="10" t="n"/>
     </row>
     <row r="299">
-      <c r="Z299" s="10" t="n"/>
+      <c r="AD299" s="10" t="n"/>
+      <c r="AE299" s="10" t="n"/>
     </row>
     <row r="300">
-      <c r="Z300" s="10" t="n"/>
+      <c r="AD300" s="10" t="n"/>
+      <c r="AE300" s="10" t="n"/>
     </row>
     <row r="301">
-      <c r="Z301" s="10" t="n"/>
+      <c r="AD301" s="10" t="n"/>
+      <c r="AE301" s="10" t="n"/>
     </row>
     <row r="302">
-      <c r="Z302" s="10" t="n"/>
+      <c r="AD302" s="10" t="n"/>
+      <c r="AE302" s="10" t="n"/>
     </row>
     <row r="303">
-      <c r="Z303" s="10" t="n"/>
+      <c r="AD303" s="10" t="n"/>
+      <c r="AE303" s="10" t="n"/>
     </row>
     <row r="304">
-      <c r="Z304" s="10" t="n"/>
+      <c r="AD304" s="10" t="n"/>
+      <c r="AE304" s="10" t="n"/>
     </row>
     <row r="305">
-      <c r="Z305" s="10" t="n"/>
+      <c r="AD305" s="10" t="n"/>
+      <c r="AE305" s="10" t="n"/>
     </row>
     <row r="306">
-      <c r="Z306" s="10" t="n"/>
+      <c r="AD306" s="10" t="n"/>
+      <c r="AE306" s="10" t="n"/>
     </row>
     <row r="307">
-      <c r="Z307" s="10" t="n"/>
+      <c r="AD307" s="10" t="n"/>
+      <c r="AE307" s="10" t="n"/>
     </row>
     <row r="308">
-      <c r="Z308" s="10" t="n"/>
+      <c r="AD308" s="10" t="n"/>
+      <c r="AE308" s="10" t="n"/>
     </row>
     <row r="309">
-      <c r="Z309" s="10" t="n"/>
+      <c r="AD309" s="10" t="n"/>
+      <c r="AE309" s="10" t="n"/>
     </row>
     <row r="310">
-      <c r="Z310" s="10" t="n"/>
+      <c r="AD310" s="10" t="n"/>
+      <c r="AE310" s="10" t="n"/>
     </row>
     <row r="311">
-      <c r="Z311" s="10" t="n"/>
+      <c r="AD311" s="10" t="n"/>
+      <c r="AE311" s="10" t="n"/>
     </row>
     <row r="312">
-      <c r="Z312" s="10" t="n"/>
+      <c r="AD312" s="10" t="n"/>
+      <c r="AE312" s="10" t="n"/>
     </row>
     <row r="313">
-      <c r="Z313" s="10" t="n"/>
+      <c r="AD313" s="10" t="n"/>
+      <c r="AE313" s="10" t="n"/>
     </row>
     <row r="314">
-      <c r="Z314" s="10" t="n"/>
+      <c r="AD314" s="10" t="n"/>
+      <c r="AE314" s="10" t="n"/>
     </row>
     <row r="315">
-      <c r="Z315" s="10" t="n"/>
+      <c r="AD315" s="10" t="n"/>
+      <c r="AE315" s="10" t="n"/>
     </row>
     <row r="316">
-      <c r="Z316" s="10" t="n"/>
+      <c r="AD316" s="10" t="n"/>
+      <c r="AE316" s="10" t="n"/>
     </row>
     <row r="317">
-      <c r="Z317" s="10" t="n"/>
+      <c r="AD317" s="10" t="n"/>
+      <c r="AE317" s="10" t="n"/>
     </row>
     <row r="318">
-      <c r="Z318" s="10" t="n"/>
+      <c r="AD318" s="10" t="n"/>
+      <c r="AE318" s="10" t="n"/>
     </row>
     <row r="319">
-      <c r="Z319" s="10" t="n"/>
+      <c r="AD319" s="10" t="n"/>
+      <c r="AE319" s="10" t="n"/>
     </row>
     <row r="320">
-      <c r="Z320" s="10" t="n"/>
+      <c r="AD320" s="10" t="n"/>
+      <c r="AE320" s="10" t="n"/>
     </row>
     <row r="321">
-      <c r="Z321" s="10" t="n"/>
+      <c r="AD321" s="10" t="n"/>
+      <c r="AE321" s="10" t="n"/>
     </row>
     <row r="322">
-      <c r="Z322" s="10" t="n"/>
+      <c r="AD322" s="10" t="n"/>
+      <c r="AE322" s="10" t="n"/>
     </row>
     <row r="323">
-      <c r="Z323" s="10" t="n"/>
+      <c r="AD323" s="10" t="n"/>
+      <c r="AE323" s="10" t="n"/>
     </row>
     <row r="324">
-      <c r="Z324" s="10" t="n"/>
+      <c r="AD324" s="10" t="n"/>
+      <c r="AE324" s="10" t="n"/>
     </row>
     <row r="325">
-      <c r="Z325" s="10" t="n"/>
+      <c r="AD325" s="10" t="n"/>
+      <c r="AE325" s="10" t="n"/>
     </row>
     <row r="326">
-      <c r="Z326" s="10" t="n"/>
+      <c r="AD326" s="10" t="n"/>
+      <c r="AE326" s="10" t="n"/>
     </row>
     <row r="327">
-      <c r="Z327" s="10" t="n"/>
+      <c r="AD327" s="10" t="n"/>
+      <c r="AE327" s="10" t="n"/>
     </row>
     <row r="328">
-      <c r="Z328" s="10" t="n"/>
+      <c r="AD328" s="10" t="n"/>
+      <c r="AE328" s="10" t="n"/>
     </row>
     <row r="329">
-      <c r="Z329" s="10" t="n"/>
+      <c r="AD329" s="10" t="n"/>
+      <c r="AE329" s="10" t="n"/>
     </row>
     <row r="330">
-      <c r="Z330" s="10" t="n"/>
+      <c r="AD330" s="10" t="n"/>
+      <c r="AE330" s="10" t="n"/>
     </row>
     <row r="331">
-      <c r="Z331" s="10" t="n"/>
+      <c r="AD331" s="10" t="n"/>
+      <c r="AE331" s="10" t="n"/>
     </row>
     <row r="332">
-      <c r="Z332" s="10" t="n"/>
+      <c r="AD332" s="10" t="n"/>
+      <c r="AE332" s="10" t="n"/>
     </row>
     <row r="333">
-      <c r="Z333" s="10" t="n"/>
+      <c r="AD333" s="10" t="n"/>
+      <c r="AE333" s="10" t="n"/>
     </row>
     <row r="334">
-      <c r="Z334" s="10" t="n"/>
+      <c r="AD334" s="10" t="n"/>
+      <c r="AE334" s="10" t="n"/>
     </row>
     <row r="335">
-      <c r="Z335" s="10" t="n"/>
+      <c r="AD335" s="10" t="n"/>
+      <c r="AE335" s="10" t="n"/>
     </row>
     <row r="336">
-      <c r="Z336" s="10" t="n"/>
+      <c r="AD336" s="10" t="n"/>
+      <c r="AE336" s="10" t="n"/>
     </row>
     <row r="337">
-      <c r="Z337" s="10" t="n"/>
+      <c r="AD337" s="10" t="n"/>
+      <c r="AE337" s="10" t="n"/>
     </row>
     <row r="338">
-      <c r="Z338" s="10" t="n"/>
+      <c r="AD338" s="10" t="n"/>
+      <c r="AE338" s="10" t="n"/>
     </row>
     <row r="339">
-      <c r="Z339" s="10" t="n"/>
+      <c r="AD339" s="10" t="n"/>
+      <c r="AE339" s="10" t="n"/>
     </row>
     <row r="340">
-      <c r="Z340" s="10" t="n"/>
+      <c r="AD340" s="10" t="n"/>
+      <c r="AE340" s="10" t="n"/>
     </row>
     <row r="341">
-      <c r="Z341" s="10" t="n"/>
+      <c r="AD341" s="10" t="n"/>
+      <c r="AE341" s="10" t="n"/>
     </row>
     <row r="342">
-      <c r="Z342" s="10" t="n"/>
+      <c r="AD342" s="10" t="n"/>
+      <c r="AE342" s="10" t="n"/>
     </row>
     <row r="343">
-      <c r="Z343" s="10" t="n"/>
+      <c r="AD343" s="10" t="n"/>
+      <c r="AE343" s="10" t="n"/>
     </row>
     <row r="344">
-      <c r="Z344" s="10" t="n"/>
+      <c r="AD344" s="10" t="n"/>
+      <c r="AE344" s="10" t="n"/>
     </row>
     <row r="345">
-      <c r="Z345" s="10" t="n"/>
+      <c r="AD345" s="10" t="n"/>
+      <c r="AE345" s="10" t="n"/>
     </row>
     <row r="346">
-      <c r="Z346" s="10" t="n"/>
+      <c r="AD346" s="10" t="n"/>
+      <c r="AE346" s="10" t="n"/>
     </row>
     <row r="347">
-      <c r="Z347" s="10" t="n"/>
+      <c r="AD347" s="10" t="n"/>
+      <c r="AE347" s="10" t="n"/>
     </row>
     <row r="348">
-      <c r="Z348" s="10" t="n"/>
+      <c r="AD348" s="10" t="n"/>
+      <c r="AE348" s="10" t="n"/>
     </row>
     <row r="349">
-      <c r="Z349" s="10" t="n"/>
+      <c r="AD349" s="10" t="n"/>
+      <c r="AE349" s="10" t="n"/>
     </row>
     <row r="350">
-      <c r="Z350" s="10" t="n"/>
+      <c r="AD350" s="10" t="n"/>
+      <c r="AE350" s="10" t="n"/>
     </row>
     <row r="351">
-      <c r="Z351" s="10" t="n"/>
+      <c r="AD351" s="10" t="n"/>
+      <c r="AE351" s="10" t="n"/>
     </row>
     <row r="352">
-      <c r="Z352" s="10" t="n"/>
+      <c r="AD352" s="10" t="n"/>
+      <c r="AE352" s="10" t="n"/>
     </row>
     <row r="353">
-      <c r="Z353" s="10" t="n"/>
+      <c r="AD353" s="10" t="n"/>
+      <c r="AE353" s="10" t="n"/>
     </row>
     <row r="354">
-      <c r="Z354" s="10" t="n"/>
+      <c r="AD354" s="10" t="n"/>
+      <c r="AE354" s="10" t="n"/>
     </row>
     <row r="355">
-      <c r="Z355" s="10" t="n"/>
+      <c r="AD355" s="10" t="n"/>
+      <c r="AE355" s="10" t="n"/>
     </row>
     <row r="356">
-      <c r="Z356" s="10" t="n"/>
+      <c r="AD356" s="10" t="n"/>
+      <c r="AE356" s="10" t="n"/>
     </row>
     <row r="357">
-      <c r="Z357" s="10" t="n"/>
+      <c r="AD357" s="10" t="n"/>
+      <c r="AE357" s="10" t="n"/>
     </row>
     <row r="358">
-      <c r="Z358" s="10" t="n"/>
+      <c r="AD358" s="10" t="n"/>
+      <c r="AE358" s="10" t="n"/>
     </row>
     <row r="359">
-      <c r="Z359" s="10" t="n"/>
+      <c r="AD359" s="10" t="n"/>
+      <c r="AE359" s="10" t="n"/>
     </row>
     <row r="360">
-      <c r="Z360" s="10" t="n"/>
+      <c r="AD360" s="10" t="n"/>
+      <c r="AE360" s="10" t="n"/>
     </row>
     <row r="361">
-      <c r="Z361" s="10" t="n"/>
+      <c r="AD361" s="10" t="n"/>
+      <c r="AE361" s="10" t="n"/>
     </row>
     <row r="362">
-      <c r="Z362" s="10" t="n"/>
+      <c r="AD362" s="10" t="n"/>
+      <c r="AE362" s="10" t="n"/>
     </row>
     <row r="363">
-      <c r="Z363" s="10" t="n"/>
+      <c r="AD363" s="10" t="n"/>
+      <c r="AE363" s="10" t="n"/>
     </row>
     <row r="364">
-      <c r="Z364" s="10" t="n"/>
+      <c r="AD364" s="10" t="n"/>
+      <c r="AE364" s="10" t="n"/>
     </row>
     <row r="365">
-      <c r="Z365" s="10" t="n"/>
+      <c r="AD365" s="10" t="n"/>
+      <c r="AE365" s="10" t="n"/>
     </row>
     <row r="366">
-      <c r="Z366" s="10" t="n"/>
+      <c r="AD366" s="10" t="n"/>
+      <c r="AE366" s="10" t="n"/>
     </row>
     <row r="367">
-      <c r="Z367" s="10" t="n"/>
+      <c r="AD367" s="10" t="n"/>
+      <c r="AE367" s="10" t="n"/>
     </row>
     <row r="368">
-      <c r="Z368" s="10" t="n"/>
+      <c r="AD368" s="10" t="n"/>
+      <c r="AE368" s="10" t="n"/>
     </row>
     <row r="369">
-      <c r="Z369" s="10" t="n"/>
+      <c r="AD369" s="10" t="n"/>
+      <c r="AE369" s="10" t="n"/>
     </row>
     <row r="370">
-      <c r="Z370" s="10" t="n"/>
+      <c r="AD370" s="10" t="n"/>
+      <c r="AE370" s="10" t="n"/>
     </row>
     <row r="371">
-      <c r="Z371" s="10" t="n"/>
+      <c r="AD371" s="10" t="n"/>
+      <c r="AE371" s="10" t="n"/>
     </row>
     <row r="372">
-      <c r="Z372" s="10" t="n"/>
+      <c r="AD372" s="10" t="n"/>
+      <c r="AE372" s="10" t="n"/>
     </row>
     <row r="373">
-      <c r="Z373" s="10" t="n"/>
+      <c r="AD373" s="10" t="n"/>
+      <c r="AE373" s="10" t="n"/>
     </row>
     <row r="374">
-      <c r="Z374" s="10" t="n"/>
+      <c r="AD374" s="10" t="n"/>
+      <c r="AE374" s="10" t="n"/>
     </row>
     <row r="375">
-      <c r="Z375" s="10" t="n"/>
+      <c r="AD375" s="10" t="n"/>
+      <c r="AE375" s="10" t="n"/>
     </row>
     <row r="376">
-      <c r="Z376" s="10" t="n"/>
+      <c r="AD376" s="10" t="n"/>
+      <c r="AE376" s="10" t="n"/>
     </row>
     <row r="377">
-      <c r="Z377" s="10" t="n"/>
+      <c r="AD377" s="10" t="n"/>
+      <c r="AE377" s="10" t="n"/>
     </row>
     <row r="378">
-      <c r="Z378" s="10" t="n"/>
+      <c r="AD378" s="10" t="n"/>
+      <c r="AE378" s="10" t="n"/>
     </row>
     <row r="379">
-      <c r="Z379" s="10" t="n"/>
+      <c r="AD379" s="10" t="n"/>
+      <c r="AE379" s="10" t="n"/>
     </row>
     <row r="380">
-      <c r="Z380" s="10" t="n"/>
+      <c r="AD380" s="10" t="n"/>
+      <c r="AE380" s="10" t="n"/>
     </row>
     <row r="381">
-      <c r="Z381" s="10" t="n"/>
+      <c r="AD381" s="10" t="n"/>
+      <c r="AE381" s="10" t="n"/>
     </row>
     <row r="382">
-      <c r="Z382" s="10" t="n"/>
+      <c r="AD382" s="10" t="n"/>
+      <c r="AE382" s="10" t="n"/>
     </row>
     <row r="383">
-      <c r="Z383" s="10" t="n"/>
+      <c r="AD383" s="10" t="n"/>
+      <c r="AE383" s="10" t="n"/>
     </row>
     <row r="384">
-      <c r="Z384" s="10" t="n"/>
+      <c r="AD384" s="10" t="n"/>
+      <c r="AE384" s="10" t="n"/>
     </row>
     <row r="385">
-      <c r="Z385" s="10" t="n"/>
+      <c r="AD385" s="10" t="n"/>
+      <c r="AE385" s="10" t="n"/>
     </row>
     <row r="386">
-      <c r="Z386" s="10" t="n"/>
+      <c r="AD386" s="10" t="n"/>
+      <c r="AE386" s="10" t="n"/>
     </row>
     <row r="387">
-      <c r="Z387" s="10" t="n"/>
+      <c r="AD387" s="10" t="n"/>
+      <c r="AE387" s="10" t="n"/>
     </row>
     <row r="388">
-      <c r="Z388" s="10" t="n"/>
+      <c r="AD388" s="10" t="n"/>
+      <c r="AE388" s="10" t="n"/>
     </row>
     <row r="389">
-      <c r="Z389" s="10" t="n"/>
+      <c r="AD389" s="10" t="n"/>
+      <c r="AE389" s="10" t="n"/>
     </row>
     <row r="390">
-      <c r="Z390" s="10" t="n"/>
+      <c r="AD390" s="10" t="n"/>
+      <c r="AE390" s="10" t="n"/>
     </row>
     <row r="391">
-      <c r="Z391" s="10" t="n"/>
+      <c r="AD391" s="10" t="n"/>
+      <c r="AE391" s="10" t="n"/>
     </row>
     <row r="392">
-      <c r="Z392" s="10" t="n"/>
+      <c r="AD392" s="10" t="n"/>
+      <c r="AE392" s="10" t="n"/>
     </row>
     <row r="393">
-      <c r="Z393" s="10" t="n"/>
+      <c r="AD393" s="10" t="n"/>
+      <c r="AE393" s="10" t="n"/>
     </row>
     <row r="394">
-      <c r="Z394" s="10" t="n"/>
+      <c r="AD394" s="10" t="n"/>
+      <c r="AE394" s="10" t="n"/>
     </row>
     <row r="395">
-      <c r="Z395" s="10" t="n"/>
+      <c r="AD395" s="10" t="n"/>
+      <c r="AE395" s="10" t="n"/>
     </row>
     <row r="396">
-      <c r="Z396" s="10" t="n"/>
+      <c r="AD396" s="10" t="n"/>
+      <c r="AE396" s="10" t="n"/>
     </row>
     <row r="397">
-      <c r="Z397" s="10" t="n"/>
+      <c r="AD397" s="10" t="n"/>
+      <c r="AE397" s="10" t="n"/>
     </row>
     <row r="398">
-      <c r="Z398" s="10" t="n"/>
+      <c r="AD398" s="10" t="n"/>
+      <c r="AE398" s="10" t="n"/>
     </row>
     <row r="399">
-      <c r="Z399" s="10" t="n"/>
+      <c r="AD399" s="10" t="n"/>
+      <c r="AE399" s="10" t="n"/>
     </row>
     <row r="400">
-      <c r="Z400" s="10" t="n"/>
+      <c r="AD400" s="10" t="n"/>
+      <c r="AE400" s="10" t="n"/>
     </row>
     <row r="401">
-      <c r="Z401" s="10" t="n"/>
+      <c r="AD401" s="10" t="n"/>
+      <c r="AE401" s="10" t="n"/>
     </row>
     <row r="402">
-      <c r="Z402" s="10" t="n"/>
+      <c r="AD402" s="10" t="n"/>
+      <c r="AE402" s="10" t="n"/>
     </row>
     <row r="403">
-      <c r="Z403" s="10" t="n"/>
+      <c r="AD403" s="10" t="n"/>
+      <c r="AE403" s="10" t="n"/>
     </row>
     <row r="404">
-      <c r="Z404" s="10" t="n"/>
+      <c r="AD404" s="10" t="n"/>
+      <c r="AE404" s="10" t="n"/>
     </row>
     <row r="405">
-      <c r="Z405" s="10" t="n"/>
+      <c r="AD405" s="10" t="n"/>
+      <c r="AE405" s="10" t="n"/>
     </row>
     <row r="406">
-      <c r="Z406" s="10" t="n"/>
+      <c r="AD406" s="10" t="n"/>
+      <c r="AE406" s="10" t="n"/>
     </row>
     <row r="407">
-      <c r="Z407" s="10" t="n"/>
+      <c r="AD407" s="10" t="n"/>
+      <c r="AE407" s="10" t="n"/>
     </row>
     <row r="408">
-      <c r="Z408" s="10" t="n"/>
+      <c r="AD408" s="10" t="n"/>
+      <c r="AE408" s="10" t="n"/>
     </row>
     <row r="409">
-      <c r="Z409" s="10" t="n"/>
+      <c r="AD409" s="10" t="n"/>
+      <c r="AE409" s="10" t="n"/>
     </row>
     <row r="410">
-      <c r="Z410" s="10" t="n"/>
+      <c r="AD410" s="10" t="n"/>
+      <c r="AE410" s="10" t="n"/>
     </row>
     <row r="411">
-      <c r="Z411" s="10" t="n"/>
+      <c r="AD411" s="10" t="n"/>
+      <c r="AE411" s="10" t="n"/>
     </row>
     <row r="412">
-      <c r="Z412" s="10" t="n"/>
+      <c r="AD412" s="10" t="n"/>
+      <c r="AE412" s="10" t="n"/>
     </row>
     <row r="413">
-      <c r="Z413" s="10" t="n"/>
+      <c r="AD413" s="10" t="n"/>
+      <c r="AE413" s="10" t="n"/>
     </row>
     <row r="414">
-      <c r="Z414" s="10" t="n"/>
+      <c r="AD414" s="10" t="n"/>
+      <c r="AE414" s="10" t="n"/>
     </row>
     <row r="415">
-      <c r="Z415" s="10" t="n"/>
+      <c r="AD415" s="10" t="n"/>
+      <c r="AE415" s="10" t="n"/>
     </row>
     <row r="416">
-      <c r="Z416" s="10" t="n"/>
+      <c r="AD416" s="10" t="n"/>
+      <c r="AE416" s="10" t="n"/>
     </row>
     <row r="417">
-      <c r="Z417" s="10" t="n"/>
+      <c r="AD417" s="10" t="n"/>
+      <c r="AE417" s="10" t="n"/>
     </row>
     <row r="418">
-      <c r="Z418" s="10" t="n"/>
+      <c r="AD418" s="10" t="n"/>
+      <c r="AE418" s="10" t="n"/>
     </row>
     <row r="419">
-      <c r="Z419" s="10" t="n"/>
+      <c r="AD419" s="10" t="n"/>
+      <c r="AE419" s="10" t="n"/>
     </row>
     <row r="420">
-      <c r="Z420" s="10" t="n"/>
+      <c r="AD420" s="10" t="n"/>
+      <c r="AE420" s="10" t="n"/>
     </row>
     <row r="421">
-      <c r="Z421" s="10" t="n"/>
+      <c r="AD421" s="10" t="n"/>
+      <c r="AE421" s="10" t="n"/>
     </row>
     <row r="422">
-      <c r="Z422" s="10" t="n"/>
+      <c r="AD422" s="10" t="n"/>
+      <c r="AE422" s="10" t="n"/>
     </row>
     <row r="423">
-      <c r="Z423" s="10" t="n"/>
+      <c r="AD423" s="10" t="n"/>
+      <c r="AE423" s="10" t="n"/>
     </row>
     <row r="424">
-      <c r="Z424" s="10" t="n"/>
+      <c r="AD424" s="10" t="n"/>
+      <c r="AE424" s="10" t="n"/>
     </row>
     <row r="425">
-      <c r="Z425" s="10" t="n"/>
+      <c r="AD425" s="10" t="n"/>
+      <c r="AE425" s="10" t="n"/>
     </row>
     <row r="426">
-      <c r="Z426" s="10" t="n"/>
+      <c r="AD426" s="10" t="n"/>
+      <c r="AE426" s="10" t="n"/>
     </row>
     <row r="427">
-      <c r="Z427" s="10" t="n"/>
+      <c r="AD427" s="10" t="n"/>
+      <c r="AE427" s="10" t="n"/>
     </row>
     <row r="428">
-      <c r="Z428" s="10" t="n"/>
+      <c r="AD428" s="10" t="n"/>
+      <c r="AE428" s="10" t="n"/>
     </row>
     <row r="429">
-      <c r="Z429" s="10" t="n"/>
+      <c r="AD429" s="10" t="n"/>
+      <c r="AE429" s="10" t="n"/>
     </row>
     <row r="430">
-      <c r="Z430" s="10" t="n"/>
+      <c r="AD430" s="10" t="n"/>
+      <c r="AE430" s="10" t="n"/>
     </row>
     <row r="431">
-      <c r="Z431" s="10" t="n"/>
+      <c r="AD431" s="10" t="n"/>
+      <c r="AE431" s="10" t="n"/>
     </row>
     <row r="432">
-      <c r="Z432" s="10" t="n"/>
+      <c r="AD432" s="10" t="n"/>
+      <c r="AE432" s="10" t="n"/>
     </row>
     <row r="433">
-      <c r="Z433" s="10" t="n"/>
+      <c r="AD433" s="10" t="n"/>
+      <c r="AE433" s="10" t="n"/>
     </row>
     <row r="434">
-      <c r="Z434" s="10" t="n"/>
+      <c r="AD434" s="10" t="n"/>
+      <c r="AE434" s="10" t="n"/>
     </row>
     <row r="435">
-      <c r="Z435" s="10" t="n"/>
+      <c r="AD435" s="10" t="n"/>
+      <c r="AE435" s="10" t="n"/>
     </row>
     <row r="436">
-      <c r="Z436" s="10" t="n"/>
+      <c r="AD436" s="10" t="n"/>
+      <c r="AE436" s="10" t="n"/>
     </row>
     <row r="437">
-      <c r="Z437" s="10" t="n"/>
+      <c r="AD437" s="10" t="n"/>
+      <c r="AE437" s="10" t="n"/>
     </row>
     <row r="438">
-      <c r="Z438" s="10" t="n"/>
+      <c r="AD438" s="10" t="n"/>
+      <c r="AE438" s="10" t="n"/>
     </row>
     <row r="439">
-      <c r="Z439" s="10" t="n"/>
+      <c r="AD439" s="10" t="n"/>
+      <c r="AE439" s="10" t="n"/>
     </row>
     <row r="440">
-      <c r="Z440" s="10" t="n"/>
+      <c r="AD440" s="10" t="n"/>
+      <c r="AE440" s="10" t="n"/>
     </row>
     <row r="441">
-      <c r="Z441" s="10" t="n"/>
+      <c r="AD441" s="10" t="n"/>
+      <c r="AE441" s="10" t="n"/>
     </row>
     <row r="442">
-      <c r="Z442" s="10" t="n"/>
+      <c r="AD442" s="10" t="n"/>
+      <c r="AE442" s="10" t="n"/>
     </row>
     <row r="443">
-      <c r="Z443" s="10" t="n"/>
+      <c r="AD443" s="10" t="n"/>
+      <c r="AE443" s="10" t="n"/>
     </row>
     <row r="444">
-      <c r="Z444" s="10" t="n"/>
+      <c r="AD444" s="10" t="n"/>
+      <c r="AE444" s="10" t="n"/>
     </row>
     <row r="445">
-      <c r="Z445" s="10" t="n"/>
+      <c r="AD445" s="10" t="n"/>
+      <c r="AE445" s="10" t="n"/>
     </row>
     <row r="446">
-      <c r="Z446" s="10" t="n"/>
+      <c r="AD446" s="10" t="n"/>
+      <c r="AE446" s="10" t="n"/>
     </row>
     <row r="447">
-      <c r="Z447" s="10" t="n"/>
+      <c r="AD447" s="10" t="n"/>
+      <c r="AE447" s="10" t="n"/>
     </row>
     <row r="448">
-      <c r="Z448" s="10" t="n"/>
+      <c r="AD448" s="10" t="n"/>
+      <c r="AE448" s="10" t="n"/>
     </row>
     <row r="449">
-      <c r="Z449" s="10" t="n"/>
+      <c r="AD449" s="10" t="n"/>
+      <c r="AE449" s="10" t="n"/>
     </row>
     <row r="450">
-      <c r="Z450" s="10" t="n"/>
+      <c r="AD450" s="10" t="n"/>
+      <c r="AE450" s="10" t="n"/>
     </row>
     <row r="451">
-      <c r="Z451" s="10" t="n"/>
+      <c r="AD451" s="10" t="n"/>
+      <c r="AE451" s="10" t="n"/>
     </row>
     <row r="452">
-      <c r="Z452" s="10" t="n"/>
+      <c r="AD452" s="10" t="n"/>
+      <c r="AE452" s="10" t="n"/>
     </row>
     <row r="453">
-      <c r="Z453" s="10" t="n"/>
+      <c r="AD453" s="10" t="n"/>
+      <c r="AE453" s="10" t="n"/>
     </row>
     <row r="454">
-      <c r="Z454" s="10" t="n"/>
+      <c r="AD454" s="10" t="n"/>
+      <c r="AE454" s="10" t="n"/>
     </row>
     <row r="455">
-      <c r="Z455" s="10" t="n"/>
+      <c r="AD455" s="10" t="n"/>
+      <c r="AE455" s="10" t="n"/>
     </row>
     <row r="456">
-      <c r="Z456" s="10" t="n"/>
+      <c r="AD456" s="10" t="n"/>
+      <c r="AE456" s="10" t="n"/>
     </row>
     <row r="457">
-      <c r="Z457" s="10" t="n"/>
+      <c r="AD457" s="10" t="n"/>
+      <c r="AE457" s="10" t="n"/>
     </row>
     <row r="458">
-      <c r="Z458" s="10" t="n"/>
+      <c r="AD458" s="10" t="n"/>
+      <c r="AE458" s="10" t="n"/>
     </row>
     <row r="459">
-      <c r="Z459" s="10" t="n"/>
+      <c r="AD459" s="10" t="n"/>
+      <c r="AE459" s="10" t="n"/>
     </row>
     <row r="460">
-      <c r="Z460" s="10" t="n"/>
+      <c r="AD460" s="10" t="n"/>
+      <c r="AE460" s="10" t="n"/>
     </row>
     <row r="461">
-      <c r="Z461" s="10" t="n"/>
+      <c r="AD461" s="10" t="n"/>
+      <c r="AE461" s="10" t="n"/>
     </row>
     <row r="462">
-      <c r="Z462" s="10" t="n"/>
+      <c r="AD462" s="10" t="n"/>
+      <c r="AE462" s="10" t="n"/>
     </row>
     <row r="463">
-      <c r="Z463" s="10" t="n"/>
+      <c r="AD463" s="10" t="n"/>
+      <c r="AE463" s="10" t="n"/>
     </row>
     <row r="464">
-      <c r="Z464" s="10" t="n"/>
+      <c r="AD464" s="10" t="n"/>
+      <c r="AE464" s="10" t="n"/>
     </row>
     <row r="465">
-      <c r="Z465" s="10" t="n"/>
+      <c r="AD465" s="10" t="n"/>
+      <c r="AE465" s="10" t="n"/>
     </row>
     <row r="466">
-      <c r="Z466" s="10" t="n"/>
+      <c r="AD466" s="10" t="n"/>
+      <c r="AE466" s="10" t="n"/>
     </row>
     <row r="467">
-      <c r="Z467" s="10" t="n"/>
+      <c r="AD467" s="10" t="n"/>
+      <c r="AE467" s="10" t="n"/>
     </row>
     <row r="468">
-      <c r="Z468" s="10" t="n"/>
+      <c r="AD468" s="10" t="n"/>
+      <c r="AE468" s="10" t="n"/>
     </row>
     <row r="469">
-      <c r="Z469" s="10" t="n"/>
+      <c r="AD469" s="10" t="n"/>
+      <c r="AE469" s="10" t="n"/>
     </row>
     <row r="470">
-      <c r="Z470" s="10" t="n"/>
+      <c r="AD470" s="10" t="n"/>
+      <c r="AE470" s="10" t="n"/>
     </row>
     <row r="471">
-      <c r="Z471" s="10" t="n"/>
+      <c r="AD471" s="10" t="n"/>
+      <c r="AE471" s="10" t="n"/>
     </row>
     <row r="472">
-      <c r="Z472" s="10" t="n"/>
+      <c r="AD472" s="10" t="n"/>
+      <c r="AE472" s="10" t="n"/>
     </row>
     <row r="473">
-      <c r="Z473" s="10" t="n"/>
+      <c r="AD473" s="10" t="n"/>
+      <c r="AE473" s="10" t="n"/>
     </row>
     <row r="474">
-      <c r="Z474" s="10" t="n"/>
+      <c r="AD474" s="10" t="n"/>
+      <c r="AE474" s="10" t="n"/>
     </row>
     <row r="475">
-      <c r="Z475" s="10" t="n"/>
+      <c r="AD475" s="10" t="n"/>
+      <c r="AE475" s="10" t="n"/>
     </row>
     <row r="476">
-      <c r="Z476" s="10" t="n"/>
+      <c r="AD476" s="10" t="n"/>
+      <c r="AE476" s="10" t="n"/>
     </row>
     <row r="477">
-      <c r="Z477" s="10" t="n"/>
+      <c r="AD477" s="10" t="n"/>
+      <c r="AE477" s="10" t="n"/>
     </row>
     <row r="478">
-      <c r="Z478" s="10" t="n"/>
+      <c r="AD478" s="10" t="n"/>
+      <c r="AE478" s="10" t="n"/>
     </row>
     <row r="479">
-      <c r="Z479" s="10" t="n"/>
+      <c r="AD479" s="10" t="n"/>
+      <c r="AE479" s="10" t="n"/>
     </row>
     <row r="480">
-      <c r="Z480" s="10" t="n"/>
+      <c r="AD480" s="10" t="n"/>
+      <c r="AE480" s="10" t="n"/>
     </row>
     <row r="481">
-      <c r="Z481" s="10" t="n"/>
+      <c r="AD481" s="10" t="n"/>
+      <c r="AE481" s="10" t="n"/>
     </row>
     <row r="482">
-      <c r="Z482" s="10" t="n"/>
+      <c r="AD482" s="10" t="n"/>
+      <c r="AE482" s="10" t="n"/>
     </row>
     <row r="483">
-      <c r="Z483" s="10" t="n"/>
+      <c r="AD483" s="10" t="n"/>
+      <c r="AE483" s="10" t="n"/>
     </row>
     <row r="484">
-      <c r="Z484" s="10" t="n"/>
+      <c r="AD484" s="10" t="n"/>
+      <c r="AE484" s="10" t="n"/>
     </row>
     <row r="485">
-      <c r="Z485" s="10" t="n"/>
+      <c r="AD485" s="10" t="n"/>
+      <c r="AE485" s="10" t="n"/>
     </row>
     <row r="486">
-      <c r="Z486" s="10" t="n"/>
+      <c r="AD486" s="10" t="n"/>
+      <c r="AE486" s="10" t="n"/>
     </row>
     <row r="487">
-      <c r="Z487" s="10" t="n"/>
+      <c r="AD487" s="10" t="n"/>
+      <c r="AE487" s="10" t="n"/>
     </row>
     <row r="488">
-      <c r="Z488" s="10" t="n"/>
+      <c r="AD488" s="10" t="n"/>
+      <c r="AE488" s="10" t="n"/>
     </row>
     <row r="489">
-      <c r="Z489" s="10" t="n"/>
+      <c r="AD489" s="10" t="n"/>
+      <c r="AE489" s="10" t="n"/>
     </row>
     <row r="490">
-      <c r="Z490" s="10" t="n"/>
+      <c r="AD490" s="10" t="n"/>
+      <c r="AE490" s="10" t="n"/>
     </row>
     <row r="491">
-      <c r="Z491" s="10" t="n"/>
+      <c r="AD491" s="10" t="n"/>
+      <c r="AE491" s="10" t="n"/>
     </row>
     <row r="492">
-      <c r="Z492" s="10" t="n"/>
+      <c r="AD492" s="10" t="n"/>
+      <c r="AE492" s="10" t="n"/>
     </row>
     <row r="493">
-      <c r="Z493" s="10" t="n"/>
+      <c r="AD493" s="10" t="n"/>
+      <c r="AE493" s="10" t="n"/>
     </row>
     <row r="494">
-      <c r="Z494" s="10" t="n"/>
+      <c r="AD494" s="10" t="n"/>
+      <c r="AE494" s="10" t="n"/>
     </row>
     <row r="495">
-      <c r="Z495" s="10" t="n"/>
+      <c r="AD495" s="10" t="n"/>
+      <c r="AE495" s="10" t="n"/>
     </row>
     <row r="496">
-      <c r="Z496" s="10" t="n"/>
+      <c r="AD496" s="10" t="n"/>
+      <c r="AE496" s="10" t="n"/>
     </row>
     <row r="497">
-      <c r="Z497" s="10" t="n"/>
+      <c r="AD497" s="10" t="n"/>
+      <c r="AE497" s="10" t="n"/>
     </row>
     <row r="498">
-      <c r="Z498" s="10" t="n"/>
+      <c r="AD498" s="10" t="n"/>
+      <c r="AE498" s="10" t="n"/>
     </row>
     <row r="499">
-      <c r="Z499" s="10" t="n"/>
+      <c r="AD499" s="10" t="n"/>
+      <c r="AE499" s="10" t="n"/>
     </row>
     <row r="500">
-      <c r="Z500" s="10" t="n"/>
+      <c r="AD500" s="10" t="n"/>
+      <c r="AE500" s="10" t="n"/>
     </row>
     <row r="501">
-      <c r="Z501" s="10" t="n"/>
+      <c r="AD501" s="10" t="n"/>
+      <c r="AE501" s="10" t="n"/>
     </row>
     <row r="502">
-      <c r="Z502" s="10" t="n"/>
+      <c r="AD502" s="10" t="n"/>
+      <c r="AE502" s="10" t="n"/>
     </row>
     <row r="503">
-      <c r="Z503" s="10" t="n"/>
+      <c r="AD503" s="10" t="n"/>
+      <c r="AE503" s="10" t="n"/>
     </row>
     <row r="504">
-      <c r="Z504" s="10" t="n"/>
+      <c r="AD504" s="10" t="n"/>
+      <c r="AE504" s="10" t="n"/>
     </row>
     <row r="505">
-      <c r="Z505" s="10" t="n"/>
+      <c r="AD505" s="10" t="n"/>
+      <c r="AE505" s="10" t="n"/>
     </row>
     <row r="506">
-      <c r="Z506" s="10" t="n"/>
+      <c r="AD506" s="10" t="n"/>
+      <c r="AE506" s="10" t="n"/>
     </row>
     <row r="507">
-      <c r="Z507" s="10" t="n"/>
+      <c r="AD507" s="10" t="n"/>
+      <c r="AE507" s="10" t="n"/>
     </row>
     <row r="508">
-      <c r="Z508" s="10" t="n"/>
+      <c r="AD508" s="10" t="n"/>
+      <c r="AE508" s="10" t="n"/>
     </row>
     <row r="509">
-      <c r="Z509" s="10" t="n"/>
+      <c r="AD509" s="10" t="n"/>
+      <c r="AE509" s="10" t="n"/>
     </row>
     <row r="510">
-      <c r="Z510" s="10" t="n"/>
+      <c r="AD510" s="10" t="n"/>
+      <c r="AE510" s="10" t="n"/>
     </row>
     <row r="511">
-      <c r="Z511" s="10" t="n"/>
+      <c r="AD511" s="10" t="n"/>
+      <c r="AE511" s="10" t="n"/>
     </row>
     <row r="512">
-      <c r="Z512" s="10" t="n"/>
+      <c r="AD512" s="10" t="n"/>
+      <c r="AE512" s="10" t="n"/>
     </row>
     <row r="513">
-      <c r="Z513" s="10" t="n"/>
+      <c r="AD513" s="10" t="n"/>
+      <c r="AE513" s="10" t="n"/>
     </row>
     <row r="514">
-      <c r="Z514" s="10" t="n"/>
+      <c r="AD514" s="10" t="n"/>
+      <c r="AE514" s="10" t="n"/>
     </row>
     <row r="515">
-      <c r="Z515" s="10" t="n"/>
+      <c r="AD515" s="10" t="n"/>
+      <c r="AE515" s="10" t="n"/>
     </row>
     <row r="516">
-      <c r="Z516" s="10" t="n"/>
+      <c r="AD516" s="10" t="n"/>
+      <c r="AE516" s="10" t="n"/>
     </row>
     <row r="517">
-      <c r="Z517" s="10" t="n"/>
+      <c r="AD517" s="10" t="n"/>
+      <c r="AE517" s="10" t="n"/>
     </row>
     <row r="518">
-      <c r="Z518" s="10" t="n"/>
+      <c r="AD518" s="10" t="n"/>
+      <c r="AE518" s="10" t="n"/>
     </row>
     <row r="519">
-      <c r="Z519" s="10" t="n"/>
+      <c r="AD519" s="10" t="n"/>
+      <c r="AE519" s="10" t="n"/>
     </row>
     <row r="520">
-      <c r="Z520" s="10" t="n"/>
+      <c r="AD520" s="10" t="n"/>
+      <c r="AE520" s="10" t="n"/>
     </row>
     <row r="521">
-      <c r="Z521" s="10" t="n"/>
+      <c r="AD521" s="10" t="n"/>
+      <c r="AE521" s="10" t="n"/>
     </row>
     <row r="522">
-      <c r="Z522" s="10" t="n"/>
+      <c r="AD522" s="10" t="n"/>
+      <c r="AE522" s="10" t="n"/>
     </row>
     <row r="523">
-      <c r="Z523" s="10" t="n"/>
+      <c r="AD523" s="10" t="n"/>
+      <c r="AE523" s="10" t="n"/>
     </row>
     <row r="524">
-      <c r="Z524" s="10" t="n"/>
+      <c r="AD524" s="10" t="n"/>
+      <c r="AE524" s="10" t="n"/>
     </row>
     <row r="525">
-      <c r="Z525" s="10" t="n"/>
+      <c r="AD525" s="10" t="n"/>
+      <c r="AE525" s="10" t="n"/>
     </row>
     <row r="526">
-      <c r="Z526" s="10" t="n"/>
+      <c r="AD526" s="10" t="n"/>
+      <c r="AE526" s="10" t="n"/>
     </row>
     <row r="527">
-      <c r="Z527" s="10" t="n"/>
+      <c r="AD527" s="10" t="n"/>
+      <c r="AE527" s="10" t="n"/>
     </row>
     <row r="528">
-      <c r="Z528" s="10" t="n"/>
+      <c r="AD528" s="10" t="n"/>
+      <c r="AE528" s="10" t="n"/>
     </row>
     <row r="529">
-      <c r="Z529" s="10" t="n"/>
+      <c r="AD529" s="10" t="n"/>
+      <c r="AE529" s="10" t="n"/>
     </row>
     <row r="530">
-      <c r="Z530" s="10" t="n"/>
+      <c r="AD530" s="10" t="n"/>
+      <c r="AE530" s="10" t="n"/>
     </row>
     <row r="531">
-      <c r="Z531" s="10" t="n"/>
+      <c r="AD531" s="10" t="n"/>
+      <c r="AE531" s="10" t="n"/>
     </row>
     <row r="532">
-      <c r="Z532" s="10" t="n"/>
+      <c r="AD532" s="10" t="n"/>
+      <c r="AE532" s="10" t="n"/>
     </row>
     <row r="533">
-      <c r="Z533" s="10" t="n"/>
+      <c r="AD533" s="10" t="n"/>
+      <c r="AE533" s="10" t="n"/>
     </row>
     <row r="534">
-      <c r="Z534" s="10" t="n"/>
+      <c r="AD534" s="10" t="n"/>
+      <c r="AE534" s="10" t="n"/>
     </row>
     <row r="535">
-      <c r="Z535" s="10" t="n"/>
+      <c r="AD535" s="10" t="n"/>
+      <c r="AE535" s="10" t="n"/>
     </row>
     <row r="536">
-      <c r="Z536" s="10" t="n"/>
+      <c r="AD536" s="10" t="n"/>
+      <c r="AE536" s="10" t="n"/>
     </row>
     <row r="537">
-      <c r="Z537" s="10" t="n"/>
+      <c r="AD537" s="10" t="n"/>
+      <c r="AE537" s="10" t="n"/>
     </row>
     <row r="538">
-      <c r="Z538" s="10" t="n"/>
+      <c r="AD538" s="10" t="n"/>
+      <c r="AE538" s="10" t="n"/>
     </row>
     <row r="539">
-      <c r="Z539" s="10" t="n"/>
+      <c r="AD539" s="10" t="n"/>
+      <c r="AE539" s="10" t="n"/>
     </row>
     <row r="540">
-      <c r="Z540" s="10" t="n"/>
+      <c r="AD540" s="10" t="n"/>
+      <c r="AE540" s="10" t="n"/>
     </row>
     <row r="541">
-      <c r="Z541" s="10" t="n"/>
+      <c r="AD541" s="10" t="n"/>
+      <c r="AE541" s="10" t="n"/>
     </row>
     <row r="542">
-      <c r="Z542" s="10" t="n"/>
+      <c r="AD542" s="10" t="n"/>
+      <c r="AE542" s="10" t="n"/>
     </row>
     <row r="543">
-      <c r="Z543" s="10" t="n"/>
+      <c r="AD543" s="10" t="n"/>
+      <c r="AE543" s="10" t="n"/>
     </row>
     <row r="544">
-      <c r="Z544" s="10" t="n"/>
+      <c r="AD544" s="10" t="n"/>
+      <c r="AE544" s="10" t="n"/>
     </row>
     <row r="545">
-      <c r="Z545" s="10" t="n"/>
+      <c r="AD545" s="10" t="n"/>
+      <c r="AE545" s="10" t="n"/>
     </row>
     <row r="546">
-      <c r="Z546" s="10" t="n"/>
+      <c r="AD546" s="10" t="n"/>
+      <c r="AE546" s="10" t="n"/>
     </row>
     <row r="547">
-      <c r="Z547" s="10" t="n"/>
+      <c r="AD547" s="10" t="n"/>
+      <c r="AE547" s="10" t="n"/>
     </row>
     <row r="548">
-      <c r="Z548" s="10" t="n"/>
+      <c r="AD548" s="10" t="n"/>
+      <c r="AE548" s="10" t="n"/>
     </row>
     <row r="549">
-      <c r="Z549" s="10" t="n"/>
+      <c r="AD549" s="10" t="n"/>
+      <c r="AE549" s="10" t="n"/>
     </row>
     <row r="550">
-      <c r="Z550" s="10" t="n"/>
+      <c r="AD550" s="10" t="n"/>
+      <c r="AE550" s="10" t="n"/>
     </row>
     <row r="551">
-      <c r="Z551" s="10" t="n"/>
+      <c r="AD551" s="10" t="n"/>
+      <c r="AE551" s="10" t="n"/>
     </row>
     <row r="552">
-      <c r="Z552" s="10" t="n"/>
+      <c r="AD552" s="10" t="n"/>
+      <c r="AE552" s="10" t="n"/>
     </row>
     <row r="553">
-      <c r="Z553" s="10" t="n"/>
+      <c r="AD553" s="10" t="n"/>
+      <c r="AE553" s="10" t="n"/>
     </row>
     <row r="554">
-      <c r="Z554" s="10" t="n"/>
+      <c r="AD554" s="10" t="n"/>
+      <c r="AE554" s="10" t="n"/>
     </row>
     <row r="555">
-      <c r="Z555" s="10" t="n"/>
+      <c r="AD555" s="10" t="n"/>
+      <c r="AE555" s="10" t="n"/>
     </row>
     <row r="556">
-      <c r="Z556" s="10" t="n"/>
+      <c r="AD556" s="10" t="n"/>
+      <c r="AE556" s="10" t="n"/>
     </row>
     <row r="557">
-      <c r="Z557" s="10" t="n"/>
+      <c r="AD557" s="10" t="n"/>
+      <c r="AE557" s="10" t="n"/>
     </row>
     <row r="558">
-      <c r="Z558" s="10" t="n"/>
+      <c r="AD558" s="10" t="n"/>
+      <c r="AE558" s="10" t="n"/>
     </row>
     <row r="559">
-      <c r="Z559" s="10" t="n"/>
+      <c r="AD559" s="10" t="n"/>
+      <c r="AE559" s="10" t="n"/>
     </row>
     <row r="560">
-      <c r="Z560" s="10" t="n"/>
+      <c r="AD560" s="10" t="n"/>
+      <c r="AE560" s="10" t="n"/>
     </row>
     <row r="561">
-      <c r="Z561" s="10" t="n"/>
+      <c r="AD561" s="10" t="n"/>
+      <c r="AE561" s="10" t="n"/>
     </row>
     <row r="562">
-      <c r="Z562" s="10" t="n"/>
+      <c r="AD562" s="10" t="n"/>
+      <c r="AE562" s="10" t="n"/>
     </row>
     <row r="563">
-      <c r="Z563" s="10" t="n"/>
+      <c r="AD563" s="10" t="n"/>
+      <c r="AE563" s="10" t="n"/>
     </row>
     <row r="564">
-      <c r="Z564" s="10" t="n"/>
+      <c r="AD564" s="10" t="n"/>
+      <c r="AE564" s="10" t="n"/>
     </row>
     <row r="565">
-      <c r="Z565" s="10" t="n"/>
+      <c r="AD565" s="10" t="n"/>
+      <c r="AE565" s="10" t="n"/>
     </row>
     <row r="566">
-      <c r="Z566" s="10" t="n"/>
+      <c r="AD566" s="10" t="n"/>
+      <c r="AE566" s="10" t="n"/>
     </row>
     <row r="567">
-      <c r="Z567" s="10" t="n"/>
+      <c r="AD567" s="10" t="n"/>
+      <c r="AE567" s="10" t="n"/>
     </row>
     <row r="568">
-      <c r="Z568" s="10" t="n"/>
+      <c r="AD568" s="10" t="n"/>
+      <c r="AE568" s="10" t="n"/>
     </row>
     <row r="569">
-      <c r="Z569" s="10" t="n"/>
+      <c r="AD569" s="10" t="n"/>
+      <c r="AE569" s="10" t="n"/>
     </row>
     <row r="570">
-      <c r="Z570" s="10" t="n"/>
+      <c r="AD570" s="10" t="n"/>
+      <c r="AE570" s="10" t="n"/>
     </row>
     <row r="571">
-      <c r="Z571" s="10" t="n"/>
+      <c r="AD571" s="10" t="n"/>
+      <c r="AE571" s="10" t="n"/>
     </row>
     <row r="572">
-      <c r="Z572" s="10" t="n"/>
+      <c r="AD572" s="10" t="n"/>
+      <c r="AE572" s="10" t="n"/>
     </row>
     <row r="573">
-      <c r="Z573" s="10" t="n"/>
+      <c r="AD573" s="10" t="n"/>
+      <c r="AE573" s="10" t="n"/>
     </row>
     <row r="574">
-      <c r="Z574" s="10" t="n"/>
+      <c r="AD574" s="10" t="n"/>
+      <c r="AE574" s="10" t="n"/>
     </row>
     <row r="575">
-      <c r="Z575" s="10" t="n"/>
+      <c r="AD575" s="10" t="n"/>
+      <c r="AE575" s="10" t="n"/>
     </row>
     <row r="576">
-      <c r="Z576" s="10" t="n"/>
+      <c r="AD576" s="10" t="n"/>
+      <c r="AE576" s="10" t="n"/>
     </row>
     <row r="577">
-      <c r="Z577" s="10" t="n"/>
+      <c r="AD577" s="10" t="n"/>
+      <c r="AE577" s="10" t="n"/>
     </row>
     <row r="578">
-      <c r="Z578" s="10" t="n"/>
+      <c r="AD578" s="10" t="n"/>
+      <c r="AE578" s="10" t="n"/>
     </row>
     <row r="579">
-      <c r="Z579" s="10" t="n"/>
+      <c r="AD579" s="10" t="n"/>
+      <c r="AE579" s="10" t="n"/>
     </row>
     <row r="580">
-      <c r="Z580" s="10" t="n"/>
+      <c r="AD580" s="10" t="n"/>
+      <c r="AE580" s="10" t="n"/>
     </row>
     <row r="581">
-      <c r="Z581" s="10" t="n"/>
+      <c r="AD581" s="10" t="n"/>
+      <c r="AE581" s="10" t="n"/>
     </row>
     <row r="582">
-      <c r="Z582" s="10" t="n"/>
+      <c r="AD582" s="10" t="n"/>
+      <c r="AE582" s="10" t="n"/>
     </row>
     <row r="583">
-      <c r="Z583" s="10" t="n"/>
+      <c r="AD583" s="10" t="n"/>
+      <c r="AE583" s="10" t="n"/>
     </row>
     <row r="584">
-      <c r="Z584" s="10" t="n"/>
+      <c r="AD584" s="10" t="n"/>
+      <c r="AE584" s="10" t="n"/>
     </row>
     <row r="585">
-      <c r="Z585" s="10" t="n"/>
+      <c r="AD585" s="10" t="n"/>
+      <c r="AE585" s="10" t="n"/>
     </row>
     <row r="586">
-      <c r="Z586" s="10" t="n"/>
+      <c r="AD586" s="10" t="n"/>
+      <c r="AE586" s="10" t="n"/>
     </row>
     <row r="587">
-      <c r="Z587" s="10" t="n"/>
+      <c r="AD587" s="10" t="n"/>
+      <c r="AE587" s="10" t="n"/>
     </row>
     <row r="588">
-      <c r="Z588" s="10" t="n"/>
+      <c r="AD588" s="10" t="n"/>
+      <c r="AE588" s="10" t="n"/>
     </row>
     <row r="589">
-      <c r="Z589" s="10" t="n"/>
+      <c r="AD589" s="10" t="n"/>
+      <c r="AE589" s="10" t="n"/>
     </row>
     <row r="590">
-      <c r="Z590" s="10" t="n"/>
+      <c r="AD590" s="10" t="n"/>
+      <c r="AE590" s="10" t="n"/>
     </row>
     <row r="591">
-      <c r="Z591" s="10" t="n"/>
+      <c r="AD591" s="10" t="n"/>
+      <c r="AE591" s="10" t="n"/>
     </row>
     <row r="592">
-      <c r="Z592" s="10" t="n"/>
+      <c r="AD592" s="10" t="n"/>
+      <c r="AE592" s="10" t="n"/>
     </row>
     <row r="593">
-      <c r="Z593" s="10" t="n"/>
+      <c r="AD593" s="10" t="n"/>
+      <c r="AE593" s="10" t="n"/>
     </row>
     <row r="594">
-      <c r="Z594" s="10" t="n"/>
+      <c r="AD594" s="10" t="n"/>
+      <c r="AE594" s="10" t="n"/>
     </row>
     <row r="595">
-      <c r="Z595" s="10" t="n"/>
+      <c r="AD595" s="10" t="n"/>
+      <c r="AE595" s="10" t="n"/>
     </row>
     <row r="596">
-      <c r="Z596" s="10" t="n"/>
+      <c r="AD596" s="10" t="n"/>
+      <c r="AE596" s="10" t="n"/>
     </row>
     <row r="597">
-      <c r="Z597" s="10" t="n"/>
+      <c r="AD597" s="10" t="n"/>
+      <c r="AE597" s="10" t="n"/>
     </row>
     <row r="598">
-      <c r="Z598" s="10" t="n"/>
+      <c r="AD598" s="10" t="n"/>
+      <c r="AE598" s="10" t="n"/>
     </row>
     <row r="599">
-      <c r="Z599" s="10" t="n"/>
+      <c r="AD599" s="10" t="n"/>
+      <c r="AE599" s="10" t="n"/>
     </row>
     <row r="600">
-      <c r="Z600" s="10" t="n"/>
+      <c r="AD600" s="10" t="n"/>
+      <c r="AE600" s="10" t="n"/>
     </row>
     <row r="601">
-      <c r="Z601" s="10" t="n"/>
+      <c r="AD601" s="10" t="n"/>
+      <c r="AE601" s="10" t="n"/>
     </row>
     <row r="602">
-      <c r="Z602" s="10" t="n"/>
+      <c r="AD602" s="10" t="n"/>
+      <c r="AE602" s="10" t="n"/>
     </row>
     <row r="603">
-      <c r="Z603" s="10" t="n"/>
+      <c r="AD603" s="10" t="n"/>
+      <c r="AE603" s="10" t="n"/>
     </row>
     <row r="604">
-      <c r="Z604" s="10" t="n"/>
+      <c r="AD604" s="10" t="n"/>
+      <c r="AE604" s="10" t="n"/>
     </row>
     <row r="605">
-      <c r="Z605" s="10" t="n"/>
+      <c r="AD605" s="10" t="n"/>
+      <c r="AE605" s="10" t="n"/>
     </row>
     <row r="606">
-      <c r="Z606" s="10" t="n"/>
+      <c r="AD606" s="10" t="n"/>
+      <c r="AE606" s="10" t="n"/>
     </row>
     <row r="607">
-      <c r="Z607" s="10" t="n"/>
+      <c r="AD607" s="10" t="n"/>
+      <c r="AE607" s="10" t="n"/>
     </row>
     <row r="608">
-      <c r="Z608" s="10" t="n"/>
+      <c r="AD608" s="10" t="n"/>
+      <c r="AE608" s="10" t="n"/>
     </row>
     <row r="609">
-      <c r="Z609" s="10" t="n"/>
+      <c r="AD609" s="10" t="n"/>
+      <c r="AE609" s="10" t="n"/>
     </row>
     <row r="610">
-      <c r="Z610" s="10" t="n"/>
+      <c r="AD610" s="10" t="n"/>
+      <c r="AE610" s="10" t="n"/>
     </row>
     <row r="611">
-      <c r="Z611" s="10" t="n"/>
+      <c r="AD611" s="10" t="n"/>
+      <c r="AE611" s="10" t="n"/>
     </row>
     <row r="612">
-      <c r="Z612" s="10" t="n"/>
+      <c r="AD612" s="10" t="n"/>
+      <c r="AE612" s="10" t="n"/>
     </row>
     <row r="613">
-      <c r="Z613" s="10" t="n"/>
+      <c r="AD613" s="10" t="n"/>
+      <c r="AE613" s="10" t="n"/>
     </row>
     <row r="614">
-      <c r="Z614" s="10" t="n"/>
+      <c r="AD614" s="10" t="n"/>
+      <c r="AE614" s="10" t="n"/>
     </row>
     <row r="615">
-      <c r="Z615" s="10" t="n"/>
+      <c r="AD615" s="10" t="n"/>
+      <c r="AE615" s="10" t="n"/>
     </row>
     <row r="616">
-      <c r="Z616" s="10" t="n"/>
+      <c r="AD616" s="10" t="n"/>
+      <c r="AE616" s="10" t="n"/>
     </row>
     <row r="617">
-      <c r="Z617" s="10" t="n"/>
+      <c r="AD617" s="10" t="n"/>
+      <c r="AE617" s="10" t="n"/>
     </row>
     <row r="618">
-      <c r="Z618" s="10" t="n"/>
+      <c r="AD618" s="10" t="n"/>
+      <c r="AE618" s="10" t="n"/>
     </row>
     <row r="619">
-      <c r="Z619" s="10" t="n"/>
+      <c r="AD619" s="10" t="n"/>
+      <c r="AE619" s="10" t="n"/>
     </row>
     <row r="620">
-      <c r="Z620" s="10" t="n"/>
+      <c r="AD620" s="10" t="n"/>
+      <c r="AE620" s="10" t="n"/>
     </row>
     <row r="621">
-      <c r="Z621" s="10" t="n"/>
+      <c r="AD621" s="10" t="n"/>
+      <c r="AE621" s="10" t="n"/>
     </row>
     <row r="622">
-      <c r="Z622" s="10" t="n"/>
+      <c r="AD622" s="10" t="n"/>
+      <c r="AE622" s="10" t="n"/>
     </row>
     <row r="623">
-      <c r="Z623" s="10" t="n"/>
+      <c r="AD623" s="10" t="n"/>
+      <c r="AE623" s="10" t="n"/>
     </row>
     <row r="624">
-      <c r="Z624" s="10" t="n"/>
+      <c r="AD624" s="10" t="n"/>
+      <c r="AE624" s="10" t="n"/>
     </row>
     <row r="625">
-      <c r="Z625" s="10" t="n"/>
+      <c r="AD625" s="10" t="n"/>
+      <c r="AE625" s="10" t="n"/>
     </row>
     <row r="626">
-      <c r="Z626" s="10" t="n"/>
+      <c r="AD626" s="10" t="n"/>
+      <c r="AE626" s="10" t="n"/>
     </row>
     <row r="627">
-      <c r="Z627" s="10" t="n"/>
+      <c r="AD627" s="10" t="n"/>
+      <c r="AE627" s="10" t="n"/>
     </row>
     <row r="628">
-      <c r="Z628" s="10" t="n"/>
+      <c r="AD628" s="10" t="n"/>
+      <c r="AE628" s="10" t="n"/>
     </row>
     <row r="629">
-      <c r="Z629" s="10" t="n"/>
+      <c r="AD629" s="10" t="n"/>
+      <c r="AE629" s="10" t="n"/>
     </row>
     <row r="630">
-      <c r="Z630" s="10" t="n"/>
+      <c r="AD630" s="10" t="n"/>
+      <c r="AE630" s="10" t="n"/>
     </row>
     <row r="631">
-      <c r="Z631" s="10" t="n"/>
+      <c r="AD631" s="10" t="n"/>
+      <c r="AE631" s="10" t="n"/>
     </row>
     <row r="632">
-      <c r="Z632" s="10" t="n"/>
+      <c r="AD632" s="10" t="n"/>
+      <c r="AE632" s="10" t="n"/>
     </row>
     <row r="633">
-      <c r="Z633" s="10" t="n"/>
+      <c r="AD633" s="10" t="n"/>
+      <c r="AE633" s="10" t="n"/>
     </row>
     <row r="634">
-      <c r="Z634" s="10" t="n"/>
+      <c r="AD634" s="10" t="n"/>
+      <c r="AE634" s="10" t="n"/>
     </row>
     <row r="635">
-      <c r="Z635" s="10" t="n"/>
+      <c r="AD635" s="10" t="n"/>
+      <c r="AE635" s="10" t="n"/>
     </row>
     <row r="636">
-      <c r="Z636" s="10" t="n"/>
+      <c r="AD636" s="10" t="n"/>
+      <c r="AE636" s="10" t="n"/>
     </row>
     <row r="637">
-      <c r="Z637" s="10" t="n"/>
+      <c r="AD637" s="10" t="n"/>
+      <c r="AE637" s="10" t="n"/>
     </row>
     <row r="638">
-      <c r="Z638" s="10" t="n"/>
+      <c r="AD638" s="10" t="n"/>
+      <c r="AE638" s="10" t="n"/>
     </row>
     <row r="639">
-      <c r="Z639" s="10" t="n"/>
+      <c r="AD639" s="10" t="n"/>
+      <c r="AE639" s="10" t="n"/>
     </row>
     <row r="640">
-      <c r="Z640" s="10" t="n"/>
+      <c r="AD640" s="10" t="n"/>
+      <c r="AE640" s="10" t="n"/>
     </row>
     <row r="641">
-      <c r="Z641" s="10" t="n"/>
+      <c r="AD641" s="10" t="n"/>
+      <c r="AE641" s="10" t="n"/>
     </row>
     <row r="642">
-      <c r="Z642" s="10" t="n"/>
+      <c r="AD642" s="10" t="n"/>
+      <c r="AE642" s="10" t="n"/>
     </row>
     <row r="643">
-      <c r="Z643" s="10" t="n"/>
+      <c r="AD643" s="10" t="n"/>
+      <c r="AE643" s="10" t="n"/>
     </row>
     <row r="644">
-      <c r="Z644" s="10" t="n"/>
+      <c r="AD644" s="10" t="n"/>
+      <c r="AE644" s="10" t="n"/>
     </row>
     <row r="645">
-      <c r="Z645" s="10" t="n"/>
+      <c r="AD645" s="10" t="n"/>
+      <c r="AE645" s="10" t="n"/>
     </row>
     <row r="646">
-      <c r="Z646" s="10" t="n"/>
+      <c r="AD646" s="10" t="n"/>
+      <c r="AE646" s="10" t="n"/>
     </row>
     <row r="647">
-      <c r="Z647" s="10" t="n"/>
+      <c r="AD647" s="10" t="n"/>
+      <c r="AE647" s="10" t="n"/>
     </row>
     <row r="648">
-      <c r="Z648" s="10" t="n"/>
+      <c r="AD648" s="10" t="n"/>
+      <c r="AE648" s="10" t="n"/>
     </row>
     <row r="649">
-      <c r="Z649" s="10" t="n"/>
+      <c r="AD649" s="10" t="n"/>
+      <c r="AE649" s="10" t="n"/>
     </row>
     <row r="650">
-      <c r="Z650" s="10" t="n"/>
+      <c r="AD650" s="10" t="n"/>
+      <c r="AE650" s="10" t="n"/>
     </row>
     <row r="651">
-      <c r="Z651" s="10" t="n"/>
+      <c r="AD651" s="10" t="n"/>
+      <c r="AE651" s="10" t="n"/>
     </row>
     <row r="652">
-      <c r="Z652" s="10" t="n"/>
+      <c r="AD652" s="10" t="n"/>
+      <c r="AE652" s="10" t="n"/>
     </row>
     <row r="653">
-      <c r="Z653" s="10" t="n"/>
+      <c r="AD653" s="10" t="n"/>
+      <c r="AE653" s="10" t="n"/>
     </row>
     <row r="654">
-      <c r="Z654" s="10" t="n"/>
+      <c r="AD654" s="10" t="n"/>
+      <c r="AE654" s="10" t="n"/>
     </row>
     <row r="655">
-      <c r="Z655" s="10" t="n"/>
+      <c r="AD655" s="10" t="n"/>
+      <c r="AE655" s="10" t="n"/>
     </row>
     <row r="656">
-      <c r="Z656" s="10" t="n"/>
+      <c r="AD656" s="10" t="n"/>
+      <c r="AE656" s="10" t="n"/>
     </row>
     <row r="657">
-      <c r="Z657" s="10" t="n"/>
+      <c r="AD657" s="10" t="n"/>
+      <c r="AE657" s="10" t="n"/>
     </row>
     <row r="658">
-      <c r="Z658" s="10" t="n"/>
+      <c r="AD658" s="10" t="n"/>
+      <c r="AE658" s="10" t="n"/>
     </row>
     <row r="659">
-      <c r="Z659" s="10" t="n"/>
+      <c r="AD659" s="10" t="n"/>
+      <c r="AE659" s="10" t="n"/>
     </row>
     <row r="660">
-      <c r="Z660" s="10" t="n"/>
+      <c r="AD660" s="10" t="n"/>
+      <c r="AE660" s="10" t="n"/>
     </row>
     <row r="661">
-      <c r="Z661" s="10" t="n"/>
+      <c r="AD661" s="10" t="n"/>
+      <c r="AE661" s="10" t="n"/>
     </row>
     <row r="662">
-      <c r="Z662" s="10" t="n"/>
+      <c r="AD662" s="10" t="n"/>
+      <c r="AE662" s="10" t="n"/>
     </row>
     <row r="663">
-      <c r="Z663" s="10" t="n"/>
+      <c r="AD663" s="10" t="n"/>
+      <c r="AE663" s="10" t="n"/>
     </row>
     <row r="664">
-      <c r="Z664" s="10" t="n"/>
+      <c r="AD664" s="10" t="n"/>
+      <c r="AE664" s="10" t="n"/>
     </row>
     <row r="665">
-      <c r="Z665" s="10" t="n"/>
+      <c r="AD665" s="10" t="n"/>
+      <c r="AE665" s="10" t="n"/>
     </row>
     <row r="666">
-      <c r="Z666" s="10" t="n"/>
+      <c r="AD666" s="10" t="n"/>
+      <c r="AE666" s="10" t="n"/>
     </row>
     <row r="667">
-      <c r="Z667" s="10" t="n"/>
+      <c r="AD667" s="10" t="n"/>
+      <c r="AE667" s="10" t="n"/>
     </row>
     <row r="668">
-      <c r="Z668" s="10" t="n"/>
+      <c r="AD668" s="10" t="n"/>
+      <c r="AE668" s="10" t="n"/>
     </row>
     <row r="669">
-      <c r="Z669" s="10" t="n"/>
+      <c r="AD669" s="10" t="n"/>
+      <c r="AE669" s="10" t="n"/>
     </row>
     <row r="670">
-      <c r="Z670" s="10" t="n"/>
+      <c r="AD670" s="10" t="n"/>
+      <c r="AE670" s="10" t="n"/>
     </row>
     <row r="671">
-      <c r="Z671" s="10" t="n"/>
+      <c r="AD671" s="10" t="n"/>
+      <c r="AE671" s="10" t="n"/>
     </row>
     <row r="672">
-      <c r="Z672" s="10" t="n"/>
+      <c r="AD672" s="10" t="n"/>
+      <c r="AE672" s="10" t="n"/>
     </row>
     <row r="673">
-      <c r="Z673" s="10" t="n"/>
+      <c r="AD673" s="10" t="n"/>
+      <c r="AE673" s="10" t="n"/>
     </row>
     <row r="674">
-      <c r="Z674" s="10" t="n"/>
+      <c r="AD674" s="10" t="n"/>
+      <c r="AE674" s="10" t="n"/>
     </row>
     <row r="675">
-      <c r="Z675" s="10" t="n"/>
+      <c r="AD675" s="10" t="n"/>
+      <c r="AE675" s="10" t="n"/>
     </row>
     <row r="676">
-      <c r="Z676" s="10" t="n"/>
+      <c r="AD676" s="10" t="n"/>
+      <c r="AE676" s="10" t="n"/>
     </row>
     <row r="677">
-      <c r="Z677" s="10" t="n"/>
+      <c r="AD677" s="10" t="n"/>
+      <c r="AE677" s="10" t="n"/>
     </row>
     <row r="678">
-      <c r="Z678" s="10" t="n"/>
+      <c r="AD678" s="10" t="n"/>
+      <c r="AE678" s="10" t="n"/>
     </row>
     <row r="679">
-      <c r="Z679" s="10" t="n"/>
+      <c r="AD679" s="10" t="n"/>
+      <c r="AE679" s="10" t="n"/>
     </row>
     <row r="680">
-      <c r="Z680" s="10" t="n"/>
+      <c r="AD680" s="10" t="n"/>
+      <c r="AE680" s="10" t="n"/>
     </row>
     <row r="681">
-      <c r="Z681" s="10" t="n"/>
+      <c r="AD681" s="10" t="n"/>
+      <c r="AE681" s="10" t="n"/>
     </row>
     <row r="682">
-      <c r="Z682" s="10" t="n"/>
+      <c r="AD682" s="10" t="n"/>
+      <c r="AE682" s="10" t="n"/>
     </row>
     <row r="683">
-      <c r="Z683" s="10" t="n"/>
+      <c r="AD683" s="10" t="n"/>
+      <c r="AE683" s="10" t="n"/>
     </row>
     <row r="684">
-      <c r="Z684" s="10" t="n"/>
+      <c r="AD684" s="10" t="n"/>
+      <c r="AE684" s="10" t="n"/>
     </row>
     <row r="685">
-      <c r="Z685" s="10" t="n"/>
+      <c r="AD685" s="10" t="n"/>
+      <c r="AE685" s="10" t="n"/>
     </row>
     <row r="686">
-      <c r="Z686" s="10" t="n"/>
+      <c r="AD686" s="10" t="n"/>
+      <c r="AE686" s="10" t="n"/>
     </row>
     <row r="687">
-      <c r="Z687" s="10" t="n"/>
+      <c r="AD687" s="10" t="n"/>
+      <c r="AE687" s="10" t="n"/>
     </row>
     <row r="688">
-      <c r="Z688" s="10" t="n"/>
+      <c r="AD688" s="10" t="n"/>
+      <c r="AE688" s="10" t="n"/>
     </row>
     <row r="689">
-      <c r="Z689" s="10" t="n"/>
+      <c r="AD689" s="10" t="n"/>
+      <c r="AE689" s="10" t="n"/>
     </row>
     <row r="690">
-      <c r="Z690" s="10" t="n"/>
+      <c r="AD690" s="10" t="n"/>
+      <c r="AE690" s="10" t="n"/>
     </row>
     <row r="691">
-      <c r="Z691" s="10" t="n"/>
+      <c r="AD691" s="10" t="n"/>
+      <c r="AE691" s="10" t="n"/>
     </row>
     <row r="692">
-      <c r="Z692" s="10" t="n"/>
+      <c r="AD692" s="10" t="n"/>
+      <c r="AE692" s="10" t="n"/>
     </row>
     <row r="693">
-      <c r="Z693" s="10" t="n"/>
+      <c r="AD693" s="10" t="n"/>
+      <c r="AE693" s="10" t="n"/>
     </row>
     <row r="694">
-      <c r="Z694" s="10" t="n"/>
+      <c r="AD694" s="10" t="n"/>
+      <c r="AE694" s="10" t="n"/>
     </row>
     <row r="695">
-      <c r="Z695" s="10" t="n"/>
+      <c r="AD695" s="10" t="n"/>
+      <c r="AE695" s="10" t="n"/>
     </row>
     <row r="696">
-      <c r="Z696" s="10" t="n"/>
+      <c r="AD696" s="10" t="n"/>
+      <c r="AE696" s="10" t="n"/>
     </row>
     <row r="697">
-      <c r="Z697" s="10" t="n"/>
+      <c r="AD697" s="10" t="n"/>
+      <c r="AE697" s="10" t="n"/>
     </row>
     <row r="698">
-      <c r="Z698" s="10" t="n"/>
+      <c r="AD698" s="10" t="n"/>
+      <c r="AE698" s="10" t="n"/>
     </row>
     <row r="699">
-      <c r="Z699" s="10" t="n"/>
+      <c r="AD699" s="10" t="n"/>
+      <c r="AE699" s="10" t="n"/>
     </row>
     <row r="700">
-      <c r="Z700" s="10" t="n"/>
+      <c r="AD700" s="10" t="n"/>
+      <c r="AE700" s="10" t="n"/>
     </row>
     <row r="701">
-      <c r="Z701" s="10" t="n"/>
+      <c r="AD701" s="10" t="n"/>
+      <c r="AE701" s="10" t="n"/>
     </row>
     <row r="702">
-      <c r="Z702" s="10" t="n"/>
+      <c r="AD702" s="10" t="n"/>
+      <c r="AE702" s="10" t="n"/>
     </row>
     <row r="703">
-      <c r="Z703" s="10" t="n"/>
+      <c r="AD703" s="10" t="n"/>
+      <c r="AE703" s="10" t="n"/>
     </row>
     <row r="704">
-      <c r="Z704" s="10" t="n"/>
+      <c r="AD704" s="10" t="n"/>
+      <c r="AE704" s="10" t="n"/>
     </row>
     <row r="705">
-      <c r="Z705" s="10" t="n"/>
+      <c r="AD705" s="10" t="n"/>
+      <c r="AE705" s="10" t="n"/>
     </row>
     <row r="706">
-      <c r="Z706" s="10" t="n"/>
+      <c r="AD706" s="10" t="n"/>
+      <c r="AE706" s="10" t="n"/>
     </row>
     <row r="707">
-      <c r="Z707" s="10" t="n"/>
+      <c r="AD707" s="10" t="n"/>
+      <c r="AE707" s="10" t="n"/>
     </row>
     <row r="708">
-      <c r="Z708" s="10" t="n"/>
+      <c r="AD708" s="10" t="n"/>
+      <c r="AE708" s="10" t="n"/>
     </row>
     <row r="709">
-      <c r="Z709" s="10" t="n"/>
+      <c r="AD709" s="10" t="n"/>
+      <c r="AE709" s="10" t="n"/>
     </row>
     <row r="710">
-      <c r="Z710" s="10" t="n"/>
+      <c r="AD710" s="10" t="n"/>
+      <c r="AE710" s="10" t="n"/>
     </row>
     <row r="711">
-      <c r="Z711" s="10" t="n"/>
+      <c r="AD711" s="10" t="n"/>
+      <c r="AE711" s="10" t="n"/>
     </row>
     <row r="712">
-      <c r="Z712" s="10" t="n"/>
+      <c r="AD712" s="10" t="n"/>
+      <c r="AE712" s="10" t="n"/>
     </row>
     <row r="713">
-      <c r="Z713" s="10" t="n"/>
+      <c r="AD713" s="10" t="n"/>
+      <c r="AE713" s="10" t="n"/>
     </row>
     <row r="714">
-      <c r="Z714" s="10" t="n"/>
+      <c r="AD714" s="10" t="n"/>
+      <c r="AE714" s="10" t="n"/>
     </row>
     <row r="715">
-      <c r="Z715" s="10" t="n"/>
+      <c r="AD715" s="10" t="n"/>
+      <c r="AE715" s="10" t="n"/>
     </row>
     <row r="716">
-      <c r="Z716" s="10" t="n"/>
+      <c r="AD716" s="10" t="n"/>
+      <c r="AE716" s="10" t="n"/>
     </row>
     <row r="717">
-      <c r="Z717" s="10" t="n"/>
+      <c r="AD717" s="10" t="n"/>
+      <c r="AE717" s="10" t="n"/>
     </row>
     <row r="718">
-      <c r="Z718" s="10" t="n"/>
+      <c r="AD718" s="10" t="n"/>
+      <c r="AE718" s="10" t="n"/>
     </row>
     <row r="719">
-      <c r="Z719" s="10" t="n"/>
+      <c r="AD719" s="10" t="n"/>
+      <c r="AE719" s="10" t="n"/>
     </row>
     <row r="720">
-      <c r="Z720" s="10" t="n"/>
+      <c r="AD720" s="10" t="n"/>
+      <c r="AE720" s="10" t="n"/>
     </row>
     <row r="721">
-      <c r="Z721" s="10" t="n"/>
+      <c r="AD721" s="10" t="n"/>
+      <c r="AE721" s="10" t="n"/>
     </row>
     <row r="722">
-      <c r="Z722" s="10" t="n"/>
+      <c r="AD722" s="10" t="n"/>
+      <c r="AE722" s="10" t="n"/>
     </row>
     <row r="723">
-      <c r="Z723" s="10" t="n"/>
+      <c r="AD723" s="10" t="n"/>
+      <c r="AE723" s="10" t="n"/>
     </row>
     <row r="724">
-      <c r="Z724" s="10" t="n"/>
+      <c r="AD724" s="10" t="n"/>
+      <c r="AE724" s="10" t="n"/>
     </row>
     <row r="725">
-      <c r="Z725" s="10" t="n"/>
+      <c r="AD725" s="10" t="n"/>
+      <c r="AE725" s="10" t="n"/>
     </row>
     <row r="726">
-      <c r="Z726" s="10" t="n"/>
+      <c r="AD726" s="10" t="n"/>
+      <c r="AE726" s="10" t="n"/>
     </row>
     <row r="727">
-      <c r="Z727" s="10" t="n"/>
+      <c r="AD727" s="10" t="n"/>
+      <c r="AE727" s="10" t="n"/>
     </row>
     <row r="728">
-      <c r="Z728" s="10" t="n"/>
+      <c r="AD728" s="10" t="n"/>
+      <c r="AE728" s="10" t="n"/>
     </row>
     <row r="729">
-      <c r="Z729" s="10" t="n"/>
+      <c r="AD729" s="10" t="n"/>
+      <c r="AE729" s="10" t="n"/>
     </row>
     <row r="730">
-      <c r="Z730" s="10" t="n"/>
+      <c r="AD730" s="10" t="n"/>
+      <c r="AE730" s="10" t="n"/>
     </row>
     <row r="731">
-      <c r="Z731" s="10" t="n"/>
+      <c r="AD731" s="10" t="n"/>
+      <c r="AE731" s="10" t="n"/>
     </row>
     <row r="732">
-      <c r="Z732" s="10" t="n"/>
+      <c r="AD732" s="10" t="n"/>
+      <c r="AE732" s="10" t="n"/>
     </row>
     <row r="733">
-      <c r="Z733" s="10" t="n"/>
+      <c r="AD733" s="10" t="n"/>
+      <c r="AE733" s="10" t="n"/>
     </row>
     <row r="734">
-      <c r="Z734" s="10" t="n"/>
+      <c r="AD734" s="10" t="n"/>
+      <c r="AE734" s="10" t="n"/>
     </row>
     <row r="735">
-      <c r="Z735" s="10" t="n"/>
+      <c r="AD735" s="10" t="n"/>
+      <c r="AE735" s="10" t="n"/>
     </row>
     <row r="736">
-      <c r="Z736" s="10" t="n"/>
+      <c r="AD736" s="10" t="n"/>
+      <c r="AE736" s="10" t="n"/>
     </row>
     <row r="737">
-      <c r="Z737" s="10" t="n"/>
+      <c r="AD737" s="10" t="n"/>
+      <c r="AE737" s="10" t="n"/>
     </row>
     <row r="738">
-      <c r="Z738" s="10" t="n"/>
+      <c r="AD738" s="10" t="n"/>
+      <c r="AE738" s="10" t="n"/>
     </row>
     <row r="739">
-      <c r="Z739" s="10" t="n"/>
+      <c r="AD739" s="10" t="n"/>
+      <c r="AE739" s="10" t="n"/>
     </row>
     <row r="740">
-      <c r="Z740" s="10" t="n"/>
+      <c r="AD740" s="10" t="n"/>
+      <c r="AE740" s="10" t="n"/>
     </row>
     <row r="741">
-      <c r="Z741" s="10" t="n"/>
+      <c r="AD741" s="10" t="n"/>
+      <c r="AE741" s="10" t="n"/>
     </row>
     <row r="742">
-      <c r="Z742" s="10" t="n"/>
+      <c r="AD742" s="10" t="n"/>
+      <c r="AE742" s="10" t="n"/>
     </row>
     <row r="743">
-      <c r="Z743" s="10" t="n"/>
+      <c r="AD743" s="10" t="n"/>
+      <c r="AE743" s="10" t="n"/>
     </row>
     <row r="744">
-      <c r="Z744" s="10" t="n"/>
+      <c r="AD744" s="10" t="n"/>
+      <c r="AE744" s="10" t="n"/>
     </row>
     <row r="745">
-      <c r="Z745" s="10" t="n"/>
+      <c r="AD745" s="10" t="n"/>
+      <c r="AE745" s="10" t="n"/>
     </row>
     <row r="746">
-      <c r="Z746" s="10" t="n"/>
+      <c r="AD746" s="10" t="n"/>
+      <c r="AE746" s="10" t="n"/>
     </row>
     <row r="747">
-      <c r="Z747" s="10" t="n"/>
+      <c r="AD747" s="10" t="n"/>
+      <c r="AE747" s="10" t="n"/>
     </row>
     <row r="748">
-      <c r="Z748" s="10" t="n"/>
+      <c r="AD748" s="10" t="n"/>
+      <c r="AE748" s="10" t="n"/>
     </row>
     <row r="749">
-      <c r="Z749" s="10" t="n"/>
+      <c r="AD749" s="10" t="n"/>
+      <c r="AE749" s="10" t="n"/>
     </row>
     <row r="750">
-      <c r="Z750" s="10" t="n"/>
+      <c r="AD750" s="10" t="n"/>
+      <c r="AE750" s="10" t="n"/>
     </row>
     <row r="751">
-      <c r="Z751" s="10" t="n"/>
+      <c r="AD751" s="10" t="n"/>
+      <c r="AE751" s="10" t="n"/>
     </row>
     <row r="752">
-      <c r="Z752" s="10" t="n"/>
+      <c r="AD752" s="10" t="n"/>
+      <c r="AE752" s="10" t="n"/>
     </row>
     <row r="753">
-      <c r="Z753" s="10" t="n"/>
+      <c r="AD753" s="10" t="n"/>
+      <c r="AE753" s="10" t="n"/>
     </row>
     <row r="754">
-      <c r="Z754" s="10" t="n"/>
+      <c r="AD754" s="10" t="n"/>
+      <c r="AE754" s="10" t="n"/>
     </row>
     <row r="755">
-      <c r="Z755" s="10" t="n"/>
+      <c r="AD755" s="10" t="n"/>
+      <c r="AE755" s="10" t="n"/>
     </row>
     <row r="756">
-      <c r="Z756" s="10" t="n"/>
+      <c r="AD756" s="10" t="n"/>
+      <c r="AE756" s="10" t="n"/>
     </row>
     <row r="757">
-      <c r="Z757" s="10" t="n"/>
+      <c r="AD757" s="10" t="n"/>
+      <c r="AE757" s="10" t="n"/>
     </row>
     <row r="758">
-      <c r="Z758" s="10" t="n"/>
+      <c r="AD758" s="10" t="n"/>
+      <c r="AE758" s="10" t="n"/>
     </row>
     <row r="759">
-      <c r="Z759" s="10" t="n"/>
+      <c r="AD759" s="10" t="n"/>
+      <c r="AE759" s="10" t="n"/>
     </row>
     <row r="760">
-      <c r="Z760" s="10" t="n"/>
+      <c r="AD760" s="10" t="n"/>
+      <c r="AE760" s="10" t="n"/>
     </row>
     <row r="761">
-      <c r="Z761" s="10" t="n"/>
+      <c r="AD761" s="10" t="n"/>
+      <c r="AE761" s="10" t="n"/>
     </row>
     <row r="762">
-      <c r="Z762" s="10" t="n"/>
+      <c r="AD762" s="10" t="n"/>
+      <c r="AE762" s="10" t="n"/>
     </row>
     <row r="763">
-      <c r="Z763" s="10" t="n"/>
+      <c r="AD763" s="10" t="n"/>
+      <c r="AE763" s="10" t="n"/>
     </row>
     <row r="764">
-      <c r="Z764" s="10" t="n"/>
+      <c r="AD764" s="10" t="n"/>
+      <c r="AE764" s="10" t="n"/>
     </row>
     <row r="765">
-      <c r="Z765" s="10" t="n"/>
+      <c r="AD765" s="10" t="n"/>
+      <c r="AE765" s="10" t="n"/>
     </row>
     <row r="766">
-      <c r="Z766" s="10" t="n"/>
+      <c r="AD766" s="10" t="n"/>
+      <c r="AE766" s="10" t="n"/>
     </row>
     <row r="767">
-      <c r="Z767" s="10" t="n"/>
+      <c r="AD767" s="10" t="n"/>
+      <c r="AE767" s="10" t="n"/>
     </row>
     <row r="768">
-      <c r="Z768" s="10" t="n"/>
+      <c r="AD768" s="10" t="n"/>
+      <c r="AE768" s="10" t="n"/>
     </row>
     <row r="769">
-      <c r="Z769" s="10" t="n"/>
+      <c r="AD769" s="10" t="n"/>
+      <c r="AE769" s="10" t="n"/>
     </row>
     <row r="770">
-      <c r="Z770" s="10" t="n"/>
+      <c r="AD770" s="10" t="n"/>
+      <c r="AE770" s="10" t="n"/>
     </row>
     <row r="771">
-      <c r="Z771" s="10" t="n"/>
+      <c r="AD771" s="10" t="n"/>
+      <c r="AE771" s="10" t="n"/>
     </row>
     <row r="772">
-      <c r="Z772" s="10" t="n"/>
+      <c r="AD772" s="10" t="n"/>
+      <c r="AE772" s="10" t="n"/>
     </row>
     <row r="773">
-      <c r="Z773" s="10" t="n"/>
+      <c r="AD773" s="10" t="n"/>
+      <c r="AE773" s="10" t="n"/>
     </row>
     <row r="774">
-      <c r="Z774" s="10" t="n"/>
+      <c r="AD774" s="10" t="n"/>
+      <c r="AE774" s="10" t="n"/>
     </row>
     <row r="775">
-      <c r="Z775" s="10" t="n"/>
+      <c r="AD775" s="10" t="n"/>
+      <c r="AE775" s="10" t="n"/>
     </row>
     <row r="776">
-      <c r="Z776" s="10" t="n"/>
+      <c r="AD776" s="10" t="n"/>
+      <c r="AE776" s="10" t="n"/>
     </row>
     <row r="777">
-      <c r="Z777" s="10" t="n"/>
+      <c r="AD777" s="10" t="n"/>
+      <c r="AE777" s="10" t="n"/>
     </row>
     <row r="778">
-      <c r="Z778" s="10" t="n"/>
+      <c r="AD778" s="10" t="n"/>
+      <c r="AE778" s="10" t="n"/>
     </row>
     <row r="779">
-      <c r="Z779" s="10" t="n"/>
+      <c r="AD779" s="10" t="n"/>
+      <c r="AE779" s="10" t="n"/>
     </row>
     <row r="780">
-      <c r="Z780" s="10" t="n"/>
+      <c r="AD780" s="10" t="n"/>
+      <c r="AE780" s="10" t="n"/>
     </row>
     <row r="781">
-      <c r="Z781" s="10" t="n"/>
+      <c r="AD781" s="10" t="n"/>
+      <c r="AE781" s="10" t="n"/>
     </row>
     <row r="782">
-      <c r="Z782" s="10" t="n"/>
+      <c r="AD782" s="10" t="n"/>
+      <c r="AE782" s="10" t="n"/>
     </row>
     <row r="783">
-      <c r="Z783" s="10" t="n"/>
+      <c r="AD783" s="10" t="n"/>
+      <c r="AE783" s="10" t="n"/>
     </row>
     <row r="784">
-      <c r="Z784" s="10" t="n"/>
+      <c r="AD784" s="10" t="n"/>
+      <c r="AE784" s="10" t="n"/>
     </row>
     <row r="785">
-      <c r="Z785" s="10" t="n"/>
+      <c r="AD785" s="10" t="n"/>
+      <c r="AE785" s="10" t="n"/>
     </row>
     <row r="786">
-      <c r="Z786" s="10" t="n"/>
+      <c r="AD786" s="10" t="n"/>
+      <c r="AE786" s="10" t="n"/>
     </row>
     <row r="787">
-      <c r="Z787" s="10" t="n"/>
+      <c r="AD787" s="10" t="n"/>
+      <c r="AE787" s="10" t="n"/>
     </row>
     <row r="788">
-      <c r="Z788" s="10" t="n"/>
+      <c r="AD788" s="10" t="n"/>
+      <c r="AE788" s="10" t="n"/>
     </row>
     <row r="789">
-      <c r="Z789" s="10" t="n"/>
+      <c r="AD789" s="10" t="n"/>
+      <c r="AE789" s="10" t="n"/>
     </row>
     <row r="790">
-      <c r="Z790" s="10" t="n"/>
+      <c r="AD790" s="10" t="n"/>
+      <c r="AE790" s="10" t="n"/>
     </row>
     <row r="791">
-      <c r="Z791" s="10" t="n"/>
+      <c r="AD791" s="10" t="n"/>
+      <c r="AE791" s="10" t="n"/>
     </row>
     <row r="792">
-      <c r="Z792" s="10" t="n"/>
+      <c r="AD792" s="10" t="n"/>
+      <c r="AE792" s="10" t="n"/>
     </row>
     <row r="793">
-      <c r="Z793" s="10" t="n"/>
+      <c r="AD793" s="10" t="n"/>
+      <c r="AE793" s="10" t="n"/>
     </row>
     <row r="794">
-      <c r="Z794" s="10" t="n"/>
+      <c r="AD794" s="10" t="n"/>
+      <c r="AE794" s="10" t="n"/>
     </row>
     <row r="795">
-      <c r="Z795" s="10" t="n"/>
+      <c r="AD795" s="10" t="n"/>
+      <c r="AE795" s="10" t="n"/>
     </row>
     <row r="796">
-      <c r="Z796" s="10" t="n"/>
+      <c r="AD796" s="10" t="n"/>
+      <c r="AE796" s="10" t="n"/>
     </row>
     <row r="797">
-      <c r="Z797" s="10" t="n"/>
+      <c r="AD797" s="10" t="n"/>
+      <c r="AE797" s="10" t="n"/>
     </row>
     <row r="798">
-      <c r="Z798" s="10" t="n"/>
+      <c r="AD798" s="10" t="n"/>
+      <c r="AE798" s="10" t="n"/>
     </row>
     <row r="799">
-      <c r="Z799" s="10" t="n"/>
+      <c r="AD799" s="10" t="n"/>
+      <c r="AE799" s="10" t="n"/>
     </row>
     <row r="800">
-      <c r="Z800" s="10" t="n"/>
+      <c r="AD800" s="10" t="n"/>
+      <c r="AE800" s="10" t="n"/>
     </row>
     <row r="801">
-      <c r="Z801" s="10" t="n"/>
+      <c r="AD801" s="10" t="n"/>
+      <c r="AE801" s="10" t="n"/>
     </row>
     <row r="802">
-      <c r="Z802" s="10" t="n"/>
+      <c r="AD802" s="10" t="n"/>
+      <c r="AE802" s="10" t="n"/>
     </row>
     <row r="803">
-      <c r="Z803" s="10" t="n"/>
+      <c r="AD803" s="10" t="n"/>
+      <c r="AE803" s="10" t="n"/>
     </row>
     <row r="804">
-      <c r="Z804" s="10" t="n"/>
+      <c r="AD804" s="10" t="n"/>
+      <c r="AE804" s="10" t="n"/>
     </row>
     <row r="805">
-      <c r="Z805" s="10" t="n"/>
+      <c r="AD805" s="10" t="n"/>
+      <c r="AE805" s="10" t="n"/>
     </row>
     <row r="806">
-      <c r="Z806" s="10" t="n"/>
+      <c r="AD806" s="10" t="n"/>
+      <c r="AE806" s="10" t="n"/>
     </row>
     <row r="807">
-      <c r="Z807" s="10" t="n"/>
+      <c r="AD807" s="10" t="n"/>
+      <c r="AE807" s="10" t="n"/>
     </row>
     <row r="808">
-      <c r="Z808" s="10" t="n"/>
+      <c r="AD808" s="10" t="n"/>
+      <c r="AE808" s="10" t="n"/>
     </row>
     <row r="809">
-      <c r="Z809" s="10" t="n"/>
+      <c r="AD809" s="10" t="n"/>
+      <c r="AE809" s="10" t="n"/>
     </row>
     <row r="810">
-      <c r="Z810" s="10" t="n"/>
+      <c r="AD810" s="10" t="n"/>
+      <c r="AE810" s="10" t="n"/>
     </row>
     <row r="811">
-      <c r="Z811" s="10" t="n"/>
+      <c r="AD811" s="10" t="n"/>
+      <c r="AE811" s="10" t="n"/>
     </row>
     <row r="812">
-      <c r="Z812" s="10" t="n"/>
+      <c r="AD812" s="10" t="n"/>
+      <c r="AE812" s="10" t="n"/>
     </row>
     <row r="813">
-      <c r="Z813" s="10" t="n"/>
+      <c r="AD813" s="10" t="n"/>
+      <c r="AE813" s="10" t="n"/>
     </row>
     <row r="814">
-      <c r="Z814" s="10" t="n"/>
+      <c r="AD814" s="10" t="n"/>
+      <c r="AE814" s="10" t="n"/>
     </row>
     <row r="815">
-      <c r="Z815" s="10" t="n"/>
+      <c r="AD815" s="10" t="n"/>
+      <c r="AE815" s="10" t="n"/>
     </row>
     <row r="816">
-      <c r="Z816" s="10" t="n"/>
+      <c r="AD816" s="10" t="n"/>
+      <c r="AE816" s="10" t="n"/>
     </row>
     <row r="817">
-      <c r="Z817" s="10" t="n"/>
+      <c r="AD817" s="10" t="n"/>
+      <c r="AE817" s="10" t="n"/>
     </row>
     <row r="818">
-      <c r="Z818" s="10" t="n"/>
+      <c r="AD818" s="10" t="n"/>
+      <c r="AE818" s="10" t="n"/>
     </row>
     <row r="819">
-      <c r="Z819" s="10" t="n"/>
+      <c r="AD819" s="10" t="n"/>
+      <c r="AE819" s="10" t="n"/>
     </row>
     <row r="820">
-      <c r="Z820" s="10" t="n"/>
+      <c r="AD820" s="10" t="n"/>
+      <c r="AE820" s="10" t="n"/>
     </row>
     <row r="821">
-      <c r="Z821" s="10" t="n"/>
+      <c r="AD821" s="10" t="n"/>
+      <c r="AE821" s="10" t="n"/>
     </row>
     <row r="822">
-      <c r="Z822" s="10" t="n"/>
+      <c r="AD822" s="10" t="n"/>
+      <c r="AE822" s="10" t="n"/>
     </row>
     <row r="823">
-      <c r="Z823" s="10" t="n"/>
+      <c r="AD823" s="10" t="n"/>
+      <c r="AE823" s="10" t="n"/>
     </row>
     <row r="824">
-      <c r="Z824" s="10" t="n"/>
+      <c r="AD824" s="10" t="n"/>
+      <c r="AE824" s="10" t="n"/>
     </row>
     <row r="825">
-      <c r="Z825" s="10" t="n"/>
+      <c r="AD825" s="10" t="n"/>
+      <c r="AE825" s="10" t="n"/>
     </row>
     <row r="826">
-      <c r="Z826" s="10" t="n"/>
+      <c r="AD826" s="10" t="n"/>
+      <c r="AE826" s="10" t="n"/>
     </row>
     <row r="827">
-      <c r="Z827" s="10" t="n"/>
+      <c r="AD827" s="10" t="n"/>
+      <c r="AE827" s="10" t="n"/>
     </row>
     <row r="828">
-      <c r="Z828" s="10" t="n"/>
+      <c r="AD828" s="10" t="n"/>
+      <c r="AE828" s="10" t="n"/>
     </row>
     <row r="829">
-      <c r="Z829" s="10" t="n"/>
+      <c r="AD829" s="10" t="n"/>
+      <c r="AE829" s="10" t="n"/>
     </row>
     <row r="830">
-      <c r="Z830" s="10" t="n"/>
+      <c r="AD830" s="10" t="n"/>
+      <c r="AE830" s="10" t="n"/>
     </row>
     <row r="831">
-      <c r="Z831" s="10" t="n"/>
+      <c r="AD831" s="10" t="n"/>
+      <c r="AE831" s="10" t="n"/>
     </row>
     <row r="832">
-      <c r="Z832" s="10" t="n"/>
+      <c r="AD832" s="10" t="n"/>
+      <c r="AE832" s="10" t="n"/>
     </row>
     <row r="833">
-      <c r="Z833" s="10" t="n"/>
+      <c r="AD833" s="10" t="n"/>
+      <c r="AE833" s="10" t="n"/>
     </row>
     <row r="834">
-      <c r="Z834" s="10" t="n"/>
+      <c r="AD834" s="10" t="n"/>
+      <c r="AE834" s="10" t="n"/>
     </row>
     <row r="835">
-      <c r="Z835" s="10" t="n"/>
+      <c r="AD835" s="10" t="n"/>
+      <c r="AE835" s="10" t="n"/>
     </row>
     <row r="836">
-      <c r="Z836" s="10" t="n"/>
+      <c r="AD836" s="10" t="n"/>
+      <c r="AE836" s="10" t="n"/>
     </row>
     <row r="837">
-      <c r="Z837" s="10" t="n"/>
+      <c r="AD837" s="10" t="n"/>
+      <c r="AE837" s="10" t="n"/>
     </row>
     <row r="838">
-      <c r="Z838" s="10" t="n"/>
+      <c r="AD838" s="10" t="n"/>
+      <c r="AE838" s="10" t="n"/>
     </row>
     <row r="839">
-      <c r="Z839" s="10" t="n"/>
+      <c r="AD839" s="10" t="n"/>
+      <c r="AE839" s="10" t="n"/>
     </row>
     <row r="840">
-      <c r="Z840" s="10" t="n"/>
+      <c r="AD840" s="10" t="n"/>
+      <c r="AE840" s="10" t="n"/>
     </row>
     <row r="841">
-      <c r="Z841" s="10" t="n"/>
+      <c r="AD841" s="10" t="n"/>
+      <c r="AE841" s="10" t="n"/>
     </row>
     <row r="842">
-      <c r="Z842" s="10" t="n"/>
+      <c r="AD842" s="10" t="n"/>
+      <c r="AE842" s="10" t="n"/>
     </row>
     <row r="843">
-      <c r="Z843" s="10" t="n"/>
+      <c r="AD843" s="10" t="n"/>
+      <c r="AE843" s="10" t="n"/>
     </row>
     <row r="844">
-      <c r="Z844" s="10" t="n"/>
+      <c r="AD844" s="10" t="n"/>
+      <c r="AE844" s="10" t="n"/>
     </row>
     <row r="845">
-      <c r="Z845" s="10" t="n"/>
+      <c r="AD845" s="10" t="n"/>
+      <c r="AE845" s="10" t="n"/>
     </row>
     <row r="846">
-      <c r="Z846" s="10" t="n"/>
+      <c r="AD846" s="10" t="n"/>
+      <c r="AE846" s="10" t="n"/>
     </row>
     <row r="847">
-      <c r="Z847" s="10" t="n"/>
+      <c r="AD847" s="10" t="n"/>
+      <c r="AE847" s="10" t="n"/>
     </row>
     <row r="848">
-      <c r="Z848" s="10" t="n"/>
+      <c r="AD848" s="10" t="n"/>
+      <c r="AE848" s="10" t="n"/>
     </row>
     <row r="849">
-      <c r="Z849" s="10" t="n"/>
+      <c r="AD849" s="10" t="n"/>
+      <c r="AE849" s="10" t="n"/>
     </row>
     <row r="850">
-      <c r="Z850" s="10" t="n"/>
+      <c r="AD850" s="10" t="n"/>
+      <c r="AE850" s="10" t="n"/>
     </row>
     <row r="851">
-      <c r="Z851" s="10" t="n"/>
+      <c r="AD851" s="10" t="n"/>
+      <c r="AE851" s="10" t="n"/>
     </row>
     <row r="852">
-      <c r="Z852" s="10" t="n"/>
+      <c r="AD852" s="10" t="n"/>
+      <c r="AE852" s="10" t="n"/>
     </row>
     <row r="853">
-      <c r="Z853" s="10" t="n"/>
+      <c r="AD853" s="10" t="n"/>
+      <c r="AE853" s="10" t="n"/>
     </row>
     <row r="854">
-      <c r="Z854" s="10" t="n"/>
+      <c r="AD854" s="10" t="n"/>
+      <c r="AE854" s="10" t="n"/>
     </row>
     <row r="855">
-      <c r="Z855" s="10" t="n"/>
+      <c r="AD855" s="10" t="n"/>
+      <c r="AE855" s="10" t="n"/>
     </row>
     <row r="856">
-      <c r="Z856" s="10" t="n"/>
+      <c r="AD856" s="10" t="n"/>
+      <c r="AE856" s="10" t="n"/>
     </row>
     <row r="857">
-      <c r="Z857" s="10" t="n"/>
+      <c r="AD857" s="10" t="n"/>
+      <c r="AE857" s="10" t="n"/>
     </row>
     <row r="858">
-      <c r="Z858" s="10" t="n"/>
+      <c r="AD858" s="10" t="n"/>
+      <c r="AE858" s="10" t="n"/>
     </row>
     <row r="859">
-      <c r="Z859" s="10" t="n"/>
+      <c r="AD859" s="10" t="n"/>
+      <c r="AE859" s="10" t="n"/>
     </row>
     <row r="860">
-      <c r="Z860" s="10" t="n"/>
+      <c r="AD860" s="10" t="n"/>
+      <c r="AE860" s="10" t="n"/>
     </row>
     <row r="861">
-      <c r="Z861" s="10" t="n"/>
+      <c r="AD861" s="10" t="n"/>
+      <c r="AE861" s="10" t="n"/>
     </row>
     <row r="862">
-      <c r="Z862" s="10" t="n"/>
+      <c r="AD862" s="10" t="n"/>
+      <c r="AE862" s="10" t="n"/>
     </row>
     <row r="863">
-      <c r="Z863" s="10" t="n"/>
+      <c r="AD863" s="10" t="n"/>
+      <c r="AE863" s="10" t="n"/>
     </row>
     <row r="864">
-      <c r="Z864" s="10" t="n"/>
+      <c r="AD864" s="10" t="n"/>
+      <c r="AE864" s="10" t="n"/>
     </row>
     <row r="865">
-      <c r="Z865" s="10" t="n"/>
+      <c r="AD865" s="10" t="n"/>
+      <c r="AE865" s="10" t="n"/>
     </row>
     <row r="866">
-      <c r="Z866" s="10" t="n"/>
+      <c r="AD866" s="10" t="n"/>
+      <c r="AE866" s="10" t="n"/>
     </row>
     <row r="867">
-      <c r="Z867" s="10" t="n"/>
+      <c r="AD867" s="10" t="n"/>
+      <c r="AE867" s="10" t="n"/>
     </row>
     <row r="868">
-      <c r="Z868" s="10" t="n"/>
+      <c r="AD868" s="10" t="n"/>
+      <c r="AE868" s="10" t="n"/>
     </row>
     <row r="869">
-      <c r="Z869" s="10" t="n"/>
+      <c r="AD869" s="10" t="n"/>
+      <c r="AE869" s="10" t="n"/>
     </row>
     <row r="870">
-      <c r="Z870" s="10" t="n"/>
+      <c r="AD870" s="10" t="n"/>
+      <c r="AE870" s="10" t="n"/>
     </row>
     <row r="871">
-      <c r="Z871" s="10" t="n"/>
+      <c r="AD871" s="10" t="n"/>
+      <c r="AE871" s="10" t="n"/>
     </row>
     <row r="872">
-      <c r="Z872" s="10" t="n"/>
+      <c r="AD872" s="10" t="n"/>
+      <c r="AE872" s="10" t="n"/>
     </row>
     <row r="873">
-      <c r="Z873" s="10" t="n"/>
+      <c r="AD873" s="10" t="n"/>
+      <c r="AE873" s="10" t="n"/>
     </row>
     <row r="874">
-      <c r="Z874" s="10" t="n"/>
+      <c r="AD874" s="10" t="n"/>
+      <c r="AE874" s="10" t="n"/>
     </row>
     <row r="875">
-      <c r="Z875" s="10" t="n"/>
+      <c r="AD875" s="10" t="n"/>
+      <c r="AE875" s="10" t="n"/>
     </row>
     <row r="876">
-      <c r="Z876" s="10" t="n"/>
+      <c r="AD876" s="10" t="n"/>
+      <c r="AE876" s="10" t="n"/>
     </row>
     <row r="877">
-      <c r="Z877" s="10" t="n"/>
+      <c r="AD877" s="10" t="n"/>
+      <c r="AE877" s="10" t="n"/>
     </row>
     <row r="878">
-      <c r="Z878" s="10" t="n"/>
+      <c r="AD878" s="10" t="n"/>
+      <c r="AE878" s="10" t="n"/>
     </row>
     <row r="879">
-      <c r="Z879" s="10" t="n"/>
+      <c r="AD879" s="10" t="n"/>
+      <c r="AE879" s="10" t="n"/>
     </row>
     <row r="880">
-      <c r="Z880" s="10" t="n"/>
+      <c r="AD880" s="10" t="n"/>
+      <c r="AE880" s="10" t="n"/>
     </row>
     <row r="881">
-      <c r="Z881" s="10" t="n"/>
+      <c r="AD881" s="10" t="n"/>
+      <c r="AE881" s="10" t="n"/>
     </row>
     <row r="882">
-      <c r="Z882" s="10" t="n"/>
+      <c r="AD882" s="10" t="n"/>
+      <c r="AE882" s="10" t="n"/>
     </row>
     <row r="883">
-      <c r="Z883" s="10" t="n"/>
+      <c r="AD883" s="10" t="n"/>
+      <c r="AE883" s="10" t="n"/>
     </row>
     <row r="884">
-      <c r="Z884" s="10" t="n"/>
+      <c r="AD884" s="10" t="n"/>
+      <c r="AE884" s="10" t="n"/>
     </row>
     <row r="885">
-      <c r="Z885" s="10" t="n"/>
+      <c r="AD885" s="10" t="n"/>
+      <c r="AE885" s="10" t="n"/>
     </row>
     <row r="886">
-      <c r="Z886" s="10" t="n"/>
+      <c r="AD886" s="10" t="n"/>
+      <c r="AE886" s="10" t="n"/>
     </row>
     <row r="887">
-      <c r="Z887" s="10" t="n"/>
+      <c r="AD887" s="10" t="n"/>
+      <c r="AE887" s="10" t="n"/>
     </row>
     <row r="888">
-      <c r="Z888" s="10" t="n"/>
+      <c r="AD888" s="10" t="n"/>
+      <c r="AE888" s="10" t="n"/>
     </row>
     <row r="889">
-      <c r="Z889" s="10" t="n"/>
+      <c r="AD889" s="10" t="n"/>
+      <c r="AE889" s="10" t="n"/>
     </row>
     <row r="890">
-      <c r="Z890" s="10" t="n"/>
+      <c r="AD890" s="10" t="n"/>
+      <c r="AE890" s="10" t="n"/>
     </row>
     <row r="891">
-      <c r="Z891" s="10" t="n"/>
+      <c r="AD891" s="10" t="n"/>
+      <c r="AE891" s="10" t="n"/>
     </row>
     <row r="892">
-      <c r="Z892" s="10" t="n"/>
+      <c r="AD892" s="10" t="n"/>
+      <c r="AE892" s="10" t="n"/>
     </row>
     <row r="893">
-      <c r="Z893" s="10" t="n"/>
+      <c r="AD893" s="10" t="n"/>
+      <c r="AE893" s="10" t="n"/>
     </row>
     <row r="894">
-      <c r="Z894" s="10" t="n"/>
+      <c r="AD894" s="10" t="n"/>
+      <c r="AE894" s="10" t="n"/>
     </row>
     <row r="895">
-      <c r="Z895" s="10" t="n"/>
+      <c r="AD895" s="10" t="n"/>
+      <c r="AE895" s="10" t="n"/>
     </row>
     <row r="896">
-      <c r="Z896" s="10" t="n"/>
+      <c r="AD896" s="10" t="n"/>
+      <c r="AE896" s="10" t="n"/>
     </row>
     <row r="897">
-      <c r="Z897" s="10" t="n"/>
+      <c r="AD897" s="10" t="n"/>
+      <c r="AE897" s="10" t="n"/>
     </row>
     <row r="898">
-      <c r="Z898" s="10" t="n"/>
+      <c r="AD898" s="10" t="n"/>
+      <c r="AE898" s="10" t="n"/>
     </row>
     <row r="899">
-      <c r="Z899" s="10" t="n"/>
+      <c r="AD899" s="10" t="n"/>
+      <c r="AE899" s="10" t="n"/>
     </row>
     <row r="900">
-      <c r="Z900" s="10" t="n"/>
+      <c r="AD900" s="10" t="n"/>
+      <c r="AE900" s="10" t="n"/>
     </row>
     <row r="901">
-      <c r="Z901" s="10" t="n"/>
+      <c r="AD901" s="10" t="n"/>
+      <c r="AE901" s="10" t="n"/>
     </row>
     <row r="902">
-      <c r="Z902" s="10" t="n"/>
+      <c r="AD902" s="10" t="n"/>
+      <c r="AE902" s="10" t="n"/>
     </row>
     <row r="903">
-      <c r="Z903" s="10" t="n"/>
+      <c r="AD903" s="10" t="n"/>
+      <c r="AE903" s="10" t="n"/>
     </row>
     <row r="904">
-      <c r="Z904" s="10" t="n"/>
+      <c r="AD904" s="10" t="n"/>
+      <c r="AE904" s="10" t="n"/>
     </row>
     <row r="905">
-      <c r="Z905" s="10" t="n"/>
+      <c r="AD905" s="10" t="n"/>
+      <c r="AE905" s="10" t="n"/>
     </row>
     <row r="906">
-      <c r="Z906" s="10" t="n"/>
+      <c r="AD906" s="10" t="n"/>
+      <c r="AE906" s="10" t="n"/>
     </row>
     <row r="907">
-      <c r="Z907" s="10" t="n"/>
+      <c r="AD907" s="10" t="n"/>
+      <c r="AE907" s="10" t="n"/>
     </row>
     <row r="908">
-      <c r="Z908" s="10" t="n"/>
+      <c r="AD908" s="10" t="n"/>
+      <c r="AE908" s="10" t="n"/>
     </row>
     <row r="909">
-      <c r="Z909" s="10" t="n"/>
+      <c r="AD909" s="10" t="n"/>
+      <c r="AE909" s="10" t="n"/>
     </row>
     <row r="910">
-      <c r="Z910" s="10" t="n"/>
+      <c r="AD910" s="10" t="n"/>
+      <c r="AE910" s="10" t="n"/>
     </row>
     <row r="911">
-      <c r="Z911" s="10" t="n"/>
+      <c r="AD911" s="10" t="n"/>
+      <c r="AE911" s="10" t="n"/>
     </row>
     <row r="912">
-      <c r="Z912" s="10" t="n"/>
+      <c r="AD912" s="10" t="n"/>
+      <c r="AE912" s="10" t="n"/>
     </row>
     <row r="913">
-      <c r="Z913" s="10" t="n"/>
+      <c r="AD913" s="10" t="n"/>
+      <c r="AE913" s="10" t="n"/>
     </row>
     <row r="914">
-      <c r="Z914" s="10" t="n"/>
+      <c r="AD914" s="10" t="n"/>
+      <c r="AE914" s="10" t="n"/>
     </row>
     <row r="915">
-      <c r="Z915" s="10" t="n"/>
+      <c r="AD915" s="10" t="n"/>
+      <c r="AE915" s="10" t="n"/>
     </row>
     <row r="916">
-      <c r="Z916" s="10" t="n"/>
+      <c r="AD916" s="10" t="n"/>
+      <c r="AE916" s="10" t="n"/>
     </row>
     <row r="917">
-      <c r="Z917" s="10" t="n"/>
+      <c r="AD917" s="10" t="n"/>
+      <c r="AE917" s="10" t="n"/>
     </row>
     <row r="918">
-      <c r="Z918" s="10" t="n"/>
+      <c r="AD918" s="10" t="n"/>
+      <c r="AE918" s="10" t="n"/>
     </row>
     <row r="919">
-      <c r="Z919" s="10" t="n"/>
+      <c r="AD919" s="10" t="n"/>
+      <c r="AE919" s="10" t="n"/>
     </row>
     <row r="920">
-      <c r="Z920" s="10" t="n"/>
+      <c r="AD920" s="10" t="n"/>
+      <c r="AE920" s="10" t="n"/>
     </row>
     <row r="921">
-      <c r="Z921" s="10" t="n"/>
+      <c r="AD921" s="10" t="n"/>
+      <c r="AE921" s="10" t="n"/>
     </row>
     <row r="922">
-      <c r="Z922" s="10" t="n"/>
+      <c r="AD922" s="10" t="n"/>
+      <c r="AE922" s="10" t="n"/>
     </row>
     <row r="923">
-      <c r="Z923" s="10" t="n"/>
+      <c r="AD923" s="10" t="n"/>
+      <c r="AE923" s="10" t="n"/>
     </row>
     <row r="924">
-      <c r="Z924" s="10" t="n"/>
+      <c r="AD924" s="10" t="n"/>
+      <c r="AE924" s="10" t="n"/>
     </row>
     <row r="925">
-      <c r="Z925" s="10" t="n"/>
+      <c r="AD925" s="10" t="n"/>
+      <c r="AE925" s="10" t="n"/>
     </row>
     <row r="926">
-      <c r="Z926" s="10" t="n"/>
+      <c r="AD926" s="10" t="n"/>
+      <c r="AE926" s="10" t="n"/>
     </row>
     <row r="927">
-      <c r="Z927" s="10" t="n"/>
+      <c r="AD927" s="10" t="n"/>
+      <c r="AE927" s="10" t="n"/>
     </row>
     <row r="928">
-      <c r="Z928" s="10" t="n"/>
+      <c r="AD928" s="10" t="n"/>
+      <c r="AE928" s="10" t="n"/>
     </row>
     <row r="929">
-      <c r="Z929" s="10" t="n"/>
+      <c r="AD929" s="10" t="n"/>
+      <c r="AE929" s="10" t="n"/>
     </row>
     <row r="930">
-      <c r="Z930" s="10" t="n"/>
+      <c r="AD930" s="10" t="n"/>
+      <c r="AE930" s="10" t="n"/>
     </row>
     <row r="931">
-      <c r="Z931" s="10" t="n"/>
+      <c r="AD931" s="10" t="n"/>
+      <c r="AE931" s="10" t="n"/>
     </row>
     <row r="932">
-      <c r="Z932" s="10" t="n"/>
+      <c r="AD932" s="10" t="n"/>
+      <c r="AE932" s="10" t="n"/>
     </row>
     <row r="933">
-      <c r="Z933" s="10" t="n"/>
+      <c r="AD933" s="10" t="n"/>
+      <c r="AE933" s="10" t="n"/>
     </row>
     <row r="934">
-      <c r="Z934" s="10" t="n"/>
+      <c r="AD934" s="10" t="n"/>
+      <c r="AE934" s="10" t="n"/>
     </row>
     <row r="935">
-      <c r="Z935" s="10" t="n"/>
+      <c r="AD935" s="10" t="n"/>
+      <c r="AE935" s="10" t="n"/>
     </row>
     <row r="936">
-      <c r="Z936" s="10" t="n"/>
+      <c r="AD936" s="10" t="n"/>
+      <c r="AE936" s="10" t="n"/>
     </row>
     <row r="937">
-      <c r="Z937" s="10" t="n"/>
+      <c r="AD937" s="10" t="n"/>
+      <c r="AE937" s="10" t="n"/>
     </row>
     <row r="938">
-      <c r="Z938" s="10" t="n"/>
+      <c r="AD938" s="10" t="n"/>
+      <c r="AE938" s="10" t="n"/>
     </row>
     <row r="939">
-      <c r="Z939" s="10" t="n"/>
+      <c r="AD939" s="10" t="n"/>
+      <c r="AE939" s="10" t="n"/>
     </row>
     <row r="940">
-      <c r="Z940" s="10" t="n"/>
+      <c r="AD940" s="10" t="n"/>
+      <c r="AE940" s="10" t="n"/>
     </row>
     <row r="941">
-      <c r="Z941" s="10" t="n"/>
+      <c r="AD941" s="10" t="n"/>
+      <c r="AE941" s="10" t="n"/>
     </row>
     <row r="942">
-      <c r="Z942" s="10" t="n"/>
+      <c r="AD942" s="10" t="n"/>
+      <c r="AE942" s="10" t="n"/>
     </row>
     <row r="943">
-      <c r="Z943" s="10" t="n"/>
+      <c r="AD943" s="10" t="n"/>
+      <c r="AE943" s="10" t="n"/>
     </row>
     <row r="944">
-      <c r="Z944" s="10" t="n"/>
+      <c r="AD944" s="10" t="n"/>
+      <c r="AE944" s="10" t="n"/>
     </row>
     <row r="945">
-      <c r="Z945" s="10" t="n"/>
+      <c r="AD945" s="10" t="n"/>
+      <c r="AE945" s="10" t="n"/>
     </row>
     <row r="946">
-      <c r="Z946" s="10" t="n"/>
+      <c r="AD946" s="10" t="n"/>
+      <c r="AE946" s="10" t="n"/>
     </row>
     <row r="947">
-      <c r="Z947" s="10" t="n"/>
+      <c r="AD947" s="10" t="n"/>
+      <c r="AE947" s="10" t="n"/>
     </row>
     <row r="948">
-      <c r="Z948" s="10" t="n"/>
+      <c r="AD948" s="10" t="n"/>
+      <c r="AE948" s="10" t="n"/>
     </row>
     <row r="949">
-      <c r="Z949" s="10" t="n"/>
+      <c r="AD949" s="10" t="n"/>
+      <c r="AE949" s="10" t="n"/>
     </row>
     <row r="950">
-      <c r="Z950" s="10" t="n"/>
+      <c r="AD950" s="10" t="n"/>
+      <c r="AE950" s="10" t="n"/>
     </row>
     <row r="951">
-      <c r="Z951" s="10" t="n"/>
+      <c r="AD951" s="10" t="n"/>
+      <c r="AE951" s="10" t="n"/>
     </row>
     <row r="952">
-      <c r="Z952" s="10" t="n"/>
+      <c r="AD952" s="10" t="n"/>
+      <c r="AE952" s="10" t="n"/>
     </row>
     <row r="953">
-      <c r="Z953" s="10" t="n"/>
+      <c r="AD953" s="10" t="n"/>
+      <c r="AE953" s="10" t="n"/>
     </row>
     <row r="954">
-      <c r="Z954" s="10" t="n"/>
+      <c r="AD954" s="10" t="n"/>
+      <c r="AE954" s="10" t="n"/>
     </row>
     <row r="955">
-      <c r="Z955" s="10" t="n"/>
+      <c r="AD955" s="10" t="n"/>
+      <c r="AE955" s="10" t="n"/>
     </row>
     <row r="956">
-      <c r="Z956" s="10" t="n"/>
+      <c r="AD956" s="10" t="n"/>
+      <c r="AE956" s="10" t="n"/>
     </row>
     <row r="957">
-      <c r="Z957" s="10" t="n"/>
+      <c r="AD957" s="10" t="n"/>
+      <c r="AE957" s="10" t="n"/>
     </row>
     <row r="958">
-      <c r="Z958" s="10" t="n"/>
+      <c r="AD958" s="10" t="n"/>
+      <c r="AE958" s="10" t="n"/>
     </row>
     <row r="959">
-      <c r="Z959" s="10" t="n"/>
+      <c r="AD959" s="10" t="n"/>
+      <c r="AE959" s="10" t="n"/>
     </row>
     <row r="960">
-      <c r="Z960" s="10" t="n"/>
+      <c r="AD960" s="10" t="n"/>
+      <c r="AE960" s="10" t="n"/>
     </row>
     <row r="961">
-      <c r="Z961" s="10" t="n"/>
+      <c r="AD961" s="10" t="n"/>
+      <c r="AE961" s="10" t="n"/>
     </row>
     <row r="962">
-      <c r="Z962" s="10" t="n"/>
+      <c r="AD962" s="10" t="n"/>
+      <c r="AE962" s="10" t="n"/>
     </row>
     <row r="963">
-      <c r="Z963" s="10" t="n"/>
+      <c r="AD963" s="10" t="n"/>
+      <c r="AE963" s="10" t="n"/>
     </row>
     <row r="964">
-      <c r="Z964" s="10" t="n"/>
+      <c r="AD964" s="10" t="n"/>
+      <c r="AE964" s="10" t="n"/>
     </row>
     <row r="965">
-      <c r="Z965" s="10" t="n"/>
+      <c r="AD965" s="10" t="n"/>
+      <c r="AE965" s="10" t="n"/>
     </row>
     <row r="966">
-      <c r="Z966" s="10" t="n"/>
+      <c r="AD966" s="10" t="n"/>
+      <c r="AE966" s="10" t="n"/>
     </row>
     <row r="967">
-      <c r="Z967" s="10" t="n"/>
+      <c r="AD967" s="10" t="n"/>
+      <c r="AE967" s="10" t="n"/>
     </row>
     <row r="968">
-      <c r="Z968" s="10" t="n"/>
+      <c r="AD968" s="10" t="n"/>
+      <c r="AE968" s="10" t="n"/>
     </row>
     <row r="969">
-      <c r="Z969" s="10" t="n"/>
+      <c r="AD969" s="10" t="n"/>
+      <c r="AE969" s="10" t="n"/>
     </row>
     <row r="970">
-      <c r="Z970" s="10" t="n"/>
+      <c r="AD970" s="10" t="n"/>
+      <c r="AE970" s="10" t="n"/>
     </row>
     <row r="971">
-      <c r="Z971" s="10" t="n"/>
+      <c r="AD971" s="10" t="n"/>
+      <c r="AE971" s="10" t="n"/>
     </row>
     <row r="972">
-      <c r="Z972" s="10" t="n"/>
+      <c r="AD972" s="10" t="n"/>
+      <c r="AE972" s="10" t="n"/>
     </row>
     <row r="973">
-      <c r="Z973" s="10" t="n"/>
+      <c r="AD973" s="10" t="n"/>
+      <c r="AE973" s="10" t="n"/>
     </row>
     <row r="974">
-      <c r="Z974" s="10" t="n"/>
+      <c r="AD974" s="10" t="n"/>
+      <c r="AE974" s="10" t="n"/>
     </row>
     <row r="975">
-      <c r="Z975" s="10" t="n"/>
+      <c r="AD975" s="10" t="n"/>
+      <c r="AE975" s="10" t="n"/>
     </row>
     <row r="976">
-      <c r="Z976" s="10" t="n"/>
+      <c r="AD976" s="10" t="n"/>
+      <c r="AE976" s="10" t="n"/>
     </row>
     <row r="977">
-      <c r="Z977" s="10" t="n"/>
+      <c r="AD977" s="10" t="n"/>
+      <c r="AE977" s="10" t="n"/>
     </row>
     <row r="978">
-      <c r="Z978" s="10" t="n"/>
+      <c r="AD978" s="10" t="n"/>
+      <c r="AE978" s="10" t="n"/>
     </row>
     <row r="979">
-      <c r="Z979" s="10" t="n"/>
+      <c r="AD979" s="10" t="n"/>
+      <c r="AE979" s="10" t="n"/>
     </row>
     <row r="980">
-      <c r="Z980" s="10" t="n"/>
+      <c r="AD980" s="10" t="n"/>
+      <c r="AE980" s="10" t="n"/>
     </row>
     <row r="981">
-      <c r="Z981" s="10" t="n"/>
+      <c r="AD981" s="10" t="n"/>
+      <c r="AE981" s="10" t="n"/>
     </row>
     <row r="982">
-      <c r="Z982" s="10" t="n"/>
+      <c r="AD982" s="10" t="n"/>
+      <c r="AE982" s="10" t="n"/>
     </row>
     <row r="983">
-      <c r="Z983" s="10" t="n"/>
+      <c r="AD983" s="10" t="n"/>
+      <c r="AE983" s="10" t="n"/>
     </row>
     <row r="984">
-      <c r="Z984" s="10" t="n"/>
+      <c r="AD984" s="10" t="n"/>
+      <c r="AE984" s="10" t="n"/>
     </row>
     <row r="985">
-      <c r="Z985" s="10" t="n"/>
+      <c r="AD985" s="10" t="n"/>
+      <c r="AE985" s="10" t="n"/>
     </row>
     <row r="986">
-      <c r="Z986" s="10" t="n"/>
+      <c r="AD986" s="10" t="n"/>
+      <c r="AE986" s="10" t="n"/>
     </row>
     <row r="987">
-      <c r="Z987" s="10" t="n"/>
+      <c r="AD987" s="10" t="n"/>
+      <c r="AE987" s="10" t="n"/>
     </row>
     <row r="988">
-      <c r="Z988" s="10" t="n"/>
+      <c r="AD988" s="10" t="n"/>
+      <c r="AE988" s="10" t="n"/>
     </row>
     <row r="989">
-      <c r="Z989" s="10" t="n"/>
+      <c r="AD989" s="10" t="n"/>
+      <c r="AE989" s="10" t="n"/>
     </row>
     <row r="990">
-      <c r="Z990" s="10" t="n"/>
+      <c r="AD990" s="10" t="n"/>
+      <c r="AE990" s="10" t="n"/>
     </row>
     <row r="991">
-      <c r="Z991" s="10" t="n"/>
+      <c r="AD991" s="10" t="n"/>
+      <c r="AE991" s="10" t="n"/>
     </row>
     <row r="992">
-      <c r="Z992" s="10" t="n"/>
+      <c r="AD992" s="10" t="n"/>
+      <c r="AE992" s="10" t="n"/>
     </row>
     <row r="993">
-      <c r="Z993" s="10" t="n"/>
+      <c r="AD993" s="10" t="n"/>
+      <c r="AE993" s="10" t="n"/>
     </row>
     <row r="994">
-      <c r="Z994" s="10" t="n"/>
+      <c r="AD994" s="10" t="n"/>
+      <c r="AE994" s="10" t="n"/>
     </row>
     <row r="995">
-      <c r="Z995" s="10" t="n"/>
+      <c r="AD995" s="10" t="n"/>
+      <c r="AE995" s="10" t="n"/>
     </row>
     <row r="996">
-      <c r="Z996" s="10" t="n"/>
+      <c r="AD996" s="10" t="n"/>
+      <c r="AE996" s="10" t="n"/>
     </row>
     <row r="997">
-      <c r="Z997" s="10" t="n"/>
+      <c r="AD997" s="10" t="n"/>
+      <c r="AE997" s="10" t="n"/>
     </row>
     <row r="998">
-      <c r="Z998" s="10" t="n"/>
+      <c r="AD998" s="10" t="n"/>
+      <c r="AE998" s="10" t="n"/>
     </row>
     <row r="999">
-      <c r="Z999" s="10" t="n"/>
+      <c r="AD999" s="10" t="n"/>
+      <c r="AE999" s="10" t="n"/>
     </row>
     <row r="1000">
-      <c r="Z1000" s="10" t="n"/>
+      <c r="AD1000" s="10" t="n"/>
+      <c r="AE1000" s="10" t="n"/>
     </row>
     <row r="1001">
-      <c r="Z1001" s="10" t="n"/>
+      <c r="AD1001" s="10" t="n"/>
+      <c r="AE1001" s="10" t="n"/>
     </row>
     <row r="1002">
-      <c r="Z1002" s="10" t="n"/>
+      <c r="AD1002" s="10" t="n"/>
+      <c r="AE1002" s="10" t="n"/>
     </row>
     <row r="1003">
-      <c r="Z1003" s="10" t="n"/>
+      <c r="AD1003" s="10" t="n"/>
+      <c r="AE1003" s="10" t="n"/>
     </row>
     <row r="1004">
-      <c r="Z1004" s="10" t="n"/>
+      <c r="AD1004" s="10" t="n"/>
+      <c r="AE1004" s="10" t="n"/>
     </row>
     <row r="1005">
-      <c r="Z1005" s="10" t="n"/>
+      <c r="AD1005" s="10" t="n"/>
+      <c r="AE1005" s="10" t="n"/>
     </row>
     <row r="1006">
-      <c r="Z1006" s="10" t="n"/>
+      <c r="AD1006" s="10" t="n"/>
+      <c r="AE1006" s="10" t="n"/>
     </row>
     <row r="1007">
-      <c r="Z1007" s="10" t="n"/>
+      <c r="AD1007" s="10" t="n"/>
+      <c r="AE1007" s="10" t="n"/>
     </row>
     <row r="1008">
-      <c r="Z1008" s="10" t="n"/>
+      <c r="AD1008" s="10" t="n"/>
+      <c r="AE1008" s="10" t="n"/>
     </row>
     <row r="1009">
-      <c r="Z1009" s="10" t="n"/>
+      <c r="AD1009" s="10" t="n"/>
+      <c r="AE1009" s="10" t="n"/>
     </row>
     <row r="1010">
-      <c r="Z1010" s="10" t="n"/>
+      <c r="AD1010" s="10" t="n"/>
+      <c r="AE1010" s="10" t="n"/>
     </row>
     <row r="1011">
-      <c r="Z1011" s="10" t="n"/>
+      <c r="AD1011" s="10" t="n"/>
+      <c r="AE1011" s="10" t="n"/>
     </row>
     <row r="1012">
-      <c r="Z1012" s="10" t="n"/>
+      <c r="AD1012" s="10" t="n"/>
+      <c r="AE1012" s="10" t="n"/>
     </row>
     <row r="1013">
-      <c r="Z1013" s="10" t="n"/>
+      <c r="AD1013" s="10" t="n"/>
+      <c r="AE1013" s="10" t="n"/>
     </row>
     <row r="1014">
-      <c r="Z1014" s="10" t="n"/>
+      <c r="AD1014" s="10" t="n"/>
+      <c r="AE1014" s="10" t="n"/>
     </row>
     <row r="1015">
-      <c r="Z1015" s="10" t="n"/>
+      <c r="AD1015" s="10" t="n"/>
+      <c r="AE1015" s="10" t="n"/>
     </row>
     <row r="1016">
-      <c r="Z1016" s="10" t="n"/>
+      <c r="AD1016" s="10" t="n"/>
+      <c r="AE1016" s="10" t="n"/>
     </row>
     <row r="1017">
-      <c r="Z1017" s="10" t="n"/>
+      <c r="AD1017" s="10" t="n"/>
+      <c r="AE1017" s="10" t="n"/>
     </row>
     <row r="1018">
-      <c r="Z1018" s="10" t="n"/>
+      <c r="AD1018" s="10" t="n"/>
+      <c r="AE1018" s="10" t="n"/>
     </row>
     <row r="1019">
-      <c r="Z1019" s="10" t="n"/>
+      <c r="AD1019" s="10" t="n"/>
+      <c r="AE1019" s="10" t="n"/>
     </row>
     <row r="1020">
-      <c r="Z1020" s="10" t="n"/>
+      <c r="AD1020" s="10" t="n"/>
+      <c r="AE1020" s="10" t="n"/>
     </row>
     <row r="1021">
-      <c r="Z1021" s="10" t="n"/>
+      <c r="AD1021" s="10" t="n"/>
+      <c r="AE1021" s="10" t="n"/>
     </row>
     <row r="1022">
-      <c r="Z1022" s="10" t="n"/>
+      <c r="AD1022" s="10" t="n"/>
+      <c r="AE1022" s="10" t="n"/>
     </row>
     <row r="1023">
-      <c r="Z1023" s="10" t="n"/>
+      <c r="AD1023" s="10" t="n"/>
+      <c r="AE1023" s="10" t="n"/>
     </row>
     <row r="1024">
-      <c r="Z1024" s="10" t="n"/>
+      <c r="AD1024" s="10" t="n"/>
+      <c r="AE1024" s="10" t="n"/>
     </row>
     <row r="1025">
-      <c r="Z1025" s="10" t="n"/>
+      <c r="AD1025" s="10" t="n"/>
+      <c r="AE1025" s="10" t="n"/>
     </row>
     <row r="1026">
-      <c r="Z1026" s="10" t="n"/>
+      <c r="AD1026" s="10" t="n"/>
+      <c r="AE1026" s="10" t="n"/>
     </row>
     <row r="1027">
-      <c r="Z1027" s="10" t="n"/>
+      <c r="AD1027" s="10" t="n"/>
+      <c r="AE1027" s="10" t="n"/>
     </row>
     <row r="1028">
-      <c r="Z1028" s="10" t="n"/>
+      <c r="AD1028" s="10" t="n"/>
+      <c r="AE1028" s="10" t="n"/>
     </row>
     <row r="1029">
-      <c r="Z1029" s="10" t="n"/>
+      <c r="AD1029" s="10" t="n"/>
+      <c r="AE1029" s="10" t="n"/>
     </row>
     <row r="1030">
-      <c r="Z1030" s="10" t="n"/>
+      <c r="AD1030" s="10" t="n"/>
+      <c r="AE1030" s="10" t="n"/>
     </row>
     <row r="1031">
-      <c r="Z1031" s="10" t="n"/>
+      <c r="AD1031" s="10" t="n"/>
+      <c r="AE1031" s="10" t="n"/>
     </row>
     <row r="1032">
-      <c r="Z1032" s="10" t="n"/>
+      <c r="AD1032" s="10" t="n"/>
+      <c r="AE1032" s="10" t="n"/>
     </row>
     <row r="1033">
-      <c r="Z1033" s="10" t="n"/>
+      <c r="AD1033" s="10" t="n"/>
+      <c r="AE1033" s="10" t="n"/>
     </row>
     <row r="1034">
-      <c r="Z1034" s="10" t="n"/>
+      <c r="AD1034" s="10" t="n"/>
+      <c r="AE1034" s="10" t="n"/>
     </row>
     <row r="1035">
-      <c r="Z1035" s="10" t="n"/>
+      <c r="AD1035" s="10" t="n"/>
+      <c r="AE1035" s="10" t="n"/>
     </row>
     <row r="1036">
-      <c r="Z1036" s="10" t="n"/>
+      <c r="AD1036" s="10" t="n"/>
+      <c r="AE1036" s="10" t="n"/>
     </row>
     <row r="1037">
-      <c r="Z1037" s="10" t="n"/>
+      <c r="AD1037" s="10" t="n"/>
+      <c r="AE1037" s="10" t="n"/>
     </row>
     <row r="1038">
-      <c r="Z1038" s="10" t="n"/>
+      <c r="AD1038" s="10" t="n"/>
+      <c r="AE1038" s="10" t="n"/>
     </row>
     <row r="1039">
-      <c r="Z1039" s="10" t="n"/>
+      <c r="AD1039" s="10" t="n"/>
+      <c r="AE1039" s="10" t="n"/>
     </row>
     <row r="1040">
-      <c r="Z1040" s="10" t="n"/>
+      <c r="AD1040" s="10" t="n"/>
+      <c r="AE1040" s="10" t="n"/>
     </row>
     <row r="1041">
-      <c r="Z1041" s="10" t="n"/>
+      <c r="AD1041" s="10" t="n"/>
+      <c r="AE1041" s="10" t="n"/>
     </row>
     <row r="1042">
-      <c r="Z1042" s="10" t="n"/>
+      <c r="AD1042" s="10" t="n"/>
+      <c r="AE1042" s="10" t="n"/>
     </row>
     <row r="1043">
-      <c r="Z1043" s="10" t="n"/>
+      <c r="AD1043" s="10" t="n"/>
+      <c r="AE1043" s="10" t="n"/>
     </row>
     <row r="1044">
-      <c r="Z1044" s="10" t="n"/>
+      <c r="AD1044" s="10" t="n"/>
+      <c r="AE1044" s="10" t="n"/>
     </row>
     <row r="1045">
-      <c r="Z1045" s="10" t="n"/>
+      <c r="AD1045" s="10" t="n"/>
+      <c r="AE1045" s="10" t="n"/>
     </row>
     <row r="1046">
-      <c r="Z1046" s="10" t="n"/>
+      <c r="AD1046" s="10" t="n"/>
+      <c r="AE1046" s="10" t="n"/>
     </row>
     <row r="1047">
-      <c r="Z1047" s="10" t="n"/>
+      <c r="AD1047" s="10" t="n"/>
+      <c r="AE1047" s="10" t="n"/>
     </row>
     <row r="1048">
-      <c r="Z1048" s="10" t="n"/>
+      <c r="AD1048" s="10" t="n"/>
+      <c r="AE1048" s="10" t="n"/>
     </row>
     <row r="1049">
-      <c r="Z1049" s="10" t="n"/>
+      <c r="AD1049" s="10" t="n"/>
+      <c r="AE1049" s="10" t="n"/>
     </row>
     <row r="1050">
-      <c r="Z1050" s="10" t="n"/>
+      <c r="AD1050" s="10" t="n"/>
+      <c r="AE1050" s="10" t="n"/>
     </row>
     <row r="1051">
-      <c r="Z1051" s="10" t="n"/>
+      <c r="AD1051" s="10" t="n"/>
+      <c r="AE1051" s="10" t="n"/>
     </row>
     <row r="1052">
-      <c r="Z1052" s="10" t="n"/>
+      <c r="AD1052" s="10" t="n"/>
+      <c r="AE1052" s="10" t="n"/>
     </row>
     <row r="1053">
-      <c r="Z1053" s="10" t="n"/>
+      <c r="AD1053" s="10" t="n"/>
+      <c r="AE1053" s="10" t="n"/>
     </row>
     <row r="1054">
-      <c r="Z1054" s="10" t="n"/>
+      <c r="AD1054" s="10" t="n"/>
+      <c r="AE1054" s="10" t="n"/>
     </row>
     <row r="1055">
-      <c r="Z1055" s="10" t="n"/>
+      <c r="AD1055" s="10" t="n"/>
+      <c r="AE1055" s="10" t="n"/>
     </row>
     <row r="1056">
-      <c r="Z1056" s="10" t="n"/>
+      <c r="AD1056" s="10" t="n"/>
+      <c r="AE1056" s="10" t="n"/>
     </row>
     <row r="1057">
-      <c r="Z1057" s="10" t="n"/>
+      <c r="AD1057" s="10" t="n"/>
+      <c r="AE1057" s="10" t="n"/>
     </row>
     <row r="1058">
-      <c r="Z1058" s="10" t="n"/>
+      <c r="AD1058" s="10" t="n"/>
+      <c r="AE1058" s="10" t="n"/>
     </row>
     <row r="1059">
-      <c r="Z1059" s="10" t="n"/>
+      <c r="AD1059" s="10" t="n"/>
+      <c r="AE1059" s="10" t="n"/>
     </row>
     <row r="1060">
-      <c r="Z1060" s="10" t="n"/>
+      <c r="AD1060" s="10" t="n"/>
+      <c r="AE1060" s="10" t="n"/>
     </row>
     <row r="1061">
-      <c r="Z1061" s="10" t="n"/>
+      <c r="AD1061" s="10" t="n"/>
+      <c r="AE1061" s="10" t="n"/>
     </row>
     <row r="1062">
-      <c r="Z1062" s="10" t="n"/>
+      <c r="AD1062" s="10" t="n"/>
+      <c r="AE1062" s="10" t="n"/>
     </row>
     <row r="1063">
-      <c r="Z1063" s="10" t="n"/>
+      <c r="AD1063" s="10" t="n"/>
+      <c r="AE1063" s="10" t="n"/>
     </row>
     <row r="1064">
-      <c r="Z1064" s="10" t="n"/>
+      <c r="AD1064" s="10" t="n"/>
+      <c r="AE1064" s="10" t="n"/>
     </row>
     <row r="1065">
-      <c r="Z1065" s="10" t="n"/>
+      <c r="AD1065" s="10" t="n"/>
+      <c r="AE1065" s="10" t="n"/>
     </row>
     <row r="1066">
-      <c r="Z1066" s="10" t="n"/>
+      <c r="AD1066" s="10" t="n"/>
+      <c r="AE1066" s="10" t="n"/>
     </row>
     <row r="1067">
-      <c r="Z1067" s="10" t="n"/>
+      <c r="AD1067" s="10" t="n"/>
+      <c r="AE1067" s="10" t="n"/>
     </row>
     <row r="1068">
-      <c r="Z1068" s="10" t="n"/>
+      <c r="AD1068" s="10" t="n"/>
+      <c r="AE1068" s="10" t="n"/>
     </row>
     <row r="1069">
-      <c r="Z1069" s="10" t="n"/>
+      <c r="AD1069" s="10" t="n"/>
+      <c r="AE1069" s="10" t="n"/>
     </row>
     <row r="1070">
-      <c r="Z1070" s="10" t="n"/>
+      <c r="AD1070" s="10" t="n"/>
+      <c r="AE1070" s="10" t="n"/>
     </row>
     <row r="1071">
-      <c r="Z1071" s="10" t="n"/>
+      <c r="AD1071" s="10" t="n"/>
+      <c r="AE1071" s="10" t="n"/>
     </row>
     <row r="1072">
-      <c r="Z1072" s="10" t="n"/>
+      <c r="AD1072" s="10" t="n"/>
+      <c r="AE1072" s="10" t="n"/>
     </row>
     <row r="1073">
-      <c r="Z1073" s="10" t="n"/>
+      <c r="AD1073" s="10" t="n"/>
+      <c r="AE1073" s="10" t="n"/>
     </row>
     <row r="1074">
-      <c r="Z1074" s="10" t="n"/>
+      <c r="AD1074" s="10" t="n"/>
+      <c r="AE1074" s="10" t="n"/>
     </row>
     <row r="1075">
-      <c r="Z1075" s="10" t="n"/>
+      <c r="AD1075" s="10" t="n"/>
+      <c r="AE1075" s="10" t="n"/>
     </row>
     <row r="1076">
-      <c r="Z1076" s="10" t="n"/>
+      <c r="AD1076" s="10" t="n"/>
+      <c r="AE1076" s="10" t="n"/>
     </row>
     <row r="1077">
-      <c r="Z1077" s="10" t="n"/>
+      <c r="AD1077" s="10" t="n"/>
+      <c r="AE1077" s="10" t="n"/>
     </row>
     <row r="1078">
-      <c r="Z1078" s="10" t="n"/>
+      <c r="AD1078" s="10" t="n"/>
+      <c r="AE1078" s="10" t="n"/>
     </row>
     <row r="1079">
-      <c r="Z1079" s="10" t="n"/>
+      <c r="AD1079" s="10" t="n"/>
+      <c r="AE1079" s="10" t="n"/>
     </row>
     <row r="1080">
-      <c r="Z1080" s="10" t="n"/>
+      <c r="AD1080" s="10" t="n"/>
+      <c r="AE1080" s="10" t="n"/>
     </row>
     <row r="1081">
-      <c r="Z1081" s="10" t="n"/>
+      <c r="AD1081" s="10" t="n"/>
+      <c r="AE1081" s="10" t="n"/>
     </row>
     <row r="1082">
-      <c r="Z1082" s="10" t="n"/>
+      <c r="AD1082" s="10" t="n"/>
+      <c r="AE1082" s="10" t="n"/>
     </row>
     <row r="1083">
-      <c r="Z1083" s="10" t="n"/>
+      <c r="AD1083" s="10" t="n"/>
+      <c r="AE1083" s="10" t="n"/>
     </row>
     <row r="1084">
-      <c r="Z1084" s="10" t="n"/>
+      <c r="AD1084" s="10" t="n"/>
+      <c r="AE1084" s="10" t="n"/>
     </row>
     <row r="1085">
-      <c r="Z1085" s="10" t="n"/>
+      <c r="AD1085" s="10" t="n"/>
+      <c r="AE1085" s="10" t="n"/>
     </row>
     <row r="1086">
-      <c r="Z1086" s="10" t="n"/>
+      <c r="AD1086" s="10" t="n"/>
+      <c r="AE1086" s="10" t="n"/>
     </row>
     <row r="1087">
-      <c r="Z1087" s="10" t="n"/>
+      <c r="AD1087" s="10" t="n"/>
+      <c r="AE1087" s="10" t="n"/>
     </row>
     <row r="1088">
-      <c r="Z1088" s="10" t="n"/>
+      <c r="AD1088" s="10" t="n"/>
+      <c r="AE1088" s="10" t="n"/>
     </row>
     <row r="1089">
-      <c r="Z1089" s="10" t="n"/>
+      <c r="AD1089" s="10" t="n"/>
+      <c r="AE1089" s="10" t="n"/>
     </row>
     <row r="1090">
-      <c r="Z1090" s="10" t="n"/>
+      <c r="AD1090" s="10" t="n"/>
+      <c r="AE1090" s="10" t="n"/>
     </row>
     <row r="1091">
-      <c r="Z1091" s="10" t="n"/>
+      <c r="AD1091" s="10" t="n"/>
+      <c r="AE1091" s="10" t="n"/>
     </row>
     <row r="1092">
-      <c r="Z1092" s="10" t="n"/>
+      <c r="AD1092" s="10" t="n"/>
+      <c r="AE1092" s="10" t="n"/>
     </row>
     <row r="1093">
-      <c r="Z1093" s="10" t="n"/>
+      <c r="AD1093" s="10" t="n"/>
+      <c r="AE1093" s="10" t="n"/>
     </row>
     <row r="1094">
-      <c r="Z1094" s="10" t="n"/>
+      <c r="AD1094" s="10" t="n"/>
+      <c r="AE1094" s="10" t="n"/>
     </row>
     <row r="1095">
-      <c r="Z1095" s="10" t="n"/>
+      <c r="AD1095" s="10" t="n"/>
+      <c r="AE1095" s="10" t="n"/>
     </row>
     <row r="1096">
-      <c r="Z1096" s="10" t="n"/>
+      <c r="AD1096" s="10" t="n"/>
+      <c r="AE1096" s="10" t="n"/>
     </row>
     <row r="1097">
-      <c r="Z1097" s="10" t="n"/>
+      <c r="AD1097" s="10" t="n"/>
+      <c r="AE1097" s="10" t="n"/>
     </row>
     <row r="1098">
-      <c r="Z1098" s="10" t="n"/>
+      <c r="AD1098" s="10" t="n"/>
+      <c r="AE1098" s="10" t="n"/>
     </row>
     <row r="1099">
-      <c r="Z1099" s="10" t="n"/>
+      <c r="AD1099" s="10" t="n"/>
+      <c r="AE1099" s="10" t="n"/>
     </row>
     <row r="1100">
-      <c r="Z1100" s="10" t="n"/>
+      <c r="AD1100" s="10" t="n"/>
+      <c r="AE1100" s="10" t="n"/>
     </row>
     <row r="1101">
-      <c r="Z1101" s="10" t="n"/>
+      <c r="AD1101" s="10" t="n"/>
+      <c r="AE1101" s="10" t="n"/>
     </row>
     <row r="1102">
-      <c r="Z1102" s="10" t="n"/>
+      <c r="AD1102" s="10" t="n"/>
+      <c r="AE1102" s="10" t="n"/>
     </row>
     <row r="1103">
-      <c r="Z1103" s="10" t="n"/>
+      <c r="AD1103" s="10" t="n"/>
+      <c r="AE1103" s="10" t="n"/>
     </row>
     <row r="1104">
-      <c r="Z1104" s="10" t="n"/>
+      <c r="AD1104" s="10" t="n"/>
+      <c r="AE1104" s="10" t="n"/>
     </row>
     <row r="1105">
-      <c r="Z1105" s="10" t="n"/>
+      <c r="AD1105" s="10" t="n"/>
+      <c r="AE1105" s="10" t="n"/>
     </row>
     <row r="1106">
-      <c r="Z1106" s="10" t="n"/>
+      <c r="AD1106" s="10" t="n"/>
+      <c r="AE1106" s="10" t="n"/>
     </row>
     <row r="1107">
-      <c r="Z1107" s="10" t="n"/>
+      <c r="AD1107" s="10" t="n"/>
+      <c r="AE1107" s="10" t="n"/>
     </row>
     <row r="1108">
-      <c r="Z1108" s="10" t="n"/>
+      <c r="AD1108" s="10" t="n"/>
+      <c r="AE1108" s="10" t="n"/>
     </row>
     <row r="1109">
-      <c r="Z1109" s="10" t="n"/>
+      <c r="AD1109" s="10" t="n"/>
+      <c r="AE1109" s="10" t="n"/>
     </row>
     <row r="1110">
-      <c r="Z1110" s="10" t="n"/>
+      <c r="AD1110" s="10" t="n"/>
+      <c r="AE1110" s="10" t="n"/>
     </row>
     <row r="1111">
-      <c r="Z1111" s="10" t="n"/>
+      <c r="AD1111" s="10" t="n"/>
+      <c r="AE1111" s="10" t="n"/>
     </row>
     <row r="1112">
-      <c r="Z1112" s="10" t="n"/>
+      <c r="AD1112" s="10" t="n"/>
+      <c r="AE1112" s="10" t="n"/>
     </row>
     <row r="1113">
-      <c r="Z1113" s="10" t="n"/>
+      <c r="AD1113" s="10" t="n"/>
+      <c r="AE1113" s="10" t="n"/>
     </row>
     <row r="1114">
-      <c r="Z1114" s="10" t="n"/>
+      <c r="AD1114" s="10" t="n"/>
+      <c r="AE1114" s="10" t="n"/>
     </row>
     <row r="1115">
-      <c r="Z1115" s="10" t="n"/>
+      <c r="AD1115" s="10" t="n"/>
+      <c r="AE1115" s="10" t="n"/>
     </row>
     <row r="1116">
-      <c r="Z1116" s="10" t="n"/>
+      <c r="AD1116" s="10" t="n"/>
+      <c r="AE1116" s="10" t="n"/>
     </row>
     <row r="1117">
-      <c r="Z1117" s="10" t="n"/>
+      <c r="AD1117" s="10" t="n"/>
+      <c r="AE1117" s="10" t="n"/>
     </row>
     <row r="1118">
-      <c r="Z1118" s="10" t="n"/>
+      <c r="AD1118" s="10" t="n"/>
+      <c r="AE1118" s="10" t="n"/>
     </row>
     <row r="1119">
-      <c r="Z1119" s="10" t="n"/>
+      <c r="AD1119" s="10" t="n"/>
+      <c r="AE1119" s="10" t="n"/>
     </row>
     <row r="1120">
-      <c r="Z1120" s="10" t="n"/>
+      <c r="AD1120" s="10" t="n"/>
+      <c r="AE1120" s="10" t="n"/>
     </row>
     <row r="1121">
-      <c r="Z1121" s="10" t="n"/>
+      <c r="AD1121" s="10" t="n"/>
+      <c r="AE1121" s="10" t="n"/>
     </row>
     <row r="1122">
-      <c r="Z1122" s="10" t="n"/>
+      <c r="AD1122" s="10" t="n"/>
+      <c r="AE1122" s="10" t="n"/>
     </row>
     <row r="1123">
-      <c r="Z1123" s="10" t="n"/>
+      <c r="AD1123" s="10" t="n"/>
+      <c r="AE1123" s="10" t="n"/>
     </row>
     <row r="1124">
-      <c r="Z1124" s="10" t="n"/>
+      <c r="AD1124" s="10" t="n"/>
+      <c r="AE1124" s="10" t="n"/>
     </row>
     <row r="1125">
-      <c r="Z1125" s="10" t="n"/>
+      <c r="AD1125" s="10" t="n"/>
+      <c r="AE1125" s="10" t="n"/>
     </row>
     <row r="1126">
-      <c r="Z1126" s="10" t="n"/>
+      <c r="AD1126" s="10" t="n"/>
+      <c r="AE1126" s="10" t="n"/>
     </row>
     <row r="1127">
-      <c r="Z1127" s="10" t="n"/>
+      <c r="AD1127" s="10" t="n"/>
+      <c r="AE1127" s="10" t="n"/>
     </row>
     <row r="1128">
-      <c r="Z1128" s="10" t="n"/>
+      <c r="AD1128" s="10" t="n"/>
+      <c r="AE1128" s="10" t="n"/>
     </row>
     <row r="1129">
-      <c r="Z1129" s="10" t="n"/>
+      <c r="AD1129" s="10" t="n"/>
+      <c r="AE1129" s="10" t="n"/>
     </row>
     <row r="1130">
-      <c r="Z1130" s="10" t="n"/>
+      <c r="AD1130" s="10" t="n"/>
+      <c r="AE1130" s="10" t="n"/>
     </row>
     <row r="1131">
-      <c r="Z1131" s="10" t="n"/>
+      <c r="AD1131" s="10" t="n"/>
+      <c r="AE1131" s="10" t="n"/>
     </row>
     <row r="1132">
-      <c r="Z1132" s="10" t="n"/>
+      <c r="AD1132" s="10" t="n"/>
+      <c r="AE1132" s="10" t="n"/>
     </row>
     <row r="1133">
-      <c r="Z1133" s="10" t="n"/>
+      <c r="AD1133" s="10" t="n"/>
+      <c r="AE1133" s="10" t="n"/>
     </row>
     <row r="1134">
-      <c r="Z1134" s="10" t="n"/>
+      <c r="AD1134" s="10" t="n"/>
+      <c r="AE1134" s="10" t="n"/>
     </row>
     <row r="1135">
-      <c r="Z1135" s="10" t="n"/>
+      <c r="AD1135" s="10" t="n"/>
+      <c r="AE1135" s="10" t="n"/>
     </row>
     <row r="1136">
-      <c r="Z1136" s="10" t="n"/>
+      <c r="AD1136" s="10" t="n"/>
+      <c r="AE1136" s="10" t="n"/>
     </row>
     <row r="1137">
-      <c r="Z1137" s="10" t="n"/>
+      <c r="AD1137" s="10" t="n"/>
+      <c r="AE1137" s="10" t="n"/>
     </row>
     <row r="1138">
-      <c r="Z1138" s="10" t="n"/>
+      <c r="AD1138" s="10" t="n"/>
+      <c r="AE1138" s="10" t="n"/>
     </row>
     <row r="1139">
-      <c r="Z1139" s="10" t="n"/>
+      <c r="AD1139" s="10" t="n"/>
+      <c r="AE1139" s="10" t="n"/>
     </row>
     <row r="1140">
-      <c r="Z1140" s="10" t="n"/>
+      <c r="AD1140" s="10" t="n"/>
+      <c r="AE1140" s="10" t="n"/>
     </row>
     <row r="1141">
-      <c r="Z1141" s="10" t="n"/>
+      <c r="AD1141" s="10" t="n"/>
+      <c r="AE1141" s="10" t="n"/>
     </row>
     <row r="1142">
-      <c r="Z1142" s="10" t="n"/>
+      <c r="AD1142" s="10" t="n"/>
+      <c r="AE1142" s="10" t="n"/>
     </row>
     <row r="1143">
-      <c r="Z1143" s="10" t="n"/>
+      <c r="AD1143" s="10" t="n"/>
+      <c r="AE1143" s="10" t="n"/>
     </row>
     <row r="1144">
-      <c r="Z1144" s="10" t="n"/>
+      <c r="AD1144" s="10" t="n"/>
+      <c r="AE1144" s="10" t="n"/>
     </row>
     <row r="1145">
-      <c r="Z1145" s="10" t="n"/>
+      <c r="AD1145" s="10" t="n"/>
+      <c r="AE1145" s="10" t="n"/>
     </row>
     <row r="1146">
-      <c r="Z1146" s="10" t="n"/>
+      <c r="AD1146" s="10" t="n"/>
+      <c r="AE1146" s="10" t="n"/>
     </row>
     <row r="1147">
-      <c r="Z1147" s="10" t="n"/>
+      <c r="AD1147" s="10" t="n"/>
+      <c r="AE1147" s="10" t="n"/>
     </row>
     <row r="1148">
-      <c r="Z1148" s="10" t="n"/>
+      <c r="AD1148" s="10" t="n"/>
+      <c r="AE1148" s="10" t="n"/>
     </row>
     <row r="1149">
-      <c r="Z1149" s="10" t="n"/>
+      <c r="AD1149" s="10" t="n"/>
+      <c r="AE1149" s="10" t="n"/>
     </row>
     <row r="1150">
-      <c r="Z1150" s="10" t="n"/>
+      <c r="AD1150" s="10" t="n"/>
+      <c r="AE1150" s="10" t="n"/>
     </row>
     <row r="1151">
-      <c r="Z1151" s="10" t="n"/>
+      <c r="AD1151" s="10" t="n"/>
+      <c r="AE1151" s="10" t="n"/>
     </row>
     <row r="1152">
-      <c r="Z1152" s="10" t="n"/>
+      <c r="AD1152" s="10" t="n"/>
+      <c r="AE1152" s="10" t="n"/>
     </row>
     <row r="1153">
-      <c r="Z1153" s="10" t="n"/>
+      <c r="AD1153" s="10" t="n"/>
+      <c r="AE1153" s="10" t="n"/>
     </row>
     <row r="1154">
-      <c r="Z1154" s="10" t="n"/>
+      <c r="AD1154" s="10" t="n"/>
+      <c r="AE1154" s="10" t="n"/>
     </row>
     <row r="1155">
-      <c r="Z1155" s="10" t="n"/>
+      <c r="AD1155" s="10" t="n"/>
+      <c r="AE1155" s="10" t="n"/>
     </row>
     <row r="1156">
-      <c r="Z1156" s="10" t="n"/>
+      <c r="AD1156" s="10" t="n"/>
+      <c r="AE1156" s="10" t="n"/>
     </row>
     <row r="1157">
-      <c r="Z1157" s="10" t="n"/>
+      <c r="AD1157" s="10" t="n"/>
+      <c r="AE1157" s="10" t="n"/>
     </row>
     <row r="1158">
-      <c r="Z1158" s="10" t="n"/>
+      <c r="AD1158" s="10" t="n"/>
+      <c r="AE1158" s="10" t="n"/>
     </row>
     <row r="1159">
-      <c r="Z1159" s="10" t="n"/>
+      <c r="AD1159" s="10" t="n"/>
+      <c r="AE1159" s="10" t="n"/>
     </row>
     <row r="1160">
-      <c r="Z1160" s="10" t="n"/>
+      <c r="AD1160" s="10" t="n"/>
+      <c r="AE1160" s="10" t="n"/>
     </row>
     <row r="1161">
-      <c r="Z1161" s="10" t="n"/>
+      <c r="AD1161" s="10" t="n"/>
+      <c r="AE1161" s="10" t="n"/>
     </row>
     <row r="1162">
-      <c r="Z1162" s="10" t="n"/>
+      <c r="AD1162" s="10" t="n"/>
+      <c r="AE1162" s="10" t="n"/>
     </row>
     <row r="1163">
-      <c r="Z1163" s="10" t="n"/>
+      <c r="AD1163" s="10" t="n"/>
+      <c r="AE1163" s="10" t="n"/>
     </row>
     <row r="1164">
-      <c r="Z1164" s="10" t="n"/>
+      <c r="AD1164" s="10" t="n"/>
+      <c r="AE1164" s="10" t="n"/>
     </row>
     <row r="1165">
-      <c r="Z1165" s="10" t="n"/>
+      <c r="AD1165" s="10" t="n"/>
+      <c r="AE1165" s="10" t="n"/>
     </row>
     <row r="1166">
-      <c r="Z1166" s="10" t="n"/>
+      <c r="AD1166" s="10" t="n"/>
+      <c r="AE1166" s="10" t="n"/>
     </row>
     <row r="1167">
-      <c r="Z1167" s="10" t="n"/>
+      <c r="AD1167" s="10" t="n"/>
+      <c r="AE1167" s="10" t="n"/>
     </row>
     <row r="1168">
-      <c r="Z1168" s="10" t="n"/>
+      <c r="AD1168" s="10" t="n"/>
+      <c r="AE1168" s="10" t="n"/>
     </row>
     <row r="1169">
-      <c r="Z1169" s="10" t="n"/>
+      <c r="AD1169" s="10" t="n"/>
+      <c r="AE1169" s="10" t="n"/>
     </row>
     <row r="1170">
-      <c r="Z1170" s="10" t="n"/>
+      <c r="AD1170" s="10" t="n"/>
+      <c r="AE1170" s="10" t="n"/>
     </row>
     <row r="1171">
-      <c r="Z1171" s="10" t="n"/>
+      <c r="AD1171" s="10" t="n"/>
+      <c r="AE1171" s="10" t="n"/>
     </row>
     <row r="1172">
-      <c r="Z1172" s="10" t="n"/>
+      <c r="AD1172" s="10" t="n"/>
+      <c r="AE1172" s="10" t="n"/>
     </row>
     <row r="1173">
-      <c r="Z1173" s="10" t="n"/>
+      <c r="AD1173" s="10" t="n"/>
+      <c r="AE1173" s="10" t="n"/>
     </row>
     <row r="1174">
-      <c r="Z1174" s="10" t="n"/>
+      <c r="AD1174" s="10" t="n"/>
+      <c r="AE1174" s="10" t="n"/>
     </row>
     <row r="1175">
-      <c r="Z1175" s="10" t="n"/>
+      <c r="AD1175" s="10" t="n"/>
+      <c r="AE1175" s="10" t="n"/>
     </row>
     <row r="1176">
-      <c r="Z1176" s="10" t="n"/>
+      <c r="AD1176" s="10" t="n"/>
+      <c r="AE1176" s="10" t="n"/>
     </row>
     <row r="1177">
-      <c r="Z1177" s="10" t="n"/>
+      <c r="AD1177" s="10" t="n"/>
+      <c r="AE1177" s="10" t="n"/>
     </row>
     <row r="1178">
-      <c r="Z1178" s="10" t="n"/>
+      <c r="AD1178" s="10" t="n"/>
+      <c r="AE1178" s="10" t="n"/>
     </row>
     <row r="1179">
-      <c r="Z1179" s="10" t="n"/>
+      <c r="AD1179" s="10" t="n"/>
+      <c r="AE1179" s="10" t="n"/>
     </row>
     <row r="1180">
-      <c r="Z1180" s="10" t="n"/>
+      <c r="AD1180" s="10" t="n"/>
+      <c r="AE1180" s="10" t="n"/>
     </row>
     <row r="1181">
-      <c r="Z1181" s="10" t="n"/>
+      <c r="AD1181" s="10" t="n"/>
+      <c r="AE1181" s="10" t="n"/>
     </row>
     <row r="1182">
-      <c r="Z1182" s="10" t="n"/>
+      <c r="AD1182" s="10" t="n"/>
+      <c r="AE1182" s="10" t="n"/>
     </row>
     <row r="1183">
-      <c r="Z1183" s="10" t="n"/>
+      <c r="AD1183" s="10" t="n"/>
+      <c r="AE1183" s="10" t="n"/>
     </row>
     <row r="1184">
-      <c r="Z1184" s="10" t="n"/>
+      <c r="AD1184" s="10" t="n"/>
+      <c r="AE1184" s="10" t="n"/>
     </row>
     <row r="1185">
-      <c r="Z1185" s="10" t="n"/>
+      <c r="AD1185" s="10" t="n"/>
+      <c r="AE1185" s="10" t="n"/>
     </row>
     <row r="1186">
-      <c r="Z1186" s="10" t="n"/>
+      <c r="AD1186" s="10" t="n"/>
+      <c r="AE1186" s="10" t="n"/>
     </row>
     <row r="1187">
-      <c r="Z1187" s="10" t="n"/>
+      <c r="AD1187" s="10" t="n"/>
+      <c r="AE1187" s="10" t="n"/>
     </row>
     <row r="1188">
-      <c r="Z1188" s="10" t="n"/>
+      <c r="AD1188" s="10" t="n"/>
+      <c r="AE1188" s="10" t="n"/>
     </row>
     <row r="1189">
-      <c r="Z1189" s="10" t="n"/>
+      <c r="AD1189" s="10" t="n"/>
+      <c r="AE1189" s="10" t="n"/>
     </row>
     <row r="1190">
-      <c r="Z1190" s="10" t="n"/>
+      <c r="AD1190" s="10" t="n"/>
+      <c r="AE1190" s="10" t="n"/>
     </row>
     <row r="1191">
-      <c r="Z1191" s="10" t="n"/>
+      <c r="AD1191" s="10" t="n"/>
+      <c r="AE1191" s="10" t="n"/>
     </row>
     <row r="1192">
-      <c r="Z1192" s="10" t="n"/>
+      <c r="AD1192" s="10" t="n"/>
+      <c r="AE1192" s="10" t="n"/>
     </row>
     <row r="1193">
-      <c r="Z1193" s="10" t="n"/>
+      <c r="AD1193" s="10" t="n"/>
+      <c r="AE1193" s="10" t="n"/>
     </row>
     <row r="1194">
-      <c r="Z1194" s="10" t="n"/>
+      <c r="AD1194" s="10" t="n"/>
+      <c r="AE1194" s="10" t="n"/>
     </row>
     <row r="1195">
-      <c r="Z1195" s="10" t="n"/>
+      <c r="AD1195" s="10" t="n"/>
+      <c r="AE1195" s="10" t="n"/>
     </row>
     <row r="1196">
-      <c r="Z1196" s="10" t="n"/>
+      <c r="AD1196" s="10" t="n"/>
+      <c r="AE1196" s="10" t="n"/>
     </row>
     <row r="1197">
-      <c r="Z1197" s="10" t="n"/>
+      <c r="AD1197" s="10" t="n"/>
+      <c r="AE1197" s="10" t="n"/>
     </row>
     <row r="1198">
-      <c r="Z1198" s="10" t="n"/>
+      <c r="AD1198" s="10" t="n"/>
+      <c r="AE1198" s="10" t="n"/>
     </row>
     <row r="1199">
-      <c r="Z1199" s="10" t="n"/>
+      <c r="AD1199" s="10" t="n"/>
+      <c r="AE1199" s="10" t="n"/>
     </row>
     <row r="1200">
-      <c r="Z1200" s="10" t="n"/>
+      <c r="AD1200" s="10" t="n"/>
+      <c r="AE1200" s="10" t="n"/>
     </row>
     <row r="1201">
-      <c r="Z1201" s="10" t="n"/>
+      <c r="AD1201" s="10" t="n"/>
+      <c r="AE1201" s="10" t="n"/>
     </row>
     <row r="1202">
-      <c r="Z1202" s="10" t="n"/>
+      <c r="AD1202" s="10" t="n"/>
+      <c r="AE1202" s="10" t="n"/>
     </row>
     <row r="1203">
-      <c r="Z1203" s="10" t="n"/>
+      <c r="AD1203" s="10" t="n"/>
+      <c r="AE1203" s="10" t="n"/>
     </row>
     <row r="1204">
-      <c r="Z1204" s="10" t="n"/>
+      <c r="AD1204" s="10" t="n"/>
+      <c r="AE1204" s="10" t="n"/>
     </row>
     <row r="1205">
-      <c r="Z1205" s="10" t="n"/>
+      <c r="AD1205" s="10" t="n"/>
+      <c r="AE1205" s="10" t="n"/>
     </row>
     <row r="1206">
-      <c r="Z1206" s="10" t="n"/>
+      <c r="AD1206" s="10" t="n"/>
+      <c r="AE1206" s="10" t="n"/>
     </row>
     <row r="1207">
-      <c r="Z1207" s="10" t="n"/>
+      <c r="AD1207" s="10" t="n"/>
+      <c r="AE1207" s="10" t="n"/>
     </row>
     <row r="1208">
-      <c r="Z1208" s="10" t="n"/>
+      <c r="AD1208" s="10" t="n"/>
+      <c r="AE1208" s="10" t="n"/>
     </row>
     <row r="1209">
-      <c r="Z1209" s="10" t="n"/>
+      <c r="AD1209" s="10" t="n"/>
+      <c r="AE1209" s="10" t="n"/>
     </row>
     <row r="1210">
-      <c r="Z1210" s="10" t="n"/>
+      <c r="AD1210" s="10" t="n"/>
+      <c r="AE1210" s="10" t="n"/>
     </row>
     <row r="1211">
-      <c r="Z1211" s="10" t="n"/>
+      <c r="AD1211" s="10" t="n"/>
+      <c r="AE1211" s="10" t="n"/>
     </row>
     <row r="1212">
-      <c r="Z1212" s="10" t="n"/>
+      <c r="AD1212" s="10" t="n"/>
+      <c r="AE1212" s="10" t="n"/>
     </row>
     <row r="1213">
-      <c r="Z1213" s="10" t="n"/>
+      <c r="AD1213" s="10" t="n"/>
+      <c r="AE1213" s="10" t="n"/>
     </row>
     <row r="1214">
-      <c r="Z1214" s="10" t="n"/>
+      <c r="AD1214" s="10" t="n"/>
+      <c r="AE1214" s="10" t="n"/>
     </row>
     <row r="1215">
-      <c r="Z1215" s="10" t="n"/>
+      <c r="AD1215" s="10" t="n"/>
+      <c r="AE1215" s="10" t="n"/>
     </row>
     <row r="1216">
-      <c r="Z1216" s="10" t="n"/>
+      <c r="AD1216" s="10" t="n"/>
+      <c r="AE1216" s="10" t="n"/>
     </row>
     <row r="1217">
-      <c r="Z1217" s="10" t="n"/>
+      <c r="AD1217" s="10" t="n"/>
+      <c r="AE1217" s="10" t="n"/>
     </row>
     <row r="1218">
-      <c r="Z1218" s="10" t="n"/>
+      <c r="AD1218" s="10" t="n"/>
+      <c r="AE1218" s="10" t="n"/>
     </row>
     <row r="1219">
-      <c r="Z1219" s="10" t="n"/>
+      <c r="AD1219" s="10" t="n"/>
+      <c r="AE1219" s="10" t="n"/>
     </row>
     <row r="1220">
-      <c r="Z1220" s="10" t="n"/>
+      <c r="AD1220" s="10" t="n"/>
+      <c r="AE1220" s="10" t="n"/>
     </row>
     <row r="1221">
-      <c r="Z1221" s="10" t="n"/>
+      <c r="AD1221" s="10" t="n"/>
+      <c r="AE1221" s="10" t="n"/>
     </row>
     <row r="1222">
-      <c r="Z1222" s="10" t="n"/>
+      <c r="AD1222" s="10" t="n"/>
+      <c r="AE1222" s="10" t="n"/>
     </row>
     <row r="1223">
-      <c r="Z1223" s="10" t="n"/>
+      <c r="AD1223" s="10" t="n"/>
+      <c r="AE1223" s="10" t="n"/>
     </row>
     <row r="1224">
-      <c r="Z1224" s="10" t="n"/>
+      <c r="AD1224" s="10" t="n"/>
+      <c r="AE1224" s="10" t="n"/>
     </row>
     <row r="1225">
-      <c r="Z1225" s="10" t="n"/>
+      <c r="AD1225" s="10" t="n"/>
+      <c r="AE1225" s="10" t="n"/>
     </row>
     <row r="1226">
-      <c r="Z1226" s="10" t="n"/>
+      <c r="AD1226" s="10" t="n"/>
+      <c r="AE1226" s="10" t="n"/>
     </row>
     <row r="1227">
-      <c r="Z1227" s="10" t="n"/>
+      <c r="AD1227" s="10" t="n"/>
+      <c r="AE1227" s="10" t="n"/>
     </row>
     <row r="1228">
-      <c r="Z1228" s="10" t="n"/>
+      <c r="AD1228" s="10" t="n"/>
+      <c r="AE1228" s="10" t="n"/>
     </row>
     <row r="1229">
-      <c r="Z1229" s="10" t="n"/>
+      <c r="AD1229" s="10" t="n"/>
+      <c r="AE1229" s="10" t="n"/>
     </row>
     <row r="1230">
-      <c r="Z1230" s="10" t="n"/>
+      <c r="AD1230" s="10" t="n"/>
+      <c r="AE1230" s="10" t="n"/>
     </row>
     <row r="1231">
-      <c r="Z1231" s="10" t="n"/>
+      <c r="AD1231" s="10" t="n"/>
+      <c r="AE1231" s="10" t="n"/>
     </row>
     <row r="1232">
-      <c r="Z1232" s="10" t="n"/>
+      <c r="AD1232" s="10" t="n"/>
+      <c r="AE1232" s="10" t="n"/>
     </row>
     <row r="1233">
-      <c r="Z1233" s="10" t="n"/>
+      <c r="AD1233" s="10" t="n"/>
+      <c r="AE1233" s="10" t="n"/>
     </row>
     <row r="1234">
-      <c r="Z1234" s="10" t="n"/>
+      <c r="AD1234" s="10" t="n"/>
+      <c r="AE1234" s="10" t="n"/>
     </row>
     <row r="1235">
-      <c r="Z1235" s="10" t="n"/>
+      <c r="AD1235" s="10" t="n"/>
+      <c r="AE1235" s="10" t="n"/>
     </row>
     <row r="1236">
-      <c r="Z1236" s="10" t="n"/>
+      <c r="AD1236" s="10" t="n"/>
+      <c r="AE1236" s="10" t="n"/>
     </row>
     <row r="1237">
-      <c r="Z1237" s="10" t="n"/>
+      <c r="AD1237" s="10" t="n"/>
+      <c r="AE1237" s="10" t="n"/>
     </row>
     <row r="1238">
-      <c r="Z1238" s="10" t="n"/>
+      <c r="AD1238" s="10" t="n"/>
+      <c r="AE1238" s="10" t="n"/>
     </row>
     <row r="1239">
-      <c r="Z1239" s="10" t="n"/>
+      <c r="AD1239" s="10" t="n"/>
+      <c r="AE1239" s="10" t="n"/>
     </row>
     <row r="1240">
-      <c r="Z1240" s="10" t="n"/>
+      <c r="AD1240" s="10" t="n"/>
+      <c r="AE1240" s="10" t="n"/>
     </row>
     <row r="1241">
-      <c r="Z1241" s="10" t="n"/>
+      <c r="AD1241" s="10" t="n"/>
+      <c r="AE1241" s="10" t="n"/>
     </row>
     <row r="1242">
-      <c r="Z1242" s="10" t="n"/>
+      <c r="AD1242" s="10" t="n"/>
+      <c r="AE1242" s="10" t="n"/>
     </row>
     <row r="1243">
-      <c r="Z1243" s="10" t="n"/>
+      <c r="AD1243" s="10" t="n"/>
+      <c r="AE1243" s="10" t="n"/>
     </row>
     <row r="1244">
-      <c r="Z1244" s="10" t="n"/>
+      <c r="AD1244" s="10" t="n"/>
+      <c r="AE1244" s="10" t="n"/>
     </row>
     <row r="1245">
-      <c r="Z1245" s="10" t="n"/>
+      <c r="AD1245" s="10" t="n"/>
+      <c r="AE1245" s="10" t="n"/>
     </row>
     <row r="1246">
-      <c r="Z1246" s="10" t="n"/>
+      <c r="AD1246" s="10" t="n"/>
+      <c r="AE1246" s="10" t="n"/>
     </row>
     <row r="1247">
-      <c r="Z1247" s="10" t="n"/>
+      <c r="AD1247" s="10" t="n"/>
+      <c r="AE1247" s="10" t="n"/>
     </row>
     <row r="1248">
-      <c r="Z1248" s="10" t="n"/>
+      <c r="AD1248" s="10" t="n"/>
+      <c r="AE1248" s="10" t="n"/>
     </row>
     <row r="1249">
-      <c r="Z1249" s="10" t="n"/>
+      <c r="AD1249" s="10" t="n"/>
+      <c r="AE1249" s="10" t="n"/>
     </row>
     <row r="1250">
-      <c r="Z1250" s="10" t="n"/>
+      <c r="AD1250" s="10" t="n"/>
+      <c r="AE1250" s="10" t="n"/>
     </row>
     <row r="1251">
-      <c r="Z1251" s="10" t="n"/>
+      <c r="AD1251" s="10" t="n"/>
+      <c r="AE1251" s="10" t="n"/>
     </row>
     <row r="1252">
-      <c r="Z1252" s="10" t="n"/>
+      <c r="AD1252" s="10" t="n"/>
+      <c r="AE1252" s="10" t="n"/>
     </row>
     <row r="1253">
-      <c r="Z1253" s="10" t="n"/>
+      <c r="AD1253" s="10" t="n"/>
+      <c r="AE1253" s="10" t="n"/>
     </row>
     <row r="1254">
-      <c r="Z1254" s="10" t="n"/>
+      <c r="AD1254" s="10" t="n"/>
+      <c r="AE1254" s="10" t="n"/>
     </row>
     <row r="1255">
-      <c r="Z1255" s="10" t="n"/>
+      <c r="AD1255" s="10" t="n"/>
+      <c r="AE1255" s="10" t="n"/>
     </row>
     <row r="1256">
-      <c r="Z1256" s="10" t="n"/>
+      <c r="AD1256" s="10" t="n"/>
+      <c r="AE1256" s="10" t="n"/>
     </row>
     <row r="1257">
-      <c r="Z1257" s="10" t="n"/>
+      <c r="AD1257" s="10" t="n"/>
+      <c r="AE1257" s="10" t="n"/>
     </row>
     <row r="1258">
-      <c r="Z1258" s="10" t="n"/>
+      <c r="AD1258" s="10" t="n"/>
+      <c r="AE1258" s="10" t="n"/>
     </row>
     <row r="1259">
-      <c r="Z1259" s="10" t="n"/>
+      <c r="AD1259" s="10" t="n"/>
+      <c r="AE1259" s="10" t="n"/>
     </row>
     <row r="1260">
-      <c r="Z1260" s="10" t="n"/>
+      <c r="AD1260" s="10" t="n"/>
+      <c r="AE1260" s="10" t="n"/>
     </row>
     <row r="1261">
-      <c r="Z1261" s="10" t="n"/>
+      <c r="AD1261" s="10" t="n"/>
+      <c r="AE1261" s="10" t="n"/>
     </row>
     <row r="1262">
-      <c r="Z1262" s="10" t="n"/>
+      <c r="AD1262" s="10" t="n"/>
+      <c r="AE1262" s="10" t="n"/>
     </row>
     <row r="1263">
-      <c r="Z1263" s="10" t="n"/>
+      <c r="AD1263" s="10" t="n"/>
+      <c r="AE1263" s="10" t="n"/>
     </row>
     <row r="1264">
-      <c r="Z1264" s="10" t="n"/>
+      <c r="AD1264" s="10" t="n"/>
+      <c r="AE1264" s="10" t="n"/>
     </row>
     <row r="1265">
-      <c r="Z1265" s="10" t="n"/>
+      <c r="AD1265" s="10" t="n"/>
+      <c r="AE1265" s="10" t="n"/>
     </row>
     <row r="1266">
-      <c r="Z1266" s="10" t="n"/>
+      <c r="AD1266" s="10" t="n"/>
+      <c r="AE1266" s="10" t="n"/>
     </row>
     <row r="1267">
-      <c r="Z1267" s="10" t="n"/>
+      <c r="AD1267" s="10" t="n"/>
+      <c r="AE1267" s="10" t="n"/>
     </row>
     <row r="1268">
-      <c r="Z1268" s="10" t="n"/>
+      <c r="AD1268" s="10" t="n"/>
+      <c r="AE1268" s="10" t="n"/>
     </row>
     <row r="1269">
-      <c r="Z1269" s="10" t="n"/>
+      <c r="AD1269" s="10" t="n"/>
+      <c r="AE1269" s="10" t="n"/>
     </row>
     <row r="1270">
-      <c r="Z1270" s="10" t="n"/>
+      <c r="AD1270" s="10" t="n"/>
+      <c r="AE1270" s="10" t="n"/>
     </row>
     <row r="1271">
-      <c r="Z1271" s="10" t="n"/>
+      <c r="AD1271" s="10" t="n"/>
+      <c r="AE1271" s="10" t="n"/>
     </row>
     <row r="1272">
-      <c r="Z1272" s="10" t="n"/>
+      <c r="AD1272" s="10" t="n"/>
+      <c r="AE1272" s="10" t="n"/>
     </row>
     <row r="1273">
-      <c r="Z1273" s="10" t="n"/>
+      <c r="AD1273" s="10" t="n"/>
+      <c r="AE1273" s="10" t="n"/>
     </row>
     <row r="1274">
-      <c r="Z1274" s="10" t="n"/>
+      <c r="AD1274" s="10" t="n"/>
+      <c r="AE1274" s="10" t="n"/>
     </row>
     <row r="1275">
-      <c r="Z1275" s="10" t="n"/>
+      <c r="AD1275" s="10" t="n"/>
+      <c r="AE1275" s="10" t="n"/>
     </row>
     <row r="1276">
-      <c r="Z1276" s="10" t="n"/>
+      <c r="AD1276" s="10" t="n"/>
+      <c r="AE1276" s="10" t="n"/>
     </row>
     <row r="1277">
-      <c r="Z1277" s="10" t="n"/>
+      <c r="AD1277" s="10" t="n"/>
+      <c r="AE1277" s="10" t="n"/>
     </row>
     <row r="1278">
-      <c r="Z1278" s="10" t="n"/>
+      <c r="AD1278" s="10" t="n"/>
+      <c r="AE1278" s="10" t="n"/>
     </row>
     <row r="1279">
-      <c r="Z1279" s="10" t="n"/>
+      <c r="AD1279" s="10" t="n"/>
+      <c r="AE1279" s="10" t="n"/>
     </row>
     <row r="1280">
-      <c r="Z1280" s="10" t="n"/>
+      <c r="AD1280" s="10" t="n"/>
+      <c r="AE1280" s="10" t="n"/>
     </row>
     <row r="1281">
-      <c r="Z1281" s="10" t="n"/>
+      <c r="AD1281" s="10" t="n"/>
+      <c r="AE1281" s="10" t="n"/>
     </row>
     <row r="1282">
-      <c r="Z1282" s="10" t="n"/>
+      <c r="AD1282" s="10" t="n"/>
+      <c r="AE1282" s="10" t="n"/>
     </row>
     <row r="1283">
-      <c r="Z1283" s="10" t="n"/>
+      <c r="AD1283" s="10" t="n"/>
+      <c r="AE1283" s="10" t="n"/>
     </row>
     <row r="1284">
-      <c r="Z1284" s="10" t="n"/>
+      <c r="AD1284" s="10" t="n"/>
+      <c r="AE1284" s="10" t="n"/>
     </row>
     <row r="1285">
-      <c r="Z1285" s="10" t="n"/>
+      <c r="AD1285" s="10" t="n"/>
+      <c r="AE1285" s="10" t="n"/>
     </row>
     <row r="1286">
-      <c r="Z1286" s="10" t="n"/>
+      <c r="AD1286" s="10" t="n"/>
+      <c r="AE1286" s="10" t="n"/>
     </row>
     <row r="1287">
-      <c r="Z1287" s="10" t="n"/>
+      <c r="AD1287" s="10" t="n"/>
+      <c r="AE1287" s="10" t="n"/>
     </row>
     <row r="1288">
-      <c r="Z1288" s="10" t="n"/>
+      <c r="AD1288" s="10" t="n"/>
+      <c r="AE1288" s="10" t="n"/>
     </row>
     <row r="1289">
-      <c r="Z1289" s="10" t="n"/>
+      <c r="AD1289" s="10" t="n"/>
+      <c r="AE1289" s="10" t="n"/>
     </row>
     <row r="1290">
-      <c r="Z1290" s="10" t="n"/>
+      <c r="AD1290" s="10" t="n"/>
+      <c r="AE1290" s="10" t="n"/>
     </row>
     <row r="1291">
-      <c r="Z1291" s="10" t="n"/>
+      <c r="AD1291" s="10" t="n"/>
+      <c r="AE1291" s="10" t="n"/>
     </row>
     <row r="1292">
-      <c r="Z1292" s="10" t="n"/>
+      <c r="AD1292" s="10" t="n"/>
+      <c r="AE1292" s="10" t="n"/>
     </row>
     <row r="1293">
-      <c r="Z1293" s="10" t="n"/>
+      <c r="AD1293" s="10" t="n"/>
+      <c r="AE1293" s="10" t="n"/>
     </row>
     <row r="1294">
-      <c r="Z1294" s="10" t="n"/>
+      <c r="AD1294" s="10" t="n"/>
+      <c r="AE1294" s="10" t="n"/>
     </row>
     <row r="1295">
-      <c r="Z1295" s="10" t="n"/>
+      <c r="AD1295" s="10" t="n"/>
+      <c r="AE1295" s="10" t="n"/>
     </row>
     <row r="1296">
-      <c r="Z1296" s="10" t="n"/>
+      <c r="AD1296" s="10" t="n"/>
+      <c r="AE1296" s="10" t="n"/>
     </row>
     <row r="1297">
-      <c r="Z1297" s="10" t="n"/>
+      <c r="AD1297" s="10" t="n"/>
+      <c r="AE1297" s="10" t="n"/>
     </row>
     <row r="1298">
-      <c r="Z1298" s="10" t="n"/>
+      <c r="AD1298" s="10" t="n"/>
+      <c r="AE1298" s="10" t="n"/>
     </row>
     <row r="1299">
-      <c r="Z1299" s="10" t="n"/>
+      <c r="AD1299" s="10" t="n"/>
+      <c r="AE1299" s="10" t="n"/>
     </row>
     <row r="1300">
-      <c r="Z1300" s="10" t="n"/>
+      <c r="AD1300" s="10" t="n"/>
+      <c r="AE1300" s="10" t="n"/>
     </row>
     <row r="1301">
-      <c r="Z1301" s="10" t="n"/>
+      <c r="AD1301" s="10" t="n"/>
+      <c r="AE1301" s="10" t="n"/>
     </row>
     <row r="1302">
-      <c r="Z1302" s="10" t="n"/>
+      <c r="AD1302" s="10" t="n"/>
+      <c r="AE1302" s="10" t="n"/>
     </row>
     <row r="1303">
-      <c r="Z1303" s="10" t="n"/>
+      <c r="AD1303" s="10" t="n"/>
+      <c r="AE1303" s="10" t="n"/>
     </row>
     <row r="1304">
-      <c r="Z1304" s="10" t="n"/>
+      <c r="AD1304" s="10" t="n"/>
+      <c r="AE1304" s="10" t="n"/>
     </row>
     <row r="1305">
-      <c r="Z1305" s="10" t="n"/>
+      <c r="AD1305" s="10" t="n"/>
+      <c r="AE1305" s="10" t="n"/>
     </row>
     <row r="1306">
-      <c r="Z1306" s="10" t="n"/>
+      <c r="AD1306" s="10" t="n"/>
+      <c r="AE1306" s="10" t="n"/>
     </row>
     <row r="1307">
-      <c r="Z1307" s="10" t="n"/>
+      <c r="AD1307" s="10" t="n"/>
+      <c r="AE1307" s="10" t="n"/>
     </row>
     <row r="1308">
-      <c r="Z1308" s="10" t="n"/>
+      <c r="AD1308" s="10" t="n"/>
+      <c r="AE1308" s="10" t="n"/>
     </row>
     <row r="1309">
-      <c r="Z1309" s="10" t="n"/>
+      <c r="AD1309" s="10" t="n"/>
+      <c r="AE1309" s="10" t="n"/>
     </row>
     <row r="1310">
-      <c r="Z1310" s="10" t="n"/>
+      <c r="AD1310" s="10" t="n"/>
+      <c r="AE1310" s="10" t="n"/>
     </row>
     <row r="1311">
-      <c r="Z1311" s="10" t="n"/>
+      <c r="AD1311" s="10" t="n"/>
+      <c r="AE1311" s="10" t="n"/>
     </row>
     <row r="1312">
-      <c r="Z1312" s="10" t="n"/>
+      <c r="AD1312" s="10" t="n"/>
+      <c r="AE1312" s="10" t="n"/>
     </row>
     <row r="1313">
-      <c r="Z1313" s="10" t="n"/>
+      <c r="AD1313" s="10" t="n"/>
+      <c r="AE1313" s="10" t="n"/>
     </row>
     <row r="1314">
-      <c r="Z1314" s="10" t="n"/>
+      <c r="AD1314" s="10" t="n"/>
+      <c r="AE1314" s="10" t="n"/>
     </row>
     <row r="1315">
-      <c r="Z1315" s="10" t="n"/>
+      <c r="AD1315" s="10" t="n"/>
+      <c r="AE1315" s="10" t="n"/>
     </row>
     <row r="1316">
-      <c r="Z1316" s="10" t="n"/>
+      <c r="AD1316" s="10" t="n"/>
+      <c r="AE1316" s="10" t="n"/>
     </row>
     <row r="1317">
-      <c r="Z1317" s="10" t="n"/>
+      <c r="AD1317" s="10" t="n"/>
+      <c r="AE1317" s="10" t="n"/>
     </row>
     <row r="1318">
-      <c r="Z1318" s="10" t="n"/>
+      <c r="AD1318" s="10" t="n"/>
+      <c r="AE1318" s="10" t="n"/>
     </row>
     <row r="1319">
-      <c r="Z1319" s="10" t="n"/>
+      <c r="AD1319" s="10" t="n"/>
+      <c r="AE1319" s="10" t="n"/>
     </row>
     <row r="1320">
-      <c r="Z1320" s="10" t="n"/>
+      <c r="AD1320" s="10" t="n"/>
+      <c r="AE1320" s="10" t="n"/>
     </row>
     <row r="1321">
-      <c r="Z1321" s="10" t="n"/>
+      <c r="AD1321" s="10" t="n"/>
+      <c r="AE1321" s="10" t="n"/>
     </row>
     <row r="1322">
-      <c r="Z1322" s="10" t="n"/>
+      <c r="AD1322" s="10" t="n"/>
+      <c r="AE1322" s="10" t="n"/>
     </row>
     <row r="1323">
-      <c r="Z1323" s="10" t="n"/>
+      <c r="AD1323" s="10" t="n"/>
+      <c r="AE1323" s="10" t="n"/>
     </row>
     <row r="1324">
-      <c r="Z1324" s="10" t="n"/>
+      <c r="AD1324" s="10" t="n"/>
+      <c r="AE1324" s="10" t="n"/>
     </row>
     <row r="1325">
-      <c r="Z1325" s="10" t="n"/>
+      <c r="AD1325" s="10" t="n"/>
+      <c r="AE1325" s="10" t="n"/>
     </row>
     <row r="1326">
-      <c r="Z1326" s="10" t="n"/>
+      <c r="AD1326" s="10" t="n"/>
+      <c r="AE1326" s="10" t="n"/>
     </row>
     <row r="1327">
-      <c r="Z1327" s="10" t="n"/>
+      <c r="AD1327" s="10" t="n"/>
+      <c r="AE1327" s="10" t="n"/>
     </row>
     <row r="1328">
-      <c r="Z1328" s="10" t="n"/>
+      <c r="AD1328" s="10" t="n"/>
+      <c r="AE1328" s="10" t="n"/>
     </row>
     <row r="1329">
-      <c r="Z1329" s="10" t="n"/>
+      <c r="AD1329" s="10" t="n"/>
+      <c r="AE1329" s="10" t="n"/>
     </row>
     <row r="1330">
-      <c r="Z1330" s="10" t="n"/>
+      <c r="AD1330" s="10" t="n"/>
+      <c r="AE1330" s="10" t="n"/>
     </row>
     <row r="1331">
-      <c r="Z1331" s="10" t="n"/>
+      <c r="AD1331" s="10" t="n"/>
+      <c r="AE1331" s="10" t="n"/>
     </row>
     <row r="1332">
-      <c r="Z1332" s="10" t="n"/>
+      <c r="AD1332" s="10" t="n"/>
+      <c r="AE1332" s="10" t="n"/>
     </row>
     <row r="1333">
-      <c r="Z1333" s="10" t="n"/>
+      <c r="AD1333" s="10" t="n"/>
+      <c r="AE1333" s="10" t="n"/>
     </row>
     <row r="1334">
-      <c r="Z1334" s="10" t="n"/>
+      <c r="AD1334" s="10" t="n"/>
+      <c r="AE1334" s="10" t="n"/>
     </row>
     <row r="1335">
-      <c r="Z1335" s="10" t="n"/>
+      <c r="AD1335" s="10" t="n"/>
+      <c r="AE1335" s="10" t="n"/>
     </row>
     <row r="1336">
-      <c r="Z1336" s="10" t="n"/>
+      <c r="AD1336" s="10" t="n"/>
+      <c r="AE1336" s="10" t="n"/>
     </row>
     <row r="1337">
-      <c r="Z1337" s="10" t="n"/>
+      <c r="AD1337" s="10" t="n"/>
+      <c r="AE1337" s="10" t="n"/>
     </row>
     <row r="1338">
-      <c r="Z1338" s="10" t="n"/>
+      <c r="AD1338" s="10" t="n"/>
+      <c r="AE1338" s="10" t="n"/>
     </row>
     <row r="1339">
-      <c r="Z1339" s="10" t="n"/>
+      <c r="AD1339" s="10" t="n"/>
+      <c r="AE1339" s="10" t="n"/>
     </row>
     <row r="1340">
-      <c r="Z1340" s="10" t="n"/>
+      <c r="AD1340" s="10" t="n"/>
+      <c r="AE1340" s="10" t="n"/>
     </row>
     <row r="1341">
-      <c r="Z1341" s="10" t="n"/>
+      <c r="AD1341" s="10" t="n"/>
+      <c r="AE1341" s="10" t="n"/>
     </row>
     <row r="1342">
-      <c r="Z1342" s="10" t="n"/>
+      <c r="AD1342" s="10" t="n"/>
+      <c r="AE1342" s="10" t="n"/>
     </row>
     <row r="1343">
-      <c r="Z1343" s="10" t="n"/>
+      <c r="AD1343" s="10" t="n"/>
+      <c r="AE1343" s="10" t="n"/>
     </row>
     <row r="1344">
-      <c r="Z1344" s="10" t="n"/>
+      <c r="AD1344" s="10" t="n"/>
+      <c r="AE1344" s="10" t="n"/>
     </row>
     <row r="1345">
-      <c r="Z1345" s="10" t="n"/>
+      <c r="AD1345" s="10" t="n"/>
+      <c r="AE1345" s="10" t="n"/>
     </row>
     <row r="1346">
-      <c r="Z1346" s="10" t="n"/>
+      <c r="AD1346" s="10" t="n"/>
+      <c r="AE1346" s="10" t="n"/>
     </row>
     <row r="1347">
-      <c r="Z1347" s="10" t="n"/>
+      <c r="AD1347" s="10" t="n"/>
+      <c r="AE1347" s="10" t="n"/>
     </row>
     <row r="1348">
-      <c r="Z1348" s="10" t="n"/>
+      <c r="AD1348" s="10" t="n"/>
+      <c r="AE1348" s="10" t="n"/>
     </row>
     <row r="1349">
-      <c r="Z1349" s="10" t="n"/>
+      <c r="AD1349" s="10" t="n"/>
+      <c r="AE1349" s="10" t="n"/>
     </row>
     <row r="1350">
-      <c r="Z1350" s="10" t="n"/>
+      <c r="AD1350" s="10" t="n"/>
+      <c r="AE1350" s="10" t="n"/>
     </row>
     <row r="1351">
-      <c r="Z1351" s="10" t="n"/>
+      <c r="AD1351" s="10" t="n"/>
+      <c r="AE1351" s="10" t="n"/>
     </row>
     <row r="1352">
-      <c r="Z1352" s="10" t="n"/>
+      <c r="AD1352" s="10" t="n"/>
+      <c r="AE1352" s="10" t="n"/>
     </row>
     <row r="1353">
-      <c r="Z1353" s="10" t="n"/>
+      <c r="AD1353" s="10" t="n"/>
+      <c r="AE1353" s="10" t="n"/>
     </row>
     <row r="1354">
-      <c r="Z1354" s="10" t="n"/>
+      <c r="AD1354" s="10" t="n"/>
+      <c r="AE1354" s="10" t="n"/>
     </row>
     <row r="1355">
-      <c r="Z1355" s="10" t="n"/>
+      <c r="AD1355" s="10" t="n"/>
+      <c r="AE1355" s="10" t="n"/>
     </row>
     <row r="1356">
-      <c r="Z1356" s="10" t="n"/>
+      <c r="AD1356" s="10" t="n"/>
+      <c r="AE1356" s="10" t="n"/>
     </row>
     <row r="1357">
-      <c r="Z1357" s="10" t="n"/>
+      <c r="AD1357" s="10" t="n"/>
+      <c r="AE1357" s="10" t="n"/>
     </row>
     <row r="1358">
-      <c r="Z1358" s="10" t="n"/>
+      <c r="AD1358" s="10" t="n"/>
+      <c r="AE1358" s="10" t="n"/>
     </row>
     <row r="1359">
-      <c r="Z1359" s="10" t="n"/>
+      <c r="AD1359" s="10" t="n"/>
+      <c r="AE1359" s="10" t="n"/>
     </row>
     <row r="1360">
-      <c r="Z1360" s="10" t="n"/>
+      <c r="AD1360" s="10" t="n"/>
+      <c r="AE1360" s="10" t="n"/>
     </row>
     <row r="1361">
-      <c r="Z1361" s="10" t="n"/>
+      <c r="AD1361" s="10" t="n"/>
+      <c r="AE1361" s="10" t="n"/>
     </row>
     <row r="1362">
-      <c r="Z1362" s="10" t="n"/>
+      <c r="AD1362" s="10" t="n"/>
+      <c r="AE1362" s="10" t="n"/>
     </row>
     <row r="1363">
-      <c r="Z1363" s="10" t="n"/>
+      <c r="AD1363" s="10" t="n"/>
+      <c r="AE1363" s="10" t="n"/>
     </row>
     <row r="1364">
-      <c r="Z1364" s="10" t="n"/>
+      <c r="AD1364" s="10" t="n"/>
+      <c r="AE1364" s="10" t="n"/>
     </row>
     <row r="1365">
-      <c r="Z1365" s="10" t="n"/>
+      <c r="AD1365" s="10" t="n"/>
+      <c r="AE1365" s="10" t="n"/>
     </row>
     <row r="1366">
-      <c r="Z1366" s="10" t="n"/>
+      <c r="AD1366" s="10" t="n"/>
+      <c r="AE1366" s="10" t="n"/>
     </row>
     <row r="1367">
-      <c r="Z1367" s="10" t="n"/>
+      <c r="AD1367" s="10" t="n"/>
+      <c r="AE1367" s="10" t="n"/>
     </row>
     <row r="1368">
-      <c r="Z1368" s="10" t="n"/>
+      <c r="AD1368" s="10" t="n"/>
+      <c r="AE1368" s="10" t="n"/>
     </row>
     <row r="1369">
-      <c r="Z1369" s="10" t="n"/>
+      <c r="AD1369" s="10" t="n"/>
+      <c r="AE1369" s="10" t="n"/>
     </row>
     <row r="1370">
-      <c r="Z1370" s="10" t="n"/>
+      <c r="AD1370" s="10" t="n"/>
+      <c r="AE1370" s="10" t="n"/>
     </row>
     <row r="1371">
-      <c r="Z1371" s="10" t="n"/>
+      <c r="AD1371" s="10" t="n"/>
+      <c r="AE1371" s="10" t="n"/>
     </row>
     <row r="1372">
-      <c r="Z1372" s="10" t="n"/>
+      <c r="AD1372" s="10" t="n"/>
+      <c r="AE1372" s="10" t="n"/>
     </row>
     <row r="1373">
-      <c r="Z1373" s="10" t="n"/>
+      <c r="AD1373" s="10" t="n"/>
+      <c r="AE1373" s="10" t="n"/>
     </row>
     <row r="1374">
-      <c r="Z1374" s="10" t="n"/>
+      <c r="AD1374" s="10" t="n"/>
+      <c r="AE1374" s="10" t="n"/>
     </row>
     <row r="1375">
-      <c r="Z1375" s="10" t="n"/>
+      <c r="AD1375" s="10" t="n"/>
+      <c r="AE1375" s="10" t="n"/>
     </row>
     <row r="1376">
-      <c r="Z1376" s="10" t="n"/>
+      <c r="AD1376" s="10" t="n"/>
+      <c r="AE1376" s="10" t="n"/>
     </row>
     <row r="1377">
-      <c r="Z1377" s="10" t="n"/>
+      <c r="AD1377" s="10" t="n"/>
+      <c r="AE1377" s="10" t="n"/>
     </row>
     <row r="1378">
-      <c r="Z1378" s="10" t="n"/>
+      <c r="AD1378" s="10" t="n"/>
+      <c r="AE1378" s="10" t="n"/>
     </row>
     <row r="1379">
-      <c r="Z1379" s="10" t="n"/>
+      <c r="AD1379" s="10" t="n"/>
+      <c r="AE1379" s="10" t="n"/>
     </row>
     <row r="1380">
-      <c r="Z1380" s="10" t="n"/>
+      <c r="AD1380" s="10" t="n"/>
+      <c r="AE1380" s="10" t="n"/>
     </row>
     <row r="1381">
-      <c r="Z1381" s="10" t="n"/>
+      <c r="AD1381" s="10" t="n"/>
+      <c r="AE1381" s="10" t="n"/>
     </row>
     <row r="1382">
-      <c r="Z1382" s="10" t="n"/>
+      <c r="AD1382" s="10" t="n"/>
+      <c r="AE1382" s="10" t="n"/>
     </row>
     <row r="1383">
-      <c r="Z1383" s="10" t="n"/>
+      <c r="AD1383" s="10" t="n"/>
+      <c r="AE1383" s="10" t="n"/>
     </row>
     <row r="1384">
-      <c r="Z1384" s="10" t="n"/>
+      <c r="AD1384" s="10" t="n"/>
+      <c r="AE1384" s="10" t="n"/>
     </row>
     <row r="1385">
-      <c r="Z1385" s="10" t="n"/>
+      <c r="AD1385" s="10" t="n"/>
+      <c r="AE1385" s="10" t="n"/>
     </row>
     <row r="1386">
-      <c r="Z1386" s="10" t="n"/>
+      <c r="AD1386" s="10" t="n"/>
+      <c r="AE1386" s="10" t="n"/>
     </row>
     <row r="1387">
-      <c r="Z1387" s="10" t="n"/>
+      <c r="AD1387" s="10" t="n"/>
+      <c r="AE1387" s="10" t="n"/>
     </row>
     <row r="1388">
-      <c r="Z1388" s="10" t="n"/>
+      <c r="AD1388" s="10" t="n"/>
+      <c r="AE1388" s="10" t="n"/>
     </row>
     <row r="1389">
-      <c r="Z1389" s="10" t="n"/>
+      <c r="AD1389" s="10" t="n"/>
+      <c r="AE1389" s="10" t="n"/>
     </row>
     <row r="1390">
-      <c r="Z1390" s="10" t="n"/>
+      <c r="AD1390" s="10" t="n"/>
+      <c r="AE1390" s="10" t="n"/>
     </row>
     <row r="1391">
-      <c r="Z1391" s="10" t="n"/>
+      <c r="AD1391" s="10" t="n"/>
+      <c r="AE1391" s="10" t="n"/>
     </row>
     <row r="1392">
-      <c r="Z1392" s="10" t="n"/>
+      <c r="AD1392" s="10" t="n"/>
+      <c r="AE1392" s="10" t="n"/>
     </row>
     <row r="1393">
-      <c r="Z1393" s="10" t="n"/>
+      <c r="AD1393" s="10" t="n"/>
+      <c r="AE1393" s="10" t="n"/>
     </row>
     <row r="1394">
-      <c r="Z1394" s="10" t="n"/>
+      <c r="AD1394" s="10" t="n"/>
+      <c r="AE1394" s="10" t="n"/>
     </row>
     <row r="1395">
-      <c r="Z1395" s="10" t="n"/>
+      <c r="AD1395" s="10" t="n"/>
+      <c r="AE1395" s="10" t="n"/>
     </row>
     <row r="1396">
-      <c r="Z1396" s="10" t="n"/>
+      <c r="AD1396" s="10" t="n"/>
+      <c r="AE1396" s="10" t="n"/>
     </row>
     <row r="1397">
-      <c r="Z1397" s="10" t="n"/>
+      <c r="AD1397" s="10" t="n"/>
+      <c r="AE1397" s="10" t="n"/>
     </row>
     <row r="1398">
-      <c r="Z1398" s="10" t="n"/>
+      <c r="AD1398" s="10" t="n"/>
+      <c r="AE1398" s="10" t="n"/>
     </row>
     <row r="1399">
-      <c r="Z1399" s="10" t="n"/>
+      <c r="AD1399" s="10" t="n"/>
+      <c r="AE1399" s="10" t="n"/>
     </row>
     <row r="1400">
-      <c r="Z1400" s="10" t="n"/>
+      <c r="AD1400" s="10" t="n"/>
+      <c r="AE1400" s="10" t="n"/>
     </row>
     <row r="1401">
-      <c r="Z1401" s="10" t="n"/>
+      <c r="AD1401" s="10" t="n"/>
+      <c r="AE1401" s="10" t="n"/>
     </row>
     <row r="1402">
-      <c r="Z1402" s="10" t="n"/>
+      <c r="AD1402" s="10" t="n"/>
+      <c r="AE1402" s="10" t="n"/>
     </row>
     <row r="1403">
-      <c r="Z1403" s="10" t="n"/>
+      <c r="AD1403" s="10" t="n"/>
+      <c r="AE1403" s="10" t="n"/>
     </row>
     <row r="1404">
-      <c r="Z1404" s="10" t="n"/>
+      <c r="AD1404" s="10" t="n"/>
+      <c r="AE1404" s="10" t="n"/>
     </row>
     <row r="1405">
-      <c r="Z1405" s="10" t="n"/>
+      <c r="AD1405" s="10" t="n"/>
+      <c r="AE1405" s="10" t="n"/>
     </row>
     <row r="1406">
-      <c r="Z1406" s="10" t="n"/>
+      <c r="AD1406" s="10" t="n"/>
+      <c r="AE1406" s="10" t="n"/>
     </row>
     <row r="1407">
-      <c r="Z1407" s="10" t="n"/>
+      <c r="AD1407" s="10" t="n"/>
+      <c r="AE1407" s="10" t="n"/>
     </row>
     <row r="1408">
-      <c r="Z1408" s="10" t="n"/>
+      <c r="AD1408" s="10" t="n"/>
+      <c r="AE1408" s="10" t="n"/>
     </row>
     <row r="1409">
-      <c r="Z1409" s="10" t="n"/>
+      <c r="AD1409" s="10" t="n"/>
+      <c r="AE1409" s="10" t="n"/>
     </row>
     <row r="1410">
-      <c r="Z1410" s="10" t="n"/>
+      <c r="AD1410" s="10" t="n"/>
+      <c r="AE1410" s="10" t="n"/>
     </row>
     <row r="1411">
-      <c r="Z1411" s="10" t="n"/>
+      <c r="AD1411" s="10" t="n"/>
+      <c r="AE1411" s="10" t="n"/>
     </row>
     <row r="1412">
-      <c r="Z1412" s="10" t="n"/>
+      <c r="AD1412" s="10" t="n"/>
+      <c r="AE1412" s="10" t="n"/>
     </row>
     <row r="1413">
-      <c r="Z1413" s="10" t="n"/>
+      <c r="AD1413" s="10" t="n"/>
+      <c r="AE1413" s="10" t="n"/>
     </row>
     <row r="1414">
-      <c r="Z1414" s="10" t="n"/>
+      <c r="AD1414" s="10" t="n"/>
+      <c r="AE1414" s="10" t="n"/>
     </row>
     <row r="1415">
-      <c r="Z1415" s="10" t="n"/>
+      <c r="AD1415" s="10" t="n"/>
+      <c r="AE1415" s="10" t="n"/>
     </row>
     <row r="1416">
-      <c r="Z1416" s="10" t="n"/>
+      <c r="AD1416" s="10" t="n"/>
+      <c r="AE1416" s="10" t="n"/>
     </row>
     <row r="1417">
-      <c r="Z1417" s="10" t="n"/>
+      <c r="AD1417" s="10" t="n"/>
+      <c r="AE1417" s="10" t="n"/>
     </row>
     <row r="1418">
-      <c r="Z1418" s="10" t="n"/>
+      <c r="AD1418" s="10" t="n"/>
+      <c r="AE1418" s="10" t="n"/>
     </row>
     <row r="1419">
-      <c r="Z1419" s="10" t="n"/>
+      <c r="AD1419" s="10" t="n"/>
+      <c r="AE1419" s="10" t="n"/>
     </row>
     <row r="1420">
-      <c r="Z1420" s="10" t="n"/>
+      <c r="AD1420" s="10" t="n"/>
+      <c r="AE1420" s="10" t="n"/>
     </row>
     <row r="1421">
-      <c r="Z1421" s="10" t="n"/>
+      <c r="AD1421" s="10" t="n"/>
+      <c r="AE1421" s="10" t="n"/>
     </row>
     <row r="1422">
-      <c r="Z1422" s="10" t="n"/>
+      <c r="AD1422" s="10" t="n"/>
+      <c r="AE1422" s="10" t="n"/>
     </row>
     <row r="1423">
-      <c r="Z1423" s="10" t="n"/>
+      <c r="AD1423" s="10" t="n"/>
+      <c r="AE1423" s="10" t="n"/>
     </row>
     <row r="1424">
-      <c r="Z1424" s="10" t="n"/>
+      <c r="AD1424" s="10" t="n"/>
+      <c r="AE1424" s="10" t="n"/>
     </row>
     <row r="1425">
-      <c r="Z1425" s="10" t="n"/>
+      <c r="AD1425" s="10" t="n"/>
+      <c r="AE1425" s="10" t="n"/>
     </row>
     <row r="1426">
-      <c r="Z1426" s="10" t="n"/>
+      <c r="AD1426" s="10" t="n"/>
+      <c r="AE1426" s="10" t="n"/>
     </row>
     <row r="1427">
-      <c r="Z1427" s="10" t="n"/>
+      <c r="AD1427" s="10" t="n"/>
+      <c r="AE1427" s="10" t="n"/>
     </row>
     <row r="1428">
-      <c r="Z1428" s="10" t="n"/>
+      <c r="AD1428" s="10" t="n"/>
+      <c r="AE1428" s="10" t="n"/>
     </row>
     <row r="1429">
-      <c r="Z1429" s="10" t="n"/>
+      <c r="AD1429" s="10" t="n"/>
+      <c r="AE1429" s="10" t="n"/>
     </row>
     <row r="1430">
-      <c r="Z1430" s="10" t="n"/>
+      <c r="AD1430" s="10" t="n"/>
+      <c r="AE1430" s="10" t="n"/>
     </row>
     <row r="1431">
-      <c r="Z1431" s="10" t="n"/>
+      <c r="AD1431" s="10" t="n"/>
+      <c r="AE1431" s="10" t="n"/>
     </row>
     <row r="1432">
-      <c r="Z1432" s="10" t="n"/>
+      <c r="AD1432" s="10" t="n"/>
+      <c r="AE1432" s="10" t="n"/>
     </row>
     <row r="1433">
-      <c r="Z1433" s="10" t="n"/>
+      <c r="AD1433" s="10" t="n"/>
+      <c r="AE1433" s="10" t="n"/>
     </row>
     <row r="1434">
-      <c r="Z1434" s="10" t="n"/>
+      <c r="AD1434" s="10" t="n"/>
+      <c r="AE1434" s="10" t="n"/>
     </row>
     <row r="1435">
-      <c r="Z1435" s="10" t="n"/>
+      <c r="AD1435" s="10" t="n"/>
+      <c r="AE1435" s="10" t="n"/>
     </row>
     <row r="1436">
-      <c r="Z1436" s="10" t="n"/>
+      <c r="AD1436" s="10" t="n"/>
+      <c r="AE1436" s="10" t="n"/>
     </row>
     <row r="1437">
-      <c r="Z1437" s="10" t="n"/>
+      <c r="AD1437" s="10" t="n"/>
+      <c r="AE1437" s="10" t="n"/>
     </row>
     <row r="1438">
-      <c r="Z1438" s="10" t="n"/>
+      <c r="AD1438" s="10" t="n"/>
+      <c r="AE1438" s="10" t="n"/>
     </row>
     <row r="1439">
-      <c r="Z1439" s="10" t="n"/>
+      <c r="AD1439" s="10" t="n"/>
+      <c r="AE1439" s="10" t="n"/>
     </row>
     <row r="1440">
-      <c r="Z1440" s="10" t="n"/>
+      <c r="AD1440" s="10" t="n"/>
+      <c r="AE1440" s="10" t="n"/>
     </row>
     <row r="1441">
-      <c r="Z1441" s="10" t="n"/>
+      <c r="AD1441" s="10" t="n"/>
+      <c r="AE1441" s="10" t="n"/>
     </row>
     <row r="1442">
-      <c r="Z1442" s="10" t="n"/>
+      <c r="AD1442" s="10" t="n"/>
+      <c r="AE1442" s="10" t="n"/>
     </row>
     <row r="1443">
-      <c r="Z1443" s="10" t="n"/>
+      <c r="AD1443" s="10" t="n"/>
+      <c r="AE1443" s="10" t="n"/>
     </row>
     <row r="1444">
-      <c r="Z1444" s="10" t="n"/>
+      <c r="AD1444" s="10" t="n"/>
+      <c r="AE1444" s="10" t="n"/>
     </row>
     <row r="1445">
-      <c r="Z1445" s="10" t="n"/>
+      <c r="AD1445" s="10" t="n"/>
+      <c r="AE1445" s="10" t="n"/>
     </row>
     <row r="1446">
-      <c r="Z1446" s="10" t="n"/>
+      <c r="AD1446" s="10" t="n"/>
+      <c r="AE1446" s="10" t="n"/>
     </row>
     <row r="1447">
-      <c r="Z1447" s="10" t="n"/>
+      <c r="AD1447" s="10" t="n"/>
+      <c r="AE1447" s="10" t="n"/>
     </row>
     <row r="1448">
-      <c r="Z1448" s="10" t="n"/>
+      <c r="AD1448" s="10" t="n"/>
+      <c r="AE1448" s="10" t="n"/>
     </row>
     <row r="1449">
-      <c r="Z1449" s="10" t="n"/>
+      <c r="AD1449" s="10" t="n"/>
+      <c r="AE1449" s="10" t="n"/>
     </row>
     <row r="1450">
-      <c r="Z1450" s="10" t="n"/>
+      <c r="AD1450" s="10" t="n"/>
+      <c r="AE1450" s="10" t="n"/>
     </row>
     <row r="1451">
-      <c r="Z1451" s="10" t="n"/>
+      <c r="AD1451" s="10" t="n"/>
+      <c r="AE1451" s="10" t="n"/>
     </row>
     <row r="1452">
-      <c r="Z1452" s="10" t="n"/>
+      <c r="AD1452" s="10" t="n"/>
+      <c r="AE1452" s="10" t="n"/>
     </row>
     <row r="1453">
-      <c r="Z1453" s="10" t="n"/>
+      <c r="AD1453" s="10" t="n"/>
+      <c r="AE1453" s="10" t="n"/>
     </row>
     <row r="1454">
-      <c r="Z1454" s="10" t="n"/>
+      <c r="AD1454" s="10" t="n"/>
+      <c r="AE1454" s="10" t="n"/>
     </row>
     <row r="1455">
-      <c r="Z1455" s="10" t="n"/>
+      <c r="AD1455" s="10" t="n"/>
+      <c r="AE1455" s="10" t="n"/>
     </row>
     <row r="1456">
-      <c r="Z1456" s="10" t="n"/>
+      <c r="AD1456" s="10" t="n"/>
+      <c r="AE1456" s="10" t="n"/>
     </row>
     <row r="1457">
-      <c r="Z1457" s="10" t="n"/>
+      <c r="AD1457" s="10" t="n"/>
+      <c r="AE1457" s="10" t="n"/>
     </row>
     <row r="1458">
-      <c r="Z1458" s="10" t="n"/>
+      <c r="AD1458" s="10" t="n"/>
+      <c r="AE1458" s="10" t="n"/>
     </row>
     <row r="1459">
-      <c r="Z1459" s="10" t="n"/>
+      <c r="AD1459" s="10" t="n"/>
+      <c r="AE1459" s="10" t="n"/>
     </row>
     <row r="1460">
-      <c r="Z1460" s="10" t="n"/>
+      <c r="AD1460" s="10" t="n"/>
+      <c r="AE1460" s="10" t="n"/>
     </row>
     <row r="1461">
-      <c r="Z1461" s="10" t="n"/>
+      <c r="AD1461" s="10" t="n"/>
+      <c r="AE1461" s="10" t="n"/>
     </row>
     <row r="1462">
-      <c r="Z1462" s="10" t="n"/>
+      <c r="AD1462" s="10" t="n"/>
+      <c r="AE1462" s="10" t="n"/>
     </row>
     <row r="1463">
-      <c r="Z1463" s="10" t="n"/>
+      <c r="AD1463" s="10" t="n"/>
+      <c r="AE1463" s="10" t="n"/>
     </row>
     <row r="1464">
-      <c r="Z1464" s="10" t="n"/>
+      <c r="AD1464" s="10" t="n"/>
+      <c r="AE1464" s="10" t="n"/>
     </row>
     <row r="1465">
-      <c r="Z1465" s="10" t="n"/>
+      <c r="AD1465" s="10" t="n"/>
+      <c r="AE1465" s="10" t="n"/>
     </row>
     <row r="1466">
-      <c r="Z1466" s="10" t="n"/>
+      <c r="AD1466" s="10" t="n"/>
+      <c r="AE1466" s="10" t="n"/>
     </row>
     <row r="1467">
-      <c r="Z1467" s="10" t="n"/>
+      <c r="AD1467" s="10" t="n"/>
+      <c r="AE1467" s="10" t="n"/>
     </row>
     <row r="1468">
-      <c r="Z1468" s="10" t="n"/>
+      <c r="AD1468" s="10" t="n"/>
+      <c r="AE1468" s="10" t="n"/>
     </row>
     <row r="1469">
-      <c r="Z1469" s="10" t="n"/>
+      <c r="AD1469" s="10" t="n"/>
+      <c r="AE1469" s="10" t="n"/>
     </row>
     <row r="1470">
-      <c r="Z1470" s="10" t="n"/>
+      <c r="AD1470" s="10" t="n"/>
+      <c r="AE1470" s="10" t="n"/>
     </row>
     <row r="1471">
-      <c r="Z1471" s="10" t="n"/>
+      <c r="AD1471" s="10" t="n"/>
+      <c r="AE1471" s="10" t="n"/>
     </row>
     <row r="1472">
-      <c r="Z1472" s="10" t="n"/>
+      <c r="AD1472" s="10" t="n"/>
+      <c r="AE1472" s="10" t="n"/>
     </row>
     <row r="1473">
-      <c r="Z1473" s="10" t="n"/>
+      <c r="AD1473" s="10" t="n"/>
+      <c r="AE1473" s="10" t="n"/>
     </row>
     <row r="1474">
-      <c r="Z1474" s="10" t="n"/>
+      <c r="AD1474" s="10" t="n"/>
+      <c r="AE1474" s="10" t="n"/>
     </row>
     <row r="1475">
-      <c r="Z1475" s="10" t="n"/>
+      <c r="AD1475" s="10" t="n"/>
+      <c r="AE1475" s="10" t="n"/>
     </row>
     <row r="1476">
-      <c r="Z1476" s="10" t="n"/>
+      <c r="AD1476" s="10" t="n"/>
+      <c r="AE1476" s="10" t="n"/>
     </row>
     <row r="1477">
-      <c r="Z1477" s="10" t="n"/>
+      <c r="AD1477" s="10" t="n"/>
+      <c r="AE1477" s="10" t="n"/>
     </row>
     <row r="1478">
-      <c r="Z1478" s="10" t="n"/>
+      <c r="AD1478" s="10" t="n"/>
+      <c r="AE1478" s="10" t="n"/>
     </row>
     <row r="1479">
-      <c r="Z1479" s="10" t="n"/>
+      <c r="AD1479" s="10" t="n"/>
+      <c r="AE1479" s="10" t="n"/>
     </row>
     <row r="1480">
-      <c r="Z1480" s="10" t="n"/>
+      <c r="AD1480" s="10" t="n"/>
+      <c r="AE1480" s="10" t="n"/>
     </row>
     <row r="1481">
-      <c r="Z1481" s="10" t="n"/>
+      <c r="AD1481" s="10" t="n"/>
+      <c r="AE1481" s="10" t="n"/>
     </row>
     <row r="1482">
-      <c r="Z1482" s="10" t="n"/>
+      <c r="AD1482" s="10" t="n"/>
+      <c r="AE1482" s="10" t="n"/>
     </row>
     <row r="1483">
-      <c r="Z1483" s="10" t="n"/>
+      <c r="AD1483" s="10" t="n"/>
+      <c r="AE1483" s="10" t="n"/>
     </row>
     <row r="1484">
-      <c r="Z1484" s="10" t="n"/>
+      <c r="AD1484" s="10" t="n"/>
+      <c r="AE1484" s="10" t="n"/>
     </row>
     <row r="1485">
-      <c r="Z1485" s="10" t="n"/>
+      <c r="AD1485" s="10" t="n"/>
+      <c r="AE1485" s="10" t="n"/>
     </row>
     <row r="1486">
-      <c r="Z1486" s="10" t="n"/>
+      <c r="AD1486" s="10" t="n"/>
+      <c r="AE1486" s="10" t="n"/>
     </row>
     <row r="1487">
-      <c r="Z1487" s="10" t="n"/>
+      <c r="AD1487" s="10" t="n"/>
+      <c r="AE1487" s="10" t="n"/>
     </row>
     <row r="1488">
-      <c r="Z1488" s="10" t="n"/>
+      <c r="AD1488" s="10" t="n"/>
+      <c r="AE1488" s="10" t="n"/>
     </row>
     <row r="1489">
-      <c r="Z1489" s="10" t="n"/>
+      <c r="AD1489" s="10" t="n"/>
+      <c r="AE1489" s="10" t="n"/>
     </row>
     <row r="1490">
-      <c r="Z1490" s="10" t="n"/>
+      <c r="AD1490" s="10" t="n"/>
+      <c r="AE1490" s="10" t="n"/>
     </row>
     <row r="1491">
-      <c r="Z1491" s="10" t="n"/>
+      <c r="AD1491" s="10" t="n"/>
+      <c r="AE1491" s="10" t="n"/>
     </row>
     <row r="1492">
-      <c r="Z1492" s="10" t="n"/>
+      <c r="AD1492" s="10" t="n"/>
+      <c r="AE1492" s="10" t="n"/>
     </row>
     <row r="1493">
-      <c r="Z1493" s="10" t="n"/>
+      <c r="AD1493" s="10" t="n"/>
+      <c r="AE1493" s="10" t="n"/>
     </row>
     <row r="1494">
-      <c r="Z1494" s="10" t="n"/>
+      <c r="AD1494" s="10" t="n"/>
+      <c r="AE1494" s="10" t="n"/>
     </row>
     <row r="1495">
-      <c r="Z1495" s="10" t="n"/>
+      <c r="AD1495" s="10" t="n"/>
+      <c r="AE1495" s="10" t="n"/>
     </row>
     <row r="1496">
-      <c r="Z1496" s="10" t="n"/>
+      <c r="AD1496" s="10" t="n"/>
+      <c r="AE1496" s="10" t="n"/>
     </row>
     <row r="1497">
-      <c r="Z1497" s="10" t="n"/>
+      <c r="AD1497" s="10" t="n"/>
+      <c r="AE1497" s="10" t="n"/>
     </row>
     <row r="1498">
-      <c r="Z1498" s="10" t="n"/>
+      <c r="AD1498" s="10" t="n"/>
+      <c r="AE1498" s="10" t="n"/>
     </row>
     <row r="1499">
-      <c r="Z1499" s="10" t="n"/>
+      <c r="AD1499" s="10" t="n"/>
+      <c r="AE1499" s="10" t="n"/>
     </row>
     <row r="1500">
-      <c r="Z1500" s="10" t="n"/>
+      <c r="AD1500" s="10" t="n"/>
+      <c r="AE1500" s="10" t="n"/>
     </row>
     <row r="1501">
-      <c r="Z1501" s="10" t="n"/>
+      <c r="AD1501" s="10" t="n"/>
+      <c r="AE1501" s="10" t="n"/>
     </row>
     <row r="1502">
-      <c r="Z1502" s="10" t="n"/>
+      <c r="AD1502" s="10" t="n"/>
+      <c r="AE1502" s="10" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AB1502"/>
+  <autoFilter ref="A2:AG1502"/>
   <conditionalFormatting sqref="A3:A1502">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND($A3&lt;&gt;"",COUNTIF($A$3:$A$1502,$A3)&gt;1)</formula>
@@ -14564,7 +16244,7 @@
       <formula>AND($E3&lt;&gt;"",COUNTIF(placeables!$A$3:$A$1502,$E3)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="24">
+  <dataValidations count="28">
     <dataValidation sqref="A3:A1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="ID format" error="IDs use UPPERCASE letters, digits, - and . with no spaces." type="custom">
       <formula1>AND(EXACT(A3,UPPER(A3)),ISERROR(SEARCH(" ",A3)))</formula1>
     </dataValidation>
@@ -14622,19 +16302,31 @@
     <dataValidation sqref="T3:T1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Whole number" error="Whole numbers only (cm, W, kg): no decimals, no units." type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="U3:U1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the list, or add a new one on the lists sheet." type="list">
+    <dataValidation sqref="U3:U1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Whole number" error="Whole numbers only (cm, W, kg): no decimals, no units." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="V3:V1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Whole number" error="Whole numbers only (cm, W, kg): no decimals, no units." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="W3:W1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Whole number" error="Whole numbers only (cm, W, kg): no decimals, no units." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="X3:X1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Whole number" error="Whole numbers only (cm, W, kg): no decimals, no units." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y3:Y1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the list, or add a new one on the lists sheet." type="list">
       <formula1>L_door</formula1>
     </dataValidation>
-    <dataValidation sqref="V3:V1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the list, or add a new one on the lists sheet." type="list">
+    <dataValidation sqref="Z3:Z1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the list, or add a new one on the lists sheet." type="list">
       <formula1>L_yesno</formula1>
     </dataValidation>
-    <dataValidation sqref="W3:W1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the list, or add a new one on the lists sheet." type="list">
+    <dataValidation sqref="AA3:AA1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the list, or add a new one on the lists sheet." type="list">
       <formula1>L_yesno</formula1>
     </dataValidation>
-    <dataValidation sqref="X3:X1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the list, or add a new one on the lists sheet." type="list">
+    <dataValidation sqref="AB3:AB1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the list, or add a new one on the lists sheet." type="list">
       <formula1>L_yesno</formula1>
     </dataValidation>
-    <dataValidation sqref="Y3:Y1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Percent full" error="A whole number from 0 to 100." type="whole" operator="between">
+    <dataValidation sqref="AC3:AC1502" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Percent full" error="A whole number from 0 to 100." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -18123,7 +19815,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GB-01</t>
+          <t>OVEN-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -18133,19 +19825,28 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Glove-2</t>
+          <t>Dry-60</t>
         </is>
       </c>
       <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>000456100</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Prep group</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>broken</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>decommissioned</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -18157,21 +19858,62 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>300</v>
-      </c>
-      <c r="O45" t="n">
-        <v>600</v>
-      </c>
-      <c r="P45" t="n">
-        <v>230</v>
-      </c>
-      <c r="R45" t="n">
-        <v>250</v>
+        <v>1200</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>left 2026-06-30, collected by the WEEE contractor</t>
+        </is>
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GB-01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ExampleCo</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Glove-2</t>
+        </is>
+      </c>
       <c r="D46" s="9" t="n"/>
       <c r="E46" s="9" t="n"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Analytics group</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>300</v>
+      </c>
+      <c r="O46" t="n">
+        <v>600</v>
+      </c>
+      <c r="P46" t="n">
+        <v>230</v>
+      </c>
+      <c r="R46" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="47">
       <c r="D47" s="9" t="n"/>
@@ -26197,7 +27939,45 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>I-0051</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Oven door seal</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>gasket; door gasket</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CAB-01.S2</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>spare-part</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>OVEN-01</t>
+        </is>
+      </c>
       <c r="J53" s="9" t="n"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>EXAMPLE WARNING: a spare for an oven that's gone</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="J54" s="9" t="n"/>

--- a/example/lab-data.original.xlsx
+++ b/example/lab-data.original.xlsx
@@ -1375,7 +1375,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Photos and SOPs aren't listed here: they're linked by file name (see README.md).</t>
+          <t>Photos and SOPs aren't listed here: they're linked by file name (see docs/adding-things.md).</t>
         </is>
       </c>
     </row>

--- a/example/lab-data.original.xlsx
+++ b/example/lab-data.original.xlsx
@@ -21,7 +21,7 @@
     <sheet name="lists" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="L_category">lists!$A$2:$A$25</definedName>
+    <definedName name="L_category">lists!$A$2:$A$44</definedName>
     <definedName name="L_mount">lists!$D$2:$D$7</definedName>
     <definedName name="L_faces">lists!$G$2:$G$9</definedName>
     <definedName name="L_shape">lists!$J$2:$J$5</definedName>
@@ -33,13 +33,13 @@
     <definedName name="L_usage">lists!$AB$2:$AB$6</definedName>
     <definedName name="L_usage_source">lists!$AE$2:$AE$4</definedName>
     <definedName name="L_plug_type">lists!$AH$2:$AH$8</definedName>
-    <definedName name="L_service_type">lists!$AK$2:$AK$10</definedName>
-    <definedName name="L_item_category">lists!$AN$2:$AN$8</definedName>
+    <definedName name="L_service_type">lists!$AK$2:$AK$11</definedName>
+    <definedName name="L_item_category">lists!$AN$2:$AN$12</definedName>
     <definedName name="L_backed">lists!$AQ$2:$AQ$4</definedName>
     <definedName name="L_phase">lists!$AT$2:$AT$3</definedName>
     <definedName name="L_doc_type">lists!$AW$2:$AW$7</definedName>
     <definedName name="L_doc_status">lists!$AZ$2:$AZ$5</definedName>
-    <definedName name="L_link_type">lists!$BC$2:$BC$11</definedName>
+    <definedName name="L_link_type">lists!$BC$2:$BC$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rooms'!$A$2:$K$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'placeables'!$A$2:$AG$1502</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'equipment'!$A$2:$V$1002</definedName>
@@ -566,7 +566,7 @@
     </comment>
     <comment ref="AF1" authorId="0" shapeId="0">
       <text>
-        <t>What it is or does, for the keep_apart sheet: e.g. vibrates, vibration-sensitive, heat-source, flammable. Anything tagged there is kept at the distance it sets.</t>
+        <t>What it is or does, for the keep_apart sheet: vibrates, vibration-sensitive, emits-light, needs-dark, emi-source, emi-sensitive, heat-source, heat-sensitive, ignition-source, flammable, oxidiser, high-voltage, noisy, quiet. Its category counts as a tag too.</t>
       </text>
     </comment>
   </commentList>
@@ -866,7 +866,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>A tag used in the tags column of the placeables sheet.</t>
+        <t>A tag used in the tags column of the placeables sheet, or a category (laser, door...).</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -1401,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1482,23 +1482,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>balances and microscopes read wrong next to centrifuges, vacuum pumps and shakers</t>
+          <t>vacuum pumps, chillers and compressors shake probe stations, balances, microscopes and optics</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>heat-source</t>
+          <t>emits-light</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>heat-sensitive</t>
+          <t>needs-dark</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1507,55 +1507,155 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>fridges, freezers and samples struggle next to ovens, hotplates and hot exhaust air</t>
+          <t>stray light from solar simulators, lasers and lamps spoils dark and low-light measurements (dark I-V, PL, EQE): keep apart, or behind curtains or in a dark box</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>flammable</t>
+          <t>laser</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>oxidiser</t>
+          <t>door</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>problem</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>flammables and oxidisers are stored apart, or in separate cabinets</t>
+          <t>class 3B / 4 beams away from doorways, or behind interlocked curtains</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>emi-source</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>emi-sensitive</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>150</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>motors, RF and high-voltage supplies couple noise into low-current measurements</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ignition-source</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>flammable</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>problem</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>hotplates, furnaces, sparks and high voltage (corona) away from solvents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>flammable</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>oxidiser</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>300</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>problem</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>flammables and oxidisers are stored apart, or in separate cabinets</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>heat-source</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>heat-sensitive</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>samples, gloveboxes and fridges struggle next to furnaces, hotplates and lamp housings</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>noisy</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>quiet</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C10" t="n">
         <v>200</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>warning</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>desks and write-up areas away from pumps and compressors</t>
         </is>
@@ -1891,10 +1991,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG35"/>
+  <dimension ref="A1:BG57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="2" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -1934,7 +2034,7 @@
     <col width="30" customWidth="1" min="38" max="38"/>
     <col width="2" customWidth="1" min="39" max="39"/>
     <col width="15" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="38" customWidth="1" min="41" max="41"/>
     <col width="2" customWidth="1" min="42" max="42"/>
     <col width="11" customWidth="1" min="43" max="43"/>
     <col width="21" customWidth="1" min="44" max="44"/>
@@ -1948,7 +2048,7 @@
     <col width="11" customWidth="1" min="52" max="52"/>
     <col width="22" customWidth="1" min="53" max="53"/>
     <col width="2" customWidth="1" min="54" max="54"/>
-    <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="14" customWidth="1" min="55" max="55"/>
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="2" customWidth="1" min="57" max="57"/>
     <col width="13" customWidth="1" min="58" max="58"/>
@@ -2328,12 +2428,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>desk</t>
+          <t>optical-table</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>write-up or computer desk</t>
+          <t>optical table or breadboard: things stand on it</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2489,24 +2589,24 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>DESK</t>
+          <t>OPT</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>desk</t>
+          <t>optical table / breadboard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>desk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>free-standing table, balance table</t>
+          <t>write-up or computer desk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2606,7 +2706,12 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>glassware</t>
+          <t>substrate</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>wafers, glass, ITO / FTO slides</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -2644,24 +2749,24 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>TBL</t>
+          <t>DESK</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>desk</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cabinet</t>
+          <t>table</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>floor-standing cupboard</t>
+          <t>free-standing table</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2741,7 +2846,12 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>spare-part</t>
+          <t>optics</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>lenses, filters, fibres, mirrors</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -2769,24 +2879,24 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>TBL</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>cabinet</t>
+          <t>table</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>shelf</t>
+          <t>cabinet</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>wall shelf or shelving unit</t>
+          <t>cupboard; solvent, acid or gas cabinet</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2851,7 +2961,12 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>cable</t>
+          <t>electronics</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>components, connectors, probe tips</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2874,24 +2989,24 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>SHELF</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>shelf / shelving unit</t>
+          <t>cabinet</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>drawer</t>
+          <t>shelf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>drawer (mount = in)</t>
+          <t>wall shelf or shelving unit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2946,7 +3061,12 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>documentation</t>
+          <t>chemical</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>precursors, solvents: see the COSHH forms</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -2964,24 +3084,24 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>PED</t>
+          <t>SHELF</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>drawer pedestal</t>
+          <t>shelf / shelving unit</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>drawer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>drawer unit, often on castors</t>
+          <t>drawer (mount = in)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3021,34 +3141,37 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>glassware</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>gas-line</t>
-        </is>
+          <t>coax</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>500</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>PED</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>box, bin, tray</t>
+          <t>drawer pedestal</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>container</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>box, bin or tray holding items</t>
+          <t>drawer unit, often on castors</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3071,31 +3194,39 @@
           <t>network port</t>
         </is>
       </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>spare-part</t>
+        </is>
+      </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>water-line</t>
-        </is>
+          <t>triax</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>300</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>cart / trolley</t>
+          <t>box, bin, tray</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cart</t>
+          <t>container</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>trolley</t>
+          <t>box, bin or tray holding items</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3108,212 +3239,284 @@
           <t>extraction point / snorkel</t>
         </is>
       </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>cable</t>
+        </is>
+      </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>exhaust</t>
-        </is>
+          <t>fiber</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>1000</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>FRG</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>fridge</t>
+          <t>cart / trolley</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>cart</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>any instrument or device</t>
+          <t>trolley</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>earth</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>clean earth / ground point</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>documentation</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
+          <t>hv-cable</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>300</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>FRZ</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>freezer</t>
+          <t>source-measure unit</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>power-supply</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PC, controller</t>
-        </is>
+          <t>DC or high-voltage supply, source-measure unit (SMU)</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>interlock</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>1000</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>PSU</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>incubator</t>
+          <t>power supply</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>monitor</t>
+          <t>measurement</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>oscilloscope, lock-in, LCR / impedance analyser, electrometer, logger</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>gas-line</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>SCOPE</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>fume hood / cabinet</t>
+          <t>oscilloscope</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fridge</t>
+          <t>probe-station</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fridge</t>
-        </is>
+          <t>probe station, test fixture</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>vacuum-line</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>200</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>SINK</t>
+          <t>LIA</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>sink</t>
+          <t>lock-in amplifier</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>freezer</t>
+          <t>sun-simulator</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-20, -80, LN2 dewar</t>
+          <t>solar simulator: xenon, LED or halogen</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>cooling-line</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>PRB</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>probe station</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fume-hood</t>
+          <t>laser</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fume hood, extraction or biosafety cabinet</t>
+          <t>laser source: note its class in notes</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>water-line</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>MON</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>monitor</t>
+          <t>solar simulator</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sink</t>
+          <t>light-source</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sink bowl, drainer</t>
+          <t>lamp, LED or monochromator source</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>exhaust</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAS</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>laser</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gas-cylinder</t>
+          <t>spectrometer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gas cylinder</t>
+          <t>UV-Vis, PL, EQE / IPCE, FTIR, Raman</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>CEN</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>centrifuge</t>
+          <t>LED / lamp source</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>safety</t>
+          <t>microscope</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eyewash, shower, extinguisher, spill kit</t>
+          <t>optical microscope, AFM, SEM</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -3330,245 +3533,699 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>structure</t>
+          <t>dark-box</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>column, pipe boxing, radiator, electrical panel</t>
+          <t>light-tight measurement enclosure</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>PUMP</t>
+          <t>EQE</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>pump</t>
+          <t>EQE / IPCE system</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>door</t>
+          <t>glovebox</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>door; clear_front = swing</t>
+          <t>inert-gas glovebox: give it inner_w/d/h/z</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>MIC</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>gas cylinder</t>
+          <t>microscope</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>window</t>
+          <t>fume-hood</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mount = wall, z = sill height</t>
+          <t>fume hood or extraction cabinet</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>EYE</t>
+          <t>DARK</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>eyewash</t>
+          <t>dark box</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>workspace</t>
+          <t>vacuum-chamber</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>working area that must stay clear</t>
+          <t>evaporator, sputter coater, ALD, vacuum oven</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>glovebox</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>overhead</t>
+          <t>vacuum-pump</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>duct, beam, cable tray, light: mount = wall, z = underside</t>
+          <t>rotary, scroll or turbo pump</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>PANEL</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>electrical panel</t>
+          <t>fume hood</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>corona-box</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>corona charging box: high voltage, ozone</t>
+        </is>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>EVAP</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>evaporator</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>spin-coater</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>spin coater</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>SPUT</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>sputter coater</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>hotplate</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>hotplate, stirrer</t>
+        </is>
+      </c>
+      <c r="BF27" t="inlineStr">
+        <is>
+          <t>VAC</t>
+        </is>
+      </c>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>vacuum pump</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>oven</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>oven, furnace, annealing</t>
+        </is>
+      </c>
+      <c r="BF28" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>corona box</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>chiller</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>recirculating chiller</t>
+        </is>
+      </c>
+      <c r="BF29" t="inlineStr">
+        <is>
+          <t>SPIN</t>
+        </is>
+      </c>
+      <c r="BG29" t="inlineStr">
+        <is>
+          <t>spin coater</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>instrument</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>any other instrument or device</t>
+        </is>
+      </c>
+      <c r="BF30" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="BG30" t="inlineStr">
+        <is>
+          <t>hotplate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>computer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PC, controller</t>
+        </is>
+      </c>
+      <c r="BF31" t="inlineStr">
+        <is>
+          <t>OVEN</t>
+        </is>
+      </c>
+      <c r="BG31" t="inlineStr">
+        <is>
+          <t>oven</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>monitor</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="BF32" t="inlineStr">
+        <is>
+          <t>FURN</t>
+        </is>
+      </c>
+      <c r="BG32" t="inlineStr">
+        <is>
+          <t>furnace</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ups</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>uninterruptible power supply</t>
+        </is>
+      </c>
+      <c r="BF33" t="inlineStr">
+        <is>
+          <t>CHIL</t>
+        </is>
+      </c>
+      <c r="BG33" t="inlineStr">
+        <is>
+          <t>chiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fridge</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fridge: solvents, inks, samples</t>
+        </is>
+      </c>
+      <c r="BF34" t="inlineStr">
+        <is>
+          <t>CRYO</t>
+        </is>
+      </c>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>cryostat</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>freezer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>freezer: precursors, samples</t>
+        </is>
+      </c>
+      <c r="BF35" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>computer</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>gas-cylinder</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>gas cylinder</t>
+        </is>
+      </c>
+      <c r="BF36" t="inlineStr">
+        <is>
+          <t>MON</t>
+        </is>
+      </c>
+      <c r="BG36" t="inlineStr">
+        <is>
+          <t>monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sink</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sink bowl, drainer</t>
+        </is>
+      </c>
+      <c r="BF37" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>eyewash, shower, extinguisher, spill kit, emergency stop</t>
+        </is>
+      </c>
+      <c r="BF38" t="inlineStr">
+        <is>
+          <t>FRG</t>
+        </is>
+      </c>
+      <c r="BG38" t="inlineStr">
+        <is>
+          <t>fridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>column, pipe boxing, radiator, electrical panel</t>
+        </is>
+      </c>
+      <c r="BF39" t="inlineStr">
+        <is>
+          <t>FRZ</t>
+        </is>
+      </c>
+      <c r="BG39" t="inlineStr">
+        <is>
+          <t>freezer</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>door</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>door; clear_front = swing</t>
+        </is>
+      </c>
+      <c r="BF40" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="BG40" t="inlineStr">
+        <is>
+          <t>gas cylinder</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>mount = wall, z = sill height</t>
+        </is>
+      </c>
+      <c r="BF41" t="inlineStr">
+        <is>
+          <t>EYE</t>
+        </is>
+      </c>
+      <c r="BG41" t="inlineStr">
+        <is>
+          <t>eyewash</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>workspace</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>working area that must stay clear</t>
+        </is>
+      </c>
+      <c r="BF42" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="BG42" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>duct, beam, cable tray, light: mount = wall, z = underside</t>
+        </is>
+      </c>
+      <c r="BF43" t="inlineStr">
+        <is>
+          <t>PANEL</t>
+        </is>
+      </c>
+      <c r="BG43" t="inlineStr">
+        <is>
+          <t>electrical panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>other</t>
         </is>
       </c>
-      <c r="BF25" t="inlineStr">
+      <c r="BF44" t="inlineStr">
         <is>
           <t>DOOR</t>
         </is>
       </c>
-      <c r="BG25" t="inlineStr">
+      <c r="BG44" t="inlineStr">
         <is>
           <t>door</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="BF26" t="inlineStr">
+    <row r="45">
+      <c r="BF45" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="BG26" t="inlineStr">
+      <c r="BG45" t="inlineStr">
         <is>
           <t>window</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="BF27" t="inlineStr">
+    <row r="46">
+      <c r="BF46" t="inlineStr">
         <is>
           <t>WS</t>
         </is>
       </c>
-      <c r="BG27" t="inlineStr">
+      <c r="BG46" t="inlineStr">
         <is>
           <t>workspace</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="BF28" t="inlineStr">
+    <row r="47">
+      <c r="BF47" t="inlineStr">
+        <is>
+          <t>DUCT</t>
+        </is>
+      </c>
+      <c r="BG47" t="inlineStr">
+        <is>
+          <t>duct / overhead</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="BF48" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="BG28" t="inlineStr">
+      <c r="BG48" t="inlineStr">
         <is>
           <t>outlet</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="BF29" t="inlineStr">
+    <row r="49">
+      <c r="BF49" t="inlineStr">
         <is>
           <t>STRIP</t>
         </is>
       </c>
-      <c r="BG29" t="inlineStr">
+      <c r="BG49" t="inlineStr">
         <is>
           <t>power strip</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="BF30" t="inlineStr">
+    <row r="50">
+      <c r="BF50" t="inlineStr">
         <is>
           <t>NET</t>
         </is>
       </c>
-      <c r="BG30" t="inlineStr">
+      <c r="BG50" t="inlineStr">
         <is>
           <t>network port</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="BF31" t="inlineStr">
+    <row r="51">
+      <c r="BF51" t="inlineStr">
         <is>
           <t>GASTAP</t>
         </is>
       </c>
-      <c r="BG31" t="inlineStr">
+      <c r="BG51" t="inlineStr">
         <is>
           <t>gas tap</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="BF32" t="inlineStr">
+    <row r="52">
+      <c r="BF52" t="inlineStr">
+        <is>
+          <t>EXH</t>
+        </is>
+      </c>
+      <c r="BG52" t="inlineStr">
+        <is>
+          <t>extraction point</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="BF53" t="inlineStr">
+        <is>
+          <t>EARTH</t>
+        </is>
+      </c>
+      <c r="BG53" t="inlineStr">
+        <is>
+          <t>earth point</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="BF54" t="inlineStr">
         <is>
           <t>X.A  X.B</t>
         </is>
       </c>
-      <c r="BG32" t="inlineStr">
+      <c r="BG54" t="inlineStr">
         <is>
           <t>parts of a composed object</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="BF33" t="inlineStr">
+    <row r="55">
+      <c r="BF55" t="inlineStr">
         <is>
           <t>X.D1  X.D2</t>
         </is>
       </c>
-      <c r="BG33" t="inlineStr">
+      <c r="BG55" t="inlineStr">
         <is>
           <t>drawers, numbered from the top</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="BF34" t="inlineStr">
+    <row r="56">
+      <c r="BF56" t="inlineStr">
         <is>
           <t>X.S1  X.S2</t>
         </is>
       </c>
-      <c r="BG34" t="inlineStr">
+      <c r="BG56" t="inlineStr">
         <is>
           <t>shelves, numbered from the top</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="BF35" t="inlineStr">
+    <row r="57">
+      <c r="BF57" t="inlineStr">
         <is>
           <t>I-0001</t>
         </is>
       </c>
-      <c r="BG35" t="inlineStr">
+      <c r="BG57" t="inlineStr">
         <is>
           <t>items: just number them</t>
         </is>
@@ -3713,7 +4370,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wet lab (EXAMPLE)</t>
+          <t>Fabrication lab (EXAMPLE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3762,7 +4419,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Instrument room (EXAMPLE)</t>
+          <t>Characterisation lab (EXAMPLE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4889,7 +5546,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>hotplate</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4924,6 +5581,11 @@
       </c>
       <c r="AD9" s="10" t="n"/>
       <c r="AE9" s="10" t="n"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>heat-source; ignition-source</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4938,7 +5600,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>hotplate</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4973,6 +5635,11 @@
       </c>
       <c r="AD10" s="10" t="n"/>
       <c r="AE10" s="10" t="n"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>heat-source; ignition-source</t>
+        </is>
+      </c>
       <c r="AG10" t="inlineStr">
         <is>
           <t>EXAMPLE WARNING: 5 cm from the sash</t>
@@ -5039,12 +5706,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WB-01</t>
+          <t>BATH-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Water bath</t>
+          <t>Ultrasonic bath, heated (substrate cleaning)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5088,17 +5755,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUTO-01</t>
+          <t>FURN-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Benchtop autoclave</t>
+          <t>Split tube furnace</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>oven</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5138,29 +5805,29 @@
       <c r="AE13" s="10" t="n"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>heat-source</t>
+          <t>heat-source; ignition-source</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>top-loading lid</t>
+          <t>the split tube opens upwards: 40 cm above it</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PH-01</t>
+          <t>HYG-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pH meter</t>
+          <t>Humidity and temperature logger</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>measurement</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5438,7 +6105,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>spectrometer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5480,12 +6147,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CEN-01</t>
+          <t>UVO-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Benchtop centrifuge</t>
+          <t>UV-ozone cleaner</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5536,7 +6203,7 @@
       <c r="AE20" s="10" t="n"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>vibrates</t>
+          <t>emits-light</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -5816,7 +6483,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>spectrometer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5865,7 +6532,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>-20 freezer (under bench)</t>
+          <t>-20 freezer, precursor solutions (under bench)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5969,7 +6636,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Red parts box</t>
+          <t>Connectors box</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6131,7 +6798,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>vibration-sensitive: away from door, HVAC, centrifuge</t>
+          <t>weighs precursors; vibration-sensitive</t>
         </is>
       </c>
     </row>
@@ -6289,7 +6956,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Under-bench fridge</t>
+          <t>Under-bench fridge, inks and solvents (spark-free)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6346,17 +7013,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PUMP-01</t>
+          <t>VAC-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vacuum pump</t>
+          <t>Rotary vane pump (vacuum oven)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>vacuum-pump</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6396,7 +7063,7 @@
       <c r="AE36" s="10" t="n"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>vibrates; noisy</t>
+          <t>vibrates; noisy; emi-source</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
@@ -6413,7 +7080,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>-80 freezer</t>
+          <t>Chemicals freezer, upright (spark-free)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6484,7 +7151,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tall storage cabinet</t>
+          <t>Solvent cabinet (ventilated)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6532,6 +7199,11 @@
       </c>
       <c r="AD38" s="10" t="n"/>
       <c r="AE38" s="10" t="n"/>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>flammable</t>
+        </is>
+      </c>
       <c r="AG38" t="inlineStr">
         <is>
           <t>EXAMPLE PROBLEM: 230 cm tall, within 45 cm of a sprinklered ceiling</t>
@@ -6695,7 +7367,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Instrument PC</t>
+          <t>Spectrometer PC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6847,7 +7519,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Central lab table</t>
+          <t>Central table (I-V testing)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6905,12 +7577,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Microscope</t>
+          <t>Optical microscope</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>microscope</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7013,7 +7685,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>power-supply</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7053,6 +7725,11 @@
       </c>
       <c r="AD48" s="10" t="n"/>
       <c r="AE48" s="10" t="n"/>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>emi-sensitive</t>
+        </is>
+      </c>
       <c r="AG48" t="inlineStr">
         <is>
           <t>bottom of a stack of three</t>
@@ -7072,7 +7749,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>power-supply</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7112,6 +7789,11 @@
       </c>
       <c r="AD49" s="10" t="n"/>
       <c r="AE49" s="10" t="n"/>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>emi-sensitive</t>
+        </is>
+      </c>
       <c r="AG49" t="inlineStr">
         <is>
           <t>stacked on SMU-01</t>
@@ -7131,7 +7813,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>power-supply</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7166,6 +7848,11 @@
       </c>
       <c r="AD50" s="10" t="n"/>
       <c r="AE50" s="10" t="n"/>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>emi-sensitive</t>
+        </is>
+      </c>
       <c r="AG50" t="inlineStr">
         <is>
           <t>top of the stack</t>
@@ -7440,17 +8127,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>INC-01</t>
+          <t>OVEN-02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Incubator (arriving)</t>
+          <t>Vacuum oven (arriving)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>oven</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7764,7 +8451,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Prep bench</t>
+          <t>Optics bench</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7809,17 +8496,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EVAP-01</t>
+          <t>LAS-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nitrogen evaporator</t>
+          <t>Diode laser, 405 nm (class 3B)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>laser</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7854,6 +8541,11 @@
       </c>
       <c r="AD63" s="10" t="n"/>
       <c r="AE63" s="10" t="n"/>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>emits-light</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8109,7 +8801,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Standards and spares cabinet</t>
+          <t>Spares cabinet</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -8301,7 +8993,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LC-MS bench (around the chamfer)</t>
+          <t>Measurement bench (around the chamfer)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8346,7 +9038,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LC-MS bench, top run</t>
+          <t>Measurement bench, top run</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8401,7 +9093,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LC-MS bench, diagonal piece</t>
+          <t>Measurement bench, diagonal piece</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8466,7 +9158,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LC-MS bench, right run</t>
+          <t>Measurement bench, right run</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8521,17 +9213,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HPLC-01</t>
+          <t>PRB-01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HPLC stack</t>
+          <t>Probe station</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>probe-station</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8570,17 +9262,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MS-01</t>
+          <t>SUN-01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mass spectrometer (LC-MS)</t>
+          <t>Solar simulator (xenon, class AAA)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>sun-simulator</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8615,6 +9307,11 @@
       </c>
       <c r="AD78" s="10" t="n"/>
       <c r="AE78" s="10" t="n"/>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>emits-light; heat-source</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8722,7 +9419,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LC-MS PC</t>
+          <t>Measurement PC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8766,17 +9463,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PUMP-02</t>
+          <t>VAC-02</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MS roughing pump</t>
+          <t>Scroll pump (probe station)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>vacuum-pump</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -8830,7 +9527,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Fittings tray</t>
+          <t>Adapters tray (BNC, triax)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8931,17 +9628,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SONIC-01</t>
+          <t>COR-01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ultrasonic bath</t>
+          <t>Corona charging box</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>corona-box</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -8976,6 +9673,11 @@
       </c>
       <c r="AD85" s="10" t="n"/>
       <c r="AE85" s="10" t="n"/>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>high-voltage; ignition-source; emi-source</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9083,7 +9785,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nitrogen generator</t>
+          <t>Nitrogen generator (for the glovebox)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9137,7 +9839,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GC bench (two-tier)</t>
+          <t>Cryostat bench (two-tier)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9182,7 +9884,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GC bench, worktop</t>
+          <t>Cryostat bench, worktop</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9242,7 +9944,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GC bench, raised tier (upper)</t>
+          <t>Cryostat bench, raised tier (upper)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9301,7 +10003,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GC bench, raised tier (lower)</t>
+          <t>Cryostat bench, raised tier (lower)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -9355,12 +10057,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GC-01</t>
+          <t>CRYO-01</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Gas chromatograph</t>
+          <t>Optical cryostat (closed cycle)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9466,7 +10168,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>spectrometer</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -9559,7 +10261,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GC PC</t>
+          <t>Cryostat PC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -9608,7 +10310,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Standards box</t>
+          <t>Reference cells box</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -9660,7 +10362,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GC consumables box</t>
+          <t>Cryostat consumables box</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -9917,17 +10619,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CEN-02</t>
+          <t>LED-01</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Microcentrifuge</t>
+          <t>LED light source (white, 1 sun)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>light-source</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9967,7 +10669,7 @@
       <c r="AE104" s="10" t="n"/>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>vibrates</t>
+          <t>emits-light</t>
         </is>
       </c>
     </row>
@@ -9979,7 +10681,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Vortex mixer</t>
+          <t>Vortex mixer (sample prep)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -10023,17 +10725,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BAL-02</t>
+          <t>DARK-01</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Analytical balance</t>
+          <t>Dark box (low-light I-V)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>dark-box</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -10073,7 +10775,12 @@
       <c r="AE106" s="10" t="n"/>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>vibration-sensitive</t>
+          <t>needs-dark</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>EXAMPLE WARNING: 145 cm from the LED source</t>
         </is>
       </c>
     </row>
@@ -10336,7 +11043,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>H2 cylinder</t>
+          <t>N2 cylinder (purge)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -10553,7 +11260,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>instrument</t>
+          <t>glovebox</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16610,7 +17317,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -16635,7 +17342,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>analysis</t>
+          <t>optical</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -16688,7 +17395,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -16713,7 +17420,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>analysis</t>
+          <t>optical</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -16739,7 +17446,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CEN-01</t>
+          <t>UVO-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -16749,7 +17456,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spin-5</t>
+          <t>UVO-42</t>
         </is>
       </c>
       <c r="D5" s="9" t="n"/>
@@ -16760,7 +17467,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Prep group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -16785,7 +17492,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>sample-prep</t>
+          <t>cleaning</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -16815,7 +17522,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>manuals/CEN-01.pdf</t>
+          <t>manuals/UVO-01.pdf</t>
         </is>
       </c>
     </row>
@@ -16839,7 +17546,7 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Prep group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -16864,7 +17571,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>sample-prep</t>
+          <t>solution-prep</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -16913,7 +17620,7 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prep group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -16938,7 +17645,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>sample-prep</t>
+          <t>solution-prep</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -16970,7 +17677,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PUMP-01</t>
+          <t>VAC-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -16980,14 +17687,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vac-2</t>
+          <t>RV-5</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="9" t="n"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prep group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -17012,7 +17719,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>sample-prep</t>
+          <t>drying</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -17054,7 +17761,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ULT-500</t>
+          <t>CF-300</t>
         </is>
       </c>
       <c r="D9" s="9" t="n"/>
@@ -17145,7 +17852,7 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prep group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -17200,7 +17907,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>EXAMPLE PROBLEM: shares circuit DB2-C07 with CEN-01</t>
+          <t>EXAMPLE PROBLEM: shares circuit DB2-C07 with UVO-01</t>
         </is>
       </c>
     </row>
@@ -17224,7 +17931,7 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Prep group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -17313,7 +18020,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>synthesis</t>
+          <t>solution-prep</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -17348,14 +18055,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Stir-600</t>
+          <t>HS-600</t>
         </is>
       </c>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Prep group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -17380,7 +18087,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>synthesis</t>
+          <t>solution-prep</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -17427,14 +18134,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Stir-600</t>
+          <t>HS-600</t>
         </is>
       </c>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="9" t="n"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Prep group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -17459,7 +18166,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>synthesis</t>
+          <t>solution-prep</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -17496,7 +18203,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AUTO-01</t>
+          <t>FURN-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -17506,14 +18213,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Clave-20</t>
+          <t>TF-1200</t>
         </is>
       </c>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Prep group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -17538,7 +18245,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>sterilisation</t>
+          <t>annealing</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -17573,14 +18280,14 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>EXAMPLE PROBLEM: with the hotplates and water bath it overloads DB2-C10</t>
+          <t>EXAMPLE PROBLEM: with the hotplates and the bath it overloads DB2-C10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WB-01</t>
+          <t>BATH-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -17590,14 +18297,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bath-10</t>
+          <t>US-10H</t>
         </is>
       </c>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Prep group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -17622,7 +18329,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>sample-prep</t>
+          <t>cleaning</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -17659,7 +18366,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PH-01</t>
+          <t>HYG-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -17669,14 +18376,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>pH-7</t>
+          <t>RH-Log</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Prep group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -17701,7 +18408,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>sample-prep</t>
+          <t>solution-prep</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -17750,7 +18457,7 @@
       <c r="E18" s="9" t="n"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -17775,7 +18482,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>analysis</t>
+          <t>optical</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -17829,7 +18536,7 @@
       <c r="E19" s="9" t="n"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -17854,7 +18561,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>analysis</t>
+          <t>optical</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -17930,7 +18637,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>imaging</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -18009,7 +18716,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>imaging</t>
+          <t>inspection</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -18118,6 +18825,11 @@
           <t>STRIP-05</t>
         </is>
       </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>earth</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18280,7 +18992,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INC-01</t>
+          <t>OVEN-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -18290,14 +19002,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inc-150</t>
+          <t>VO-50</t>
         </is>
       </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Prep group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -18317,7 +19029,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>sample-prep</t>
+          <t>drying</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -18339,7 +19051,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R25" t="n">
@@ -18354,7 +19066,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HPLC-01</t>
+          <t>PRB-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -18364,14 +19076,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LC-100</t>
+          <t>PS-4</t>
         </is>
       </c>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -18396,7 +19108,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>lc-ms</t>
+          <t>device-testing</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -18433,7 +19145,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MS-01</t>
+          <t>SUN-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -18443,14 +19155,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MS-Q</t>
+          <t>SS-150X</t>
         </is>
       </c>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -18475,7 +19187,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>lc-ms</t>
+          <t>device-testing</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -18497,7 +19209,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R27" t="n">
@@ -18515,14 +19227,14 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>must stay under vacuum</t>
+          <t>the xenon lamp makes ozone: needs extraction</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PUMP-02</t>
+          <t>VAC-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -18532,14 +19244,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rough-5</t>
+          <t>SC-15</t>
         </is>
       </c>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -18564,7 +19276,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>lc-ms</t>
+          <t>device-testing</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -18586,7 +19298,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R28" t="n">
@@ -18618,7 +19330,7 @@
       <c r="E29" s="9" t="n"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -18643,7 +19355,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>lc-ms</t>
+          <t>device-testing</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -18702,7 +19414,7 @@
       <c r="E30" s="9" t="n"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -18727,7 +19439,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>lc-ms</t>
+          <t>device-testing</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -18761,7 +19473,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EVAP-01</t>
+          <t>LAS-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -18771,14 +19483,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Evap-12</t>
+          <t>DL-405</t>
         </is>
       </c>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -18803,7 +19515,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>lc-ms</t>
+          <t>photoluminescence</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -18835,7 +19547,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SONIC-01</t>
+          <t>COR-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -18845,14 +19557,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sonic-3</t>
+          <t>CC-30</t>
         </is>
       </c>
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="9" t="n"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -18877,7 +19589,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>lc-ms</t>
+          <t>device-testing</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -18931,7 +19643,7 @@
       <c r="E33" s="9" t="n"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -19002,7 +19714,7 @@
       <c r="E34" s="9" t="n"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -19076,7 +19788,7 @@
       <c r="E35" s="9" t="n"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -19101,7 +19813,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>lc-ms</t>
+          <t>glovebox</t>
         </is>
       </c>
       <c r="L35" t="n">
@@ -19138,7 +19850,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GC-01</t>
+          <t>CRYO-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -19148,14 +19860,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GC-8</t>
+          <t>CC-4K</t>
         </is>
       </c>
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="9" t="n"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -19180,7 +19892,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>gc</t>
+          <t>low-temperature</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -19215,7 +19927,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>gas:He; gas:H2</t>
+          <t>gas:He; gas:N2</t>
         </is>
       </c>
     </row>
@@ -19239,7 +19951,7 @@
       <c r="E37" s="9" t="n"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -19264,7 +19976,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>gc</t>
+          <t>low-temperature</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -19318,7 +20030,7 @@
       <c r="E38" s="9" t="n"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -19343,7 +20055,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>gc</t>
+          <t>low-temperature</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -19394,7 +20106,7 @@
       <c r="E39" s="9" t="n"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -19473,7 +20185,7 @@
       <c r="E40" s="9" t="n"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -19544,7 +20256,7 @@
       <c r="E41" s="9" t="n"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -19593,7 +20305,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CEN-02</t>
+          <t>LED-01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -19603,14 +20315,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mini-12</t>
+          <t>LED-1S</t>
         </is>
       </c>
       <c r="D42" s="9" t="n"/>
       <c r="E42" s="9" t="n"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -19635,7 +20347,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>lc-ms</t>
+          <t>device-testing</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -19684,7 +20396,7 @@
       <c r="E43" s="9" t="n"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -19709,7 +20421,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>lc-ms</t>
+          <t>sample-prep</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -19741,7 +20453,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BAL-02</t>
+          <t>DARK-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19751,14 +20463,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bal-220</t>
+          <t>DB-2</t>
         </is>
       </c>
       <c r="D44" s="9" t="n"/>
       <c r="E44" s="9" t="n"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Characterisation group</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -19783,7 +20495,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>lc-ms</t>
+          <t>device-testing</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -19836,7 +20548,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Prep group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -19886,7 +20598,7 @@
       <c r="E46" s="9" t="n"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Analytics group</t>
+          <t>Fabrication group</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -23804,7 +24516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24236,7 +24948,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>EXAMPLE PROBLEM: a 10 A socket with the autoclave on it</t>
+          <t>EXAMPLE PROBLEM: a 10 A socket with the tube furnace on it</t>
         </is>
       </c>
     </row>
@@ -24467,7 +25179,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>above the prep bench</t>
+          <t>above the optics bench</t>
         </is>
       </c>
     </row>
@@ -24511,7 +25223,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>UPS-backed, above the LC-MS</t>
+          <t>UPS-backed, above the solar simulator</t>
         </is>
       </c>
     </row>
@@ -24754,7 +25466,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>under the LC-MS bench</t>
+          <t>under the measurement bench</t>
         </is>
       </c>
     </row>
@@ -24855,7 +25567,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>under the GC bench</t>
+          <t>under the cryostat bench</t>
         </is>
       </c>
     </row>
@@ -24960,6 +25672,47 @@
       <c r="N24" t="inlineStr">
         <is>
           <t>the only extraction point in LAB-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EARTH-01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>earth</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LAB-A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TBL-01</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>150</v>
+      </c>
+      <c r="F25" t="n">
+        <v>45</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>clean earth bar</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>under the I-V table, for the SMUs</t>
         </is>
       </c>
     </row>
@@ -25345,7 +26098,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>prep bench and island</t>
+          <t>optics bench and island</t>
         </is>
       </c>
     </row>
@@ -25381,7 +26134,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>LC-MS, on the building UPS</t>
+          <t>measurement bench, on the building UPS</t>
         </is>
       </c>
     </row>
@@ -25453,7 +26206,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>GC bench</t>
+          <t>cryostat bench</t>
         </is>
       </c>
     </row>
@@ -25767,12 +26520,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HPLC-01</t>
+          <t>PRB-01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ethernet</t>
+          <t>triax</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>low-current measurement leads to the probes</t>
         </is>
       </c>
     </row>
@@ -25784,12 +26542,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MS-01</t>
+          <t>SUN-01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ethernet</t>
+          <t>usb</t>
         </is>
       </c>
     </row>
@@ -25813,17 +26571,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PUMP-02</t>
+          <t>VAC-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MS-01</t>
+          <t>PRB-01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>vacuum-line</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -25831,7 +26589,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>vacuum hose</t>
+          <t>vacuum chuck</t>
         </is>
       </c>
     </row>
@@ -25843,7 +26601,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MS-01</t>
+          <t>GB-01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -25854,25 +26612,32 @@
       <c r="D15" t="n">
         <v>1500</v>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>for the glovebox when it arrives</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N2G-01</t>
+          <t>LAS-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EVAP-01</t>
+          <t>PRB-01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>gas-line</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1500</v>
+          <t>fiber</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>laser light to the probe station</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -25883,7 +26648,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GC-01</t>
+          <t>CRYO-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -25917,7 +26682,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GC-01</t>
+          <t>CRYO-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -25930,7 +26695,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>carrier gas</t>
+          <t>helium for the cold head</t>
         </is>
       </c>
     </row>
@@ -25942,7 +26707,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GC-01</t>
+          <t>CRYO-01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -25955,7 +26720,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FID fuel</t>
+          <t>N2 purge of the window</t>
         </is>
       </c>
     </row>
@@ -26287,7 +27052,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CEN-01</t>
+          <t>UVO-01</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
@@ -26340,12 +27105,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Centrifuge adaptors for 15 mL tubes</t>
+          <t>UV lamp for the UV-ozone cleaner (spare)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>adapters; inserts; falcon adaptors</t>
+          <t>uv lamp; ozone lamp; low-pressure mercury lamp</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -26354,10 +27119,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -26366,7 +27131,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CEN-01</t>
+          <t>UVO-01</t>
         </is>
       </c>
       <c r="J8" s="9" t="n"/>
@@ -26613,12 +27378,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pH buffer solutions 4 / 7 / 10</t>
+          <t>Desiccant packs</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ph buffers; calibration buffers</t>
+          <t>silica gel; desiccant</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -26628,7 +27393,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3 bottles</t>
+          <t>3 bags</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -26639,7 +27404,7 @@
       <c r="J16" s="9" t="n"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>for PH-01</t>
+          <t>for the substrate boxes</t>
         </is>
       </c>
     </row>
@@ -26715,12 +27480,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Autoclave tape</t>
+          <t>Quartz boats</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>indicator tape; sterilisation tape</t>
+          <t>boats; combustion boats; crucibles</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -26728,10 +27493,8 @@
           <t>PED-01.D1</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>4 rolls</t>
-        </is>
+      <c r="F19" t="n">
+        <v>4</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -26741,7 +27504,7 @@
       <c r="J19" s="9" t="n"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>for AUTO-01</t>
+          <t>for FURN-01</t>
         </is>
       </c>
     </row>
@@ -26758,7 +27521,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>oven gloves; autoclave gloves; thermal gloves</t>
+          <t>oven gloves; furnace gloves; thermal gloves</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -26786,12 +27549,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Microscope slides</t>
+          <t>Glass substrates 25 × 25 mm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>slides; glass slides</t>
+          <t>glass slides; substrates; soda-lime glass</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -26806,7 +27569,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>consumable</t>
+          <t>substrate</t>
         </is>
       </c>
       <c r="J21" s="9" t="n"/>
@@ -26819,12 +27582,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cover slips</t>
+          <t>ITO substrates 25 × 25 mm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>coverslips; cover glass</t>
+          <t>ito; ito glass; indium tin oxide; substrates</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -26839,7 +27602,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>consumable</t>
+          <t>substrate</t>
         </is>
       </c>
       <c r="J22" s="9" t="n"/>
@@ -27031,7 +27794,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PUMP-01</t>
+          <t>VAC-01</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
@@ -27053,12 +27816,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HPLC vials 2 mL</t>
+          <t>Sample storage boxes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>autosampler vials; vials</t>
+          <t>membrane boxes; wafer boxes; sample boxes</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -27086,12 +27849,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vial caps with septa</t>
+          <t>Kapton tape</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>caps; septa; screw caps</t>
+          <t>polyimide tape; kapton</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -27099,10 +27862,8 @@
           <t>PED-02.D1</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2 boxes</t>
-        </is>
+      <c r="F29" t="n">
+        <v>4</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -27119,12 +27880,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Syringe filters 0.22 µm</t>
+          <t>Silver paste</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>filters; syringe filter; ptfe filters</t>
+          <t>conductive paste; silver epoxy; contact paste</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -27132,10 +27893,8 @@
           <t>PED-02.D2</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1 box</t>
-        </is>
+      <c r="F30" t="n">
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -27152,12 +27911,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Disposable syringes 5 mL</t>
+          <t>Indium wire</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>syringes</t>
+          <t>indium; contact wire</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -27167,7 +27926,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1 box</t>
+          <t>1 spool</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -27185,12 +27944,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HPLC column C18 (spare)</t>
+          <t>Xenon lamp 150 W (spare)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>column; c18; lc column</t>
+          <t>arc lamp; xe lamp; solar simulator lamp</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -27199,7 +27958,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -27211,13 +27970,13 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>HPLC-01</t>
+          <t>SUN-01</t>
         </is>
       </c>
       <c r="J32" s="9" t="n"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.example.com/columns/c18-150</t>
+          <t>https://www.example.com/lamps/xenon-150</t>
         </is>
       </c>
     </row>
@@ -27229,12 +27988,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Guard cartridges</t>
+          <t>Probe tips, tungsten</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>guard column; precolumn</t>
+          <t>probe needles; tips; tungsten tips</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -27255,7 +28014,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>HPLC-01</t>
+          <t>PRB-01</t>
         </is>
       </c>
       <c r="J33" s="9" t="n"/>
@@ -27273,12 +28032,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mobile phase bottles 1 L</t>
+          <t>Reference solar cell (calibrated)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>solvent bottles; reservoirs</t>
+          <t>reference cell; calibration cell; si reference</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -27287,14 +28046,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>glassware</t>
+          <t>tool</t>
         </is>
       </c>
       <c r="J34" s="9" t="n"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>for SUN-01: irradiance calibration</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -27304,12 +28068,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Solvent inlet filters</t>
+          <t>BNC to triax adapters</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>frits; sinker frits</t>
+          <t>triax; bnc; adapters</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -27322,12 +28086,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>spare-part</t>
+          <t>electronics</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>HPLC-01</t>
+          <t>PRB-01</t>
         </is>
       </c>
       <c r="J35" s="9" t="n"/>
@@ -27340,12 +28104,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PEEK tubing and fittings</t>
+          <t>BNC coax cables</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>fittings; ferrules; peek</t>
+          <t>bnc cables; coaxial cables; coax</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -27360,12 +28124,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>spare-part</t>
+          <t>cable</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>HPLC-01; MS-01</t>
+          <t>PRB-01; SUN-01</t>
         </is>
       </c>
       <c r="J36" s="9" t="n"/>
@@ -27378,12 +28142,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GC septa</t>
+          <t>Cryogenic grease</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>septum; inlet septa</t>
+          <t>apiezon; vacuum grease; n grease; thermal grease</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -27392,7 +28156,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -27402,7 +28166,7 @@
       <c r="J37" s="9" t="n"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>for GC-01</t>
+          <t>for CRYO-01</t>
         </is>
       </c>
     </row>
@@ -27414,12 +28178,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GC inlet liners</t>
+          <t>Cold-head O-rings</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>liner; liners</t>
+          <t>o-rings; seals; o ring</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -27440,7 +28204,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>GC-01</t>
+          <t>CRYO-01</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
@@ -27462,12 +28226,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GC column (spare)</t>
+          <t>Cryostat window, quartz (spare)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>capillary column</t>
+          <t>optical window; quartz window</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -27488,7 +28252,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>GC-01</t>
+          <t>CRYO-01</t>
         </is>
       </c>
       <c r="J39" s="9" t="n"/>
@@ -27501,12 +28265,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Graphite ferrules</t>
+          <t>Indium foil</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ferrule; ferrules</t>
+          <t>indium; thermal contact foil</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -27527,7 +28291,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>GC-01</t>
+          <t>CRYO-01</t>
         </is>
       </c>
       <c r="J40" s="9" t="n"/>
@@ -27640,12 +28404,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Calibration standards kit</t>
+          <t>Neutral density filters</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>standards; reference standards</t>
+          <t>nd filters; attenuators; filters</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -27653,12 +28417,14 @@
           <t>BOX-03</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1 set</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>consumable</t>
+          <t>optics</t>
         </is>
       </c>
       <c r="J44" s="9" t="n"/>
@@ -27671,12 +28437,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Microcentrifuge tubes 1.5 mL</t>
+          <t>Shadow masks, 0.1 cm² cells</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>eppendorf tubes; eppis; microtubes</t>
+          <t>masks; aperture masks; evaporation masks</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -27686,12 +28452,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2 bags</t>
+          <t>2 sets</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>consumable</t>
+          <t>tool</t>
         </is>
       </c>
       <c r="J45" s="9" t="n"/>
@@ -27704,12 +28470,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tube racks</t>
+          <t>Substrate racks (PTFE)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>racks; eppendorf racks</t>
+          <t>racks; cleaning racks; teflon racks</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -43032,12 +43798,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Benchtop autoclave operation</t>
+          <t>Tube furnace operation</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AUTO-01</t>
+          <t>FURN-01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -43080,12 +43846,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Balance calibration certificate</t>
+          <t>Balance and solar simulator irradiance calibration</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BAL-01; BAL-02</t>
+          <t>BAL-01; SUN-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -43123,7 +43889,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PAT tests, wet lab</t>
+          <t>PAT tests, fabrication lab</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -43151,22 +43917,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COSHH-022</t>
+          <t>RA-022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>coshh</t>
+          <t>risk-assessment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LC-MS mobile phase solvents</t>
+          <t>Optical radiation: solar simulator and laser</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HPLC-01; MS-01</t>
+          <t>SUN-01; LAS-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/example/lab-data.original.xlsx
+++ b/example/lab-data.original.xlsx
@@ -531,7 +531,7 @@
     </comment>
     <comment ref="Y1" authorId="0" shapeId="0">
       <text>
-        <t>Fridges, freezers, cabinets: which side the door is hinged on, as you face the front (left, right, both = double doors). The swing is kept clear in front, and door_gap (settings) beside the hinge so it opens fully.</t>
+        <t>Fridges, freezers, cabinets: which side the door is hinged on, as you face the front (left, right, both = double doors). The swing is kept clear in front. Something right beside the hinge is only a warning (the door still opens to 90 degrees): where you need more, measure it into clear_left or clear_right.</t>
       </text>
     </comment>
     <comment ref="Z1" authorId="0" shapeId="0">

--- a/example/lab-data.original.xlsx
+++ b/example/lab-data.original.xlsx
@@ -531,7 +531,7 @@
     </comment>
     <comment ref="Y1" authorId="0" shapeId="0">
       <text>
-        <t>Fridges, freezers, cabinets: which side the door is hinged on, as you face the front (left, right, both = double doors). The swing is kept clear in front. Something right beside the hinge is only a warning (the door still opens to 90 degrees): where you need more, measure it into clear_left or clear_right.</t>
+        <t>Fridges, freezers, cabinets: which side the door is hinged on, as you face the front (left, right, both = double doors). The width it sweeps opening to 90 degrees is kept clear in front. Nothing is kept clear beside the hinge, so cupboards can stand in a row: where a door has to open further back, measure that into clear_left or clear_right.</t>
       </text>
     </comment>
     <comment ref="Z1" authorId="0" shapeId="0">
@@ -1688,7 +1688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1902,11 +1902,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>door_gap</t>
+          <t>utility_reach</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1915,18 +1915,18 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kept free beside a door's hinge (door column) so it opens past 90 degrees.</t>
+          <t>How far a gas, water, drain, vacuum, air, network or exhaust point may be (needs column).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>utility_reach</t>
+          <t>sprinkler_clearance</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>300</v>
+        <v>45</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1935,18 +1935,18 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>How far a gas, water, drain, vacuum, air, network or exhaust point may be (needs column).</t>
+          <t>In rooms with sprinklers, nothing may reach higher than this below the ceiling.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sprinkler_clearance</t>
+          <t>sash_clearance</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,45 +1955,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>In rooms with sprinklers, nothing may reach higher than this below the ceiling.</t>
+          <t>Work inside a fume hood is kept at least this far behind the sash.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sash_clearance</t>
+          <t>stock_check_days</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cm</t>
+          <t>days</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
-        <is>
-          <t>Work inside a fume hood is kept at least this far behind the sash.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>stock_check_days</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>180</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
         <is>
           <t>Count the required spares (min_qty on the items sheet) at least this often.</t>
         </is>
@@ -2001,7 +1981,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Whole number" error="A whole number above 0, in the unit shown." type="whole" operator="greaterThan">
+    <dataValidation sqref="B2:B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Whole number" error="A whole number above 0, in the unit shown." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/example/lab-data.original.xlsx
+++ b/example/lab-data.original.xlsx
@@ -21,7 +21,7 @@
     <sheet name="lists" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="L_category">lists!$A$2:$A$44</definedName>
+    <definedName name="L_category">lists!$A$2:$A$45</definedName>
     <definedName name="L_mount">lists!$D$2:$D$7</definedName>
     <definedName name="L_faces">lists!$G$2:$G$9</definedName>
     <definedName name="L_shape">lists!$J$2:$J$5</definedName>
@@ -1996,7 +1996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG57"/>
+  <dimension ref="A1:BG58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2383,6 +2383,11 @@
           <t>tool</t>
         </is>
       </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>hand tools: clamps, saws, drivers, files</t>
+        </is>
+      </c>
       <c r="AQ2" t="inlineStr">
         <is>
           <t>none</t>
@@ -3780,12 +3785,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PC, controller</t>
+          <t>workshop machine or tool: 3D printer, drill, saw, grinder, soldering station</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
@@ -3802,12 +3807,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>monitor</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>screen</t>
+          <t>PC, controller</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
@@ -3824,12 +3829,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ups</t>
+          <t>monitor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>uninterruptible power supply</t>
+          <t>screen</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
@@ -3846,12 +3851,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fridge</t>
+          <t>ups</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>fridge: solvents, inks, samples</t>
+          <t>uninterruptible power supply</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
@@ -3868,369 +3873,391 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>freezer</t>
+          <t>fridge</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>freezer: precursors, samples</t>
+          <t>fridge: solvents, inks, samples</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>TOOL</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>workshop machine or tool</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gas-cylinder</t>
+          <t>freezer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>gas cylinder</t>
+          <t>freezer: precursors, samples</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>MON</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>monitor</t>
+          <t>computer</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sink</t>
+          <t>gas-cylinder</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>sink bowl, drainer</t>
+          <t>gas cylinder</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MON</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>monitor</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>safety</t>
+          <t>sink</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>eyewash, shower, extinguisher, spill kit, emergency stop</t>
+          <t>sink bowl, drainer</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>FRG</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr">
         <is>
-          <t>fridge</t>
+          <t>UPS</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>structure</t>
+          <t>safety</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>column, pipe boxing, radiator, electrical panel</t>
+          <t>eyewash, shower, extinguisher, spill kit, emergency stop</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>FRZ</t>
+          <t>FRG</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
         <is>
-          <t>freezer</t>
+          <t>fridge</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>door</t>
+          <t>structure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>door; clear_front = swing</t>
+          <t>column, pipe boxing, radiator, electrical panel</t>
         </is>
       </c>
       <c r="BF40" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>FRZ</t>
         </is>
       </c>
       <c r="BG40" t="inlineStr">
         <is>
-          <t>gas cylinder</t>
+          <t>freezer</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>window</t>
+          <t>door</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>mount = wall, z = sill height</t>
+          <t>door; clear_front = swing</t>
         </is>
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>EYE</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="BG41" t="inlineStr">
         <is>
-          <t>eyewash</t>
+          <t>gas cylinder</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>workspace</t>
+          <t>window</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>working area that must stay clear</t>
+          <t>mount = wall, z = sill height</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>EYE</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>eyewash</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>overhead</t>
+          <t>workspace</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>duct, beam, cable tray, light: mount = wall, z = underside</t>
+          <t>working area that must stay clear</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>PANEL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>electrical panel</t>
+          <t>column</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>duct, beam, cable tray, light: mount = wall, z = underside</t>
+        </is>
+      </c>
+      <c r="BF44" t="inlineStr">
+        <is>
+          <t>PANEL</t>
+        </is>
+      </c>
+      <c r="BG44" t="inlineStr">
+        <is>
+          <t>electrical panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>other</t>
         </is>
       </c>
-      <c r="BF44" t="inlineStr">
+      <c r="BF45" t="inlineStr">
         <is>
           <t>DOOR</t>
         </is>
       </c>
-      <c r="BG44" t="inlineStr">
+      <c r="BG45" t="inlineStr">
         <is>
           <t>door</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="BF45" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="BG45" t="inlineStr">
-        <is>
-          <t>window</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="BF46" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr">
         <is>
-          <t>workspace</t>
+          <t>window</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="BF47" t="inlineStr">
         <is>
-          <t>DUCT</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr">
         <is>
-          <t>duct / overhead</t>
+          <t>workspace</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="BF48" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>DUCT</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr">
         <is>
-          <t>outlet</t>
+          <t>duct / overhead</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="BF49" t="inlineStr">
         <is>
-          <t>STRIP</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>power strip</t>
+          <t>outlet</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="BF50" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>STRIP</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>network port</t>
+          <t>power strip</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="BF51" t="inlineStr">
         <is>
-          <t>GASTAP</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr">
         <is>
-          <t>gas tap</t>
+          <t>network port</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="BF52" t="inlineStr">
         <is>
-          <t>EXH</t>
+          <t>GASTAP</t>
         </is>
       </c>
       <c r="BG52" t="inlineStr">
         <is>
-          <t>extraction point</t>
+          <t>gas tap</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="BF53" t="inlineStr">
         <is>
-          <t>EARTH</t>
+          <t>EXH</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>earth point</t>
+          <t>extraction point</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="BF54" t="inlineStr">
         <is>
-          <t>X.A  X.B</t>
+          <t>EARTH</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>parts of a composed object</t>
+          <t>earth point</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="BF55" t="inlineStr">
         <is>
-          <t>X.D1  X.D2</t>
+          <t>X.A  X.B</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr">
         <is>
-          <t>drawers, numbered from the top</t>
+          <t>parts of a composed object</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="BF56" t="inlineStr">
         <is>
-          <t>X.S1  X.S2</t>
+          <t>X.D1  X.D2</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>shelves, numbered from the top</t>
+          <t>drawers, numbered from the top</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="BF57" t="inlineStr">
         <is>
+          <t>X.S1  X.S2</t>
+        </is>
+      </c>
+      <c r="BG57" t="inlineStr">
+        <is>
+          <t>shelves, numbered from the top</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="BF58" t="inlineStr">
+        <is>
           <t>I-0001</t>
         </is>
       </c>
-      <c r="BG57" t="inlineStr">
+      <c r="BG58" t="inlineStr">
         <is>
           <t>items: just number them</t>
         </is>

--- a/example/lab-data.original.xlsx
+++ b/example/lab-data.original.xlsx
@@ -536,7 +536,7 @@
     </comment>
     <comment ref="Z1" authorId="0" shapeId="0">
       <text>
-        <t>yes = plumbing, structure or safety equipment. The layout must work around it.</t>
+        <t>yes = plumbing, structure or safety equipment. The layout must work around it: it is locked in Inkscape and pull ignores moving it. One with no x and y yet isn't locked, so a new door or column can be dragged into place once.</t>
       </text>
     </comment>
     <comment ref="AA1" authorId="0" shapeId="0">

--- a/example/lab-data.original.xlsx
+++ b/example/lab-data.original.xlsx
@@ -17,8 +17,9 @@
     <sheet name="items" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="documents" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="keep_apart" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="settings" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="lists" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="accepted" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="settings" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="lists" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="L_category">lists!$A$2:$A$45</definedName>
@@ -49,6 +50,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'items'!$A$2:$N$5002</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'documents'!$A$2:$J$502</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'keep_apart'!$A$2:$E$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'accepted'!$A$2:$F$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -304,6 +306,41 @@
 </file>
 
 <file path=xl/comments/comment10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>lab-map</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>The check, as the report names it beside the problem: clear-zone, overlap, headroom... The report's 'To live with it' column has it ready to copy.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>The things involved, separated by commas. Name both to accept that pair only; name one to accept this rule wherever that thing is involved.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Why it's accepted, for whoever reads the report next.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Who decided.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Blank = for good. After this date it counts as a problem again: a reminder to look at it afresh.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment11.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>lab-map</author>
@@ -1187,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="125" customWidth="1" min="1" max="1"/>
@@ -1380,15 +1417,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>accepted sheet: problems you have decided to live with (a cupboard by a door that will just be like that). The report still shows them, with your reason, but doesn't count them. Copy rule and ids from the report's 'To live with it' column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>Photos and SOPs aren't listed here: they're linked by file name (see docs/adding-things.md).</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="n"/>
-    </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>This is the worked EXAMPLE. Your own data goes in ../lab-data.xlsx.</t>
         </is>
@@ -1684,6 +1728,691 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008C8C8C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F202"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>ids</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>by</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>until</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>e.g. clear-zone</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>e.g. CAB-18-01, DOOR-18</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>why it's all right</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>who</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>date, or blank</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="E3" s="10" t="n"/>
+    </row>
+    <row r="4">
+      <c r="E4" s="10" t="n"/>
+    </row>
+    <row r="5">
+      <c r="E5" s="10" t="n"/>
+    </row>
+    <row r="6">
+      <c r="E6" s="10" t="n"/>
+    </row>
+    <row r="7">
+      <c r="E7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="E8" s="10" t="n"/>
+    </row>
+    <row r="9">
+      <c r="E9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="E14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="E15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="E20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="E21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="E26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="E27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="E31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="E34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="E35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="E36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="E37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="E38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="E39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="E40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="E41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="E42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="E43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="E44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="E45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="E46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="E47" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="E48" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="E49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="E50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="E51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="E52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="E53" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="E54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="E55" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="E56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="E57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="E58" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="E59" s="10" t="n"/>
+    </row>
+    <row r="60">
+      <c r="E60" s="10" t="n"/>
+    </row>
+    <row r="61">
+      <c r="E61" s="10" t="n"/>
+    </row>
+    <row r="62">
+      <c r="E62" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="E63" s="10" t="n"/>
+    </row>
+    <row r="64">
+      <c r="E64" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="E65" s="10" t="n"/>
+    </row>
+    <row r="66">
+      <c r="E66" s="10" t="n"/>
+    </row>
+    <row r="67">
+      <c r="E67" s="10" t="n"/>
+    </row>
+    <row r="68">
+      <c r="E68" s="10" t="n"/>
+    </row>
+    <row r="69">
+      <c r="E69" s="10" t="n"/>
+    </row>
+    <row r="70">
+      <c r="E70" s="10" t="n"/>
+    </row>
+    <row r="71">
+      <c r="E71" s="10" t="n"/>
+    </row>
+    <row r="72">
+      <c r="E72" s="10" t="n"/>
+    </row>
+    <row r="73">
+      <c r="E73" s="10" t="n"/>
+    </row>
+    <row r="74">
+      <c r="E74" s="10" t="n"/>
+    </row>
+    <row r="75">
+      <c r="E75" s="10" t="n"/>
+    </row>
+    <row r="76">
+      <c r="E76" s="10" t="n"/>
+    </row>
+    <row r="77">
+      <c r="E77" s="10" t="n"/>
+    </row>
+    <row r="78">
+      <c r="E78" s="10" t="n"/>
+    </row>
+    <row r="79">
+      <c r="E79" s="10" t="n"/>
+    </row>
+    <row r="80">
+      <c r="E80" s="10" t="n"/>
+    </row>
+    <row r="81">
+      <c r="E81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="E82" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="E83" s="10" t="n"/>
+    </row>
+    <row r="84">
+      <c r="E84" s="10" t="n"/>
+    </row>
+    <row r="85">
+      <c r="E85" s="10" t="n"/>
+    </row>
+    <row r="86">
+      <c r="E86" s="10" t="n"/>
+    </row>
+    <row r="87">
+      <c r="E87" s="10" t="n"/>
+    </row>
+    <row r="88">
+      <c r="E88" s="10" t="n"/>
+    </row>
+    <row r="89">
+      <c r="E89" s="10" t="n"/>
+    </row>
+    <row r="90">
+      <c r="E90" s="10" t="n"/>
+    </row>
+    <row r="91">
+      <c r="E91" s="10" t="n"/>
+    </row>
+    <row r="92">
+      <c r="E92" s="10" t="n"/>
+    </row>
+    <row r="93">
+      <c r="E93" s="10" t="n"/>
+    </row>
+    <row r="94">
+      <c r="E94" s="10" t="n"/>
+    </row>
+    <row r="95">
+      <c r="E95" s="10" t="n"/>
+    </row>
+    <row r="96">
+      <c r="E96" s="10" t="n"/>
+    </row>
+    <row r="97">
+      <c r="E97" s="10" t="n"/>
+    </row>
+    <row r="98">
+      <c r="E98" s="10" t="n"/>
+    </row>
+    <row r="99">
+      <c r="E99" s="10" t="n"/>
+    </row>
+    <row r="100">
+      <c r="E100" s="10" t="n"/>
+    </row>
+    <row r="101">
+      <c r="E101" s="10" t="n"/>
+    </row>
+    <row r="102">
+      <c r="E102" s="10" t="n"/>
+    </row>
+    <row r="103">
+      <c r="E103" s="10" t="n"/>
+    </row>
+    <row r="104">
+      <c r="E104" s="10" t="n"/>
+    </row>
+    <row r="105">
+      <c r="E105" s="10" t="n"/>
+    </row>
+    <row r="106">
+      <c r="E106" s="10" t="n"/>
+    </row>
+    <row r="107">
+      <c r="E107" s="10" t="n"/>
+    </row>
+    <row r="108">
+      <c r="E108" s="10" t="n"/>
+    </row>
+    <row r="109">
+      <c r="E109" s="10" t="n"/>
+    </row>
+    <row r="110">
+      <c r="E110" s="10" t="n"/>
+    </row>
+    <row r="111">
+      <c r="E111" s="10" t="n"/>
+    </row>
+    <row r="112">
+      <c r="E112" s="10" t="n"/>
+    </row>
+    <row r="113">
+      <c r="E113" s="10" t="n"/>
+    </row>
+    <row r="114">
+      <c r="E114" s="10" t="n"/>
+    </row>
+    <row r="115">
+      <c r="E115" s="10" t="n"/>
+    </row>
+    <row r="116">
+      <c r="E116" s="10" t="n"/>
+    </row>
+    <row r="117">
+      <c r="E117" s="10" t="n"/>
+    </row>
+    <row r="118">
+      <c r="E118" s="10" t="n"/>
+    </row>
+    <row r="119">
+      <c r="E119" s="10" t="n"/>
+    </row>
+    <row r="120">
+      <c r="E120" s="10" t="n"/>
+    </row>
+    <row r="121">
+      <c r="E121" s="10" t="n"/>
+    </row>
+    <row r="122">
+      <c r="E122" s="10" t="n"/>
+    </row>
+    <row r="123">
+      <c r="E123" s="10" t="n"/>
+    </row>
+    <row r="124">
+      <c r="E124" s="10" t="n"/>
+    </row>
+    <row r="125">
+      <c r="E125" s="10" t="n"/>
+    </row>
+    <row r="126">
+      <c r="E126" s="10" t="n"/>
+    </row>
+    <row r="127">
+      <c r="E127" s="10" t="n"/>
+    </row>
+    <row r="128">
+      <c r="E128" s="10" t="n"/>
+    </row>
+    <row r="129">
+      <c r="E129" s="10" t="n"/>
+    </row>
+    <row r="130">
+      <c r="E130" s="10" t="n"/>
+    </row>
+    <row r="131">
+      <c r="E131" s="10" t="n"/>
+    </row>
+    <row r="132">
+      <c r="E132" s="10" t="n"/>
+    </row>
+    <row r="133">
+      <c r="E133" s="10" t="n"/>
+    </row>
+    <row r="134">
+      <c r="E134" s="10" t="n"/>
+    </row>
+    <row r="135">
+      <c r="E135" s="10" t="n"/>
+    </row>
+    <row r="136">
+      <c r="E136" s="10" t="n"/>
+    </row>
+    <row r="137">
+      <c r="E137" s="10" t="n"/>
+    </row>
+    <row r="138">
+      <c r="E138" s="10" t="n"/>
+    </row>
+    <row r="139">
+      <c r="E139" s="10" t="n"/>
+    </row>
+    <row r="140">
+      <c r="E140" s="10" t="n"/>
+    </row>
+    <row r="141">
+      <c r="E141" s="10" t="n"/>
+    </row>
+    <row r="142">
+      <c r="E142" s="10" t="n"/>
+    </row>
+    <row r="143">
+      <c r="E143" s="10" t="n"/>
+    </row>
+    <row r="144">
+      <c r="E144" s="10" t="n"/>
+    </row>
+    <row r="145">
+      <c r="E145" s="10" t="n"/>
+    </row>
+    <row r="146">
+      <c r="E146" s="10" t="n"/>
+    </row>
+    <row r="147">
+      <c r="E147" s="10" t="n"/>
+    </row>
+    <row r="148">
+      <c r="E148" s="10" t="n"/>
+    </row>
+    <row r="149">
+      <c r="E149" s="10" t="n"/>
+    </row>
+    <row r="150">
+      <c r="E150" s="10" t="n"/>
+    </row>
+    <row r="151">
+      <c r="E151" s="10" t="n"/>
+    </row>
+    <row r="152">
+      <c r="E152" s="10" t="n"/>
+    </row>
+    <row r="153">
+      <c r="E153" s="10" t="n"/>
+    </row>
+    <row r="154">
+      <c r="E154" s="10" t="n"/>
+    </row>
+    <row r="155">
+      <c r="E155" s="10" t="n"/>
+    </row>
+    <row r="156">
+      <c r="E156" s="10" t="n"/>
+    </row>
+    <row r="157">
+      <c r="E157" s="10" t="n"/>
+    </row>
+    <row r="158">
+      <c r="E158" s="10" t="n"/>
+    </row>
+    <row r="159">
+      <c r="E159" s="10" t="n"/>
+    </row>
+    <row r="160">
+      <c r="E160" s="10" t="n"/>
+    </row>
+    <row r="161">
+      <c r="E161" s="10" t="n"/>
+    </row>
+    <row r="162">
+      <c r="E162" s="10" t="n"/>
+    </row>
+    <row r="163">
+      <c r="E163" s="10" t="n"/>
+    </row>
+    <row r="164">
+      <c r="E164" s="10" t="n"/>
+    </row>
+    <row r="165">
+      <c r="E165" s="10" t="n"/>
+    </row>
+    <row r="166">
+      <c r="E166" s="10" t="n"/>
+    </row>
+    <row r="167">
+      <c r="E167" s="10" t="n"/>
+    </row>
+    <row r="168">
+      <c r="E168" s="10" t="n"/>
+    </row>
+    <row r="169">
+      <c r="E169" s="10" t="n"/>
+    </row>
+    <row r="170">
+      <c r="E170" s="10" t="n"/>
+    </row>
+    <row r="171">
+      <c r="E171" s="10" t="n"/>
+    </row>
+    <row r="172">
+      <c r="E172" s="10" t="n"/>
+    </row>
+    <row r="173">
+      <c r="E173" s="10" t="n"/>
+    </row>
+    <row r="174">
+      <c r="E174" s="10" t="n"/>
+    </row>
+    <row r="175">
+      <c r="E175" s="10" t="n"/>
+    </row>
+    <row r="176">
+      <c r="E176" s="10" t="n"/>
+    </row>
+    <row r="177">
+      <c r="E177" s="10" t="n"/>
+    </row>
+    <row r="178">
+      <c r="E178" s="10" t="n"/>
+    </row>
+    <row r="179">
+      <c r="E179" s="10" t="n"/>
+    </row>
+    <row r="180">
+      <c r="E180" s="10" t="n"/>
+    </row>
+    <row r="181">
+      <c r="E181" s="10" t="n"/>
+    </row>
+    <row r="182">
+      <c r="E182" s="10" t="n"/>
+    </row>
+    <row r="183">
+      <c r="E183" s="10" t="n"/>
+    </row>
+    <row r="184">
+      <c r="E184" s="10" t="n"/>
+    </row>
+    <row r="185">
+      <c r="E185" s="10" t="n"/>
+    </row>
+    <row r="186">
+      <c r="E186" s="10" t="n"/>
+    </row>
+    <row r="187">
+      <c r="E187" s="10" t="n"/>
+    </row>
+    <row r="188">
+      <c r="E188" s="10" t="n"/>
+    </row>
+    <row r="189">
+      <c r="E189" s="10" t="n"/>
+    </row>
+    <row r="190">
+      <c r="E190" s="10" t="n"/>
+    </row>
+    <row r="191">
+      <c r="E191" s="10" t="n"/>
+    </row>
+    <row r="192">
+      <c r="E192" s="10" t="n"/>
+    </row>
+    <row r="193">
+      <c r="E193" s="10" t="n"/>
+    </row>
+    <row r="194">
+      <c r="E194" s="10" t="n"/>
+    </row>
+    <row r="195">
+      <c r="E195" s="10" t="n"/>
+    </row>
+    <row r="196">
+      <c r="E196" s="10" t="n"/>
+    </row>
+    <row r="197">
+      <c r="E197" s="10" t="n"/>
+    </row>
+    <row r="198">
+      <c r="E198" s="10" t="n"/>
+    </row>
+    <row r="199">
+      <c r="E199" s="10" t="n"/>
+    </row>
+    <row r="200">
+      <c r="E200" s="10" t="n"/>
+    </row>
+    <row r="201">
+      <c r="E201" s="10" t="n"/>
+    </row>
+    <row r="202">
+      <c r="E202" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:F202"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00595959"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1989,7 +2718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A5A5A5"/>
